--- a/research/traditional_assets/database/data/bahrain/bahrain_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_telecom_services.xlsx
@@ -647,10 +647,10 @@
         <v>0.14312226263826</v>
       </c>
       <c r="X2">
-        <v>0.1327882010686699</v>
+        <v>0.1327940131085882</v>
       </c>
       <c r="Y2">
-        <v>0.0103340615695901</v>
+        <v>0.01032824952967173</v>
       </c>
       <c r="Z2">
         <v>0.9472282740256598</v>
@@ -659,10 +659,10 @@
         <v>0.2051150663069093</v>
       </c>
       <c r="AB2">
-        <v>0.1309606396660845</v>
+        <v>0.1309647948913874</v>
       </c>
       <c r="AC2">
-        <v>0.07415442664082481</v>
+        <v>0.07415027141552188</v>
       </c>
       <c r="AD2">
         <v>866.8</v>
@@ -781,10 +781,10 @@
         <v>0.14312226263826</v>
       </c>
       <c r="X3">
-        <v>0.1327882010686699</v>
+        <v>0.1327940131085882</v>
       </c>
       <c r="Y3">
-        <v>0.0103340615695901</v>
+        <v>0.01032824952967173</v>
       </c>
       <c r="Z3">
         <v>0.9472282740256598</v>
@@ -793,10 +793,10 @@
         <v>0.2051150663069093</v>
       </c>
       <c r="AB3">
-        <v>0.1309606396660845</v>
+        <v>0.1309647948913874</v>
       </c>
       <c r="AC3">
-        <v>0.07415442664082481</v>
+        <v>0.07415027141552188</v>
       </c>
       <c r="AD3">
         <v>866.8</v>
@@ -1151,13 +1151,13 @@
         <v>2173.9</v>
       </c>
       <c r="L2">
-        <v>4008.41832679338</v>
+        <v>4008.35367386677</v>
       </c>
       <c r="M2">
         <v>2620.1</v>
       </c>
       <c r="N2">
-        <v>3587.81832679338</v>
+        <v>3587.75367386677</v>
       </c>
       <c r="O2">
         <v>866.8</v>
@@ -1166,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.130960639666085</v>
+        <v>0.130964794891387</v>
       </c>
       <c r="R2">
-        <v>0.107990827869629</v>
+        <v>0.107994983094932</v>
       </c>
       <c r="S2">
         <v>0.126377188197372</v>
       </c>
       <c r="T2">
-        <v>0.106177188197372</v>
+        <v>0.104777188197372</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.13278820106867</v>
+        <v>0.132794013108588</v>
       </c>
       <c r="X2">
-        <v>0.107990827869629</v>
+        <v>0.107994983094932</v>
       </c>
       <c r="Y2">
         <v>0.745171901817582</v>
@@ -1230,7 +1230,7 @@
         <v>2173.9</v>
       </c>
       <c r="AK2">
-        <v>0.1167357503100869</v>
+        <v>0.1167435499062663</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1079908278696292</v>
+        <v>0.1079949830949321</v>
       </c>
       <c r="C2">
-        <v>4008.418326793379</v>
+        <v>4008.353673866769</v>
       </c>
       <c r="D2">
-        <v>3587.81832679338</v>
+        <v>3587.75367386677</v>
       </c>
       <c r="E2">
         <v>-866.8</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1079908278696292</v>
+        <v>0.1079949830949321</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1085945997516029</v>
+        <v>0.1085847549769058</v>
       </c>
       <c r="C3">
-        <v>3943.514350430496</v>
+        <v>3944.24492195147</v>
       </c>
       <c r="D3">
-        <v>3553.321350430496</v>
+        <v>3554.05192195147</v>
       </c>
       <c r="E3">
         <v>-836.3929999999999</v>
@@ -1533,37 +1533,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M3">
-        <v>3.228529761517481</v>
+        <v>3.18595996151748</v>
       </c>
       <c r="N3">
-        <v>302.9270257940381</v>
+        <v>302.9695955940381</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>302.9270257940381</v>
+        <v>302.9695955940381</v>
       </c>
       <c r="Q3">
-        <v>484.327025794038</v>
+        <v>484.3695955940381</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1086190180501305</v>
+        <v>0.1086232152474061</v>
       </c>
       <c r="T3">
         <v>0.5381300748336596</v>
       </c>
       <c r="U3">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>94.82816581243334</v>
+        <v>96.09523008874629</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1091983716335766</v>
+        <v>0.1091745268588795</v>
       </c>
       <c r="C4">
-        <v>3879.267435244558</v>
+        <v>3880.76343612045</v>
       </c>
       <c r="D4">
-        <v>3519.481435244558</v>
+        <v>3520.97743612045</v>
       </c>
       <c r="E4">
         <v>-805.986</v>
@@ -1615,37 +1615,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M4">
-        <v>6.457059523034961</v>
+        <v>6.371919923034961</v>
       </c>
       <c r="N4">
-        <v>299.6984960325206</v>
+        <v>299.7836356325206</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>299.6984960325206</v>
+        <v>299.7836356325206</v>
       </c>
       <c r="Q4">
-        <v>481.0984960325206</v>
+        <v>481.1836356325206</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1092600284383971</v>
+        <v>0.1092642684642164</v>
       </c>
       <c r="T4">
         <v>0.5436211980462479</v>
       </c>
       <c r="U4">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>47.41408290621668</v>
+        <v>48.04761504437315</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1098021435155503</v>
+        <v>0.1097642987408532</v>
       </c>
       <c r="C5">
-        <v>3815.658985839776</v>
+        <v>3817.891865574609</v>
       </c>
       <c r="D5">
-        <v>3486.279985839776</v>
+        <v>3488.512865574609</v>
       </c>
       <c r="E5">
         <v>-775.579</v>
@@ -1697,37 +1697,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M5">
-        <v>9.685589284552441</v>
+        <v>9.55787988455244</v>
       </c>
       <c r="N5">
-        <v>296.4699662710031</v>
+        <v>296.5976756710031</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>296.4699662710031</v>
+        <v>296.5976756710031</v>
       </c>
       <c r="Q5">
-        <v>477.8699662710031</v>
+        <v>477.9976756710031</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1099142555357002</v>
+        <v>0.1099185392731258</v>
       </c>
       <c r="T5">
         <v>0.5492255402941473</v>
       </c>
       <c r="U5">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.60938860414445</v>
+        <v>32.03174336291544</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.110405915397524</v>
+        <v>0.110354070622827</v>
       </c>
       <c r="C6">
-        <v>3752.671101950333</v>
+        <v>3755.61349358878</v>
       </c>
       <c r="D6">
-        <v>3453.699101950333</v>
+        <v>3456.641493588781</v>
       </c>
       <c r="E6">
         <v>-745.1719999999999</v>
@@ -1779,37 +1779,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M6">
-        <v>12.91411904606992</v>
+        <v>12.74383984606992</v>
       </c>
       <c r="N6">
-        <v>293.2414365094857</v>
+        <v>293.4117157094856</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>293.2414365094857</v>
+        <v>293.4117157094856</v>
       </c>
       <c r="Q6">
-        <v>474.6414365094856</v>
+        <v>474.8117157094856</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1105821123641971</v>
+        <v>0.1105864407238876</v>
       </c>
       <c r="T6">
         <v>0.5549466396722115</v>
       </c>
       <c r="U6">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.70704145310834</v>
+        <v>24.02380752218657</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1110096872794977</v>
+        <v>0.1109438425048007</v>
       </c>
       <c r="C7">
-        <v>3690.286546259602</v>
+        <v>3693.912208809187</v>
       </c>
       <c r="D7">
-        <v>3421.721546259602</v>
+        <v>3425.347208809187</v>
       </c>
       <c r="E7">
         <v>-714.765</v>
@@ -1861,37 +1861,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M7">
-        <v>16.1426488075874</v>
+        <v>15.9297998075874</v>
       </c>
       <c r="N7">
-        <v>290.0129067479681</v>
+        <v>290.2257557479682</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>290.0129067479681</v>
+        <v>290.2257557479682</v>
       </c>
       <c r="Q7">
-        <v>471.4129067479681</v>
+        <v>471.6257557479681</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1112640293364517</v>
+        <v>0.1112684032578233</v>
       </c>
       <c r="T7">
         <v>0.5607881832477083</v>
       </c>
       <c r="U7">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.96563316248667</v>
+        <v>19.21904601774926</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1116134591614715</v>
+        <v>0.1115336143867744</v>
       </c>
       <c r="C8">
-        <v>3628.488713990679</v>
+        <v>3632.772478096006</v>
       </c>
       <c r="D8">
-        <v>3390.330713990679</v>
+        <v>3394.614478096006</v>
       </c>
       <c r="E8">
         <v>-684.3579999999999</v>
@@ -1943,37 +1943,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M8">
-        <v>19.37117856910488</v>
+        <v>19.11575976910488</v>
       </c>
       <c r="N8">
-        <v>286.7843769864507</v>
+        <v>287.0397957864507</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>286.7843769864507</v>
+        <v>287.0397957864507</v>
       </c>
       <c r="Q8">
-        <v>468.1843769864507</v>
+        <v>468.4397957864506</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1119604551804566</v>
+        <v>0.1119648756329065</v>
       </c>
       <c r="T8">
         <v>0.5667540149843862</v>
       </c>
       <c r="U8">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.80469430207223</v>
+        <v>16.01587168145772</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1122172310434452</v>
+        <v>0.1121233862687481</v>
       </c>
       <c r="C9">
-        <v>3567.261604155621</v>
+        <v>3572.179320814931</v>
       </c>
       <c r="D9">
-        <v>3359.510604155621</v>
+        <v>3364.428320814931</v>
       </c>
       <c r="E9">
         <v>-653.9509999999999</v>
@@ -2025,37 +2025,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M9">
-        <v>22.59970833062237</v>
+        <v>22.30171973062236</v>
       </c>
       <c r="N9">
-        <v>283.5558472249332</v>
+        <v>283.8538358249332</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>283.5558472249332</v>
+        <v>283.8538358249332</v>
       </c>
       <c r="Q9">
-        <v>464.9558472249332</v>
+        <v>465.2538358249332</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1126718579243324</v>
+        <v>0.1126763259085291</v>
       </c>
       <c r="T9">
         <v>0.5728481441777665</v>
       </c>
       <c r="U9">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>13.54688083034762</v>
+        <v>13.72789001267804</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1129090029254189</v>
+        <v>0.1128331581507218</v>
       </c>
       <c r="C10">
-        <v>3502.224154114064</v>
+        <v>3506.148508855165</v>
       </c>
       <c r="D10">
-        <v>3324.880154114064</v>
+        <v>3328.804508855165</v>
       </c>
       <c r="E10">
         <v>-623.544</v>
@@ -2107,37 +2107,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M10">
-        <v>26.09581969213984</v>
+        <v>25.85256369213984</v>
       </c>
       <c r="N10">
-        <v>280.0597358634157</v>
+        <v>280.3029918634157</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>280.0597358634157</v>
+        <v>280.3029918634157</v>
       </c>
       <c r="Q10">
-        <v>461.4597358634157</v>
+        <v>461.7029918634157</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1133987259452491</v>
+        <v>0.1134032424944914</v>
       </c>
       <c r="T10">
         <v>0.5790747544405684</v>
       </c>
       <c r="U10">
-        <v>0.1072771881973717</v>
+        <v>0.1062771881973717</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.1072771881973717</v>
+        <v>0.1062771881973717</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.73197696670822</v>
+        <v>11.84236732578435</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1135237748073926</v>
+        <v>0.1134379300326956</v>
       </c>
       <c r="C11">
-        <v>3441.635097140793</v>
+        <v>3445.977626865137</v>
       </c>
       <c r="D11">
-        <v>3294.698097140793</v>
+        <v>3299.040626865137</v>
       </c>
       <c r="E11">
         <v>-593.1369999999999</v>
@@ -2189,37 +2189,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M11">
-        <v>29.35779715365732</v>
+        <v>29.08413415365732</v>
       </c>
       <c r="N11">
-        <v>276.7977584018982</v>
+        <v>277.0714214018982</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>276.7977584018982</v>
+        <v>277.0714214018982</v>
       </c>
       <c r="Q11">
-        <v>458.1977584018982</v>
+        <v>458.4714214018983</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1141415690875046</v>
+        <v>0.1141461352691562</v>
       </c>
       <c r="T11">
         <v>0.5854382132805748</v>
       </c>
       <c r="U11">
-        <v>0.1072771881973717</v>
+        <v>0.1062771881973717</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.1072771881973717</v>
+        <v>0.1062771881973717</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.42842397040731</v>
+        <v>10.52654873403053</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1143585466893663</v>
+        <v>0.1142127019146693</v>
       </c>
       <c r="C12">
-        <v>3371.111708099657</v>
+        <v>3378.209086629931</v>
       </c>
       <c r="D12">
-        <v>3254.581708099658</v>
+        <v>3261.679086629932</v>
       </c>
       <c r="E12">
         <v>-562.73</v>
@@ -2271,37 +2271,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M12">
-        <v>33.2887286151748</v>
+        <v>32.8326236151748</v>
       </c>
       <c r="N12">
-        <v>272.8668269403807</v>
+        <v>273.3229319403808</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>272.8668269403807</v>
+        <v>273.3229319403808</v>
       </c>
       <c r="Q12">
-        <v>454.2668269403807</v>
+        <v>454.7229319403808</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1149009198551435</v>
+        <v>0.1149055367721468</v>
       </c>
       <c r="T12">
         <v>0.5919430823170255</v>
       </c>
       <c r="U12">
-        <v>0.1094771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.1094771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.196973519018485</v>
+        <v>9.324736248432323</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1149953185713401</v>
+        <v>0.114834473796643</v>
       </c>
       <c r="C13">
-        <v>3310.754327610157</v>
+        <v>3318.425164745046</v>
       </c>
       <c r="D13">
-        <v>3224.631327610157</v>
+        <v>3232.302164745046</v>
       </c>
       <c r="E13">
         <v>-532.323</v>
@@ -2353,37 +2353,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M13">
-        <v>36.61760147669229</v>
+        <v>36.11588597669228</v>
       </c>
       <c r="N13">
-        <v>269.5379540788633</v>
+        <v>270.0396695788633</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>269.5379540788633</v>
+        <v>270.0396695788633</v>
       </c>
       <c r="Q13">
-        <v>450.9379540788633</v>
+        <v>451.4396695788632</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1156773346849766</v>
+        <v>0.1156820034774518</v>
       </c>
       <c r="T13">
         <v>0.5985941281857562</v>
       </c>
       <c r="U13">
-        <v>0.1094771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0.1094771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.360885017289531</v>
+        <v>8.477032953120293</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1156320904533138</v>
+        <v>0.1154562456786167</v>
       </c>
       <c r="C14">
-        <v>3250.943159042034</v>
+        <v>3259.165696735874</v>
       </c>
       <c r="D14">
-        <v>3195.227159042034</v>
+        <v>3203.449696735875</v>
       </c>
       <c r="E14">
         <v>-501.916</v>
@@ -2435,37 +2435,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M14">
-        <v>39.94647433820976</v>
+        <v>39.39914833820976</v>
       </c>
       <c r="N14">
-        <v>266.2090812173458</v>
+        <v>266.7564072173458</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>266.2090812173458</v>
+        <v>266.7564072173458</v>
       </c>
       <c r="Q14">
-        <v>447.6090812173458</v>
+        <v>448.1564072173458</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1164713953063968</v>
+        <v>0.1164761171533319</v>
       </c>
       <c r="T14">
         <v>0.605396334187867</v>
       </c>
       <c r="U14">
-        <v>0.1094771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.1094771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.664144599182071</v>
+        <v>7.770613540360269</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1164638623352875</v>
+        <v>0.1161820175605904</v>
       </c>
       <c r="C15">
-        <v>3182.925702727041</v>
+        <v>3195.72506405823</v>
       </c>
       <c r="D15">
-        <v>3157.616702727041</v>
+        <v>3170.41606405823</v>
       </c>
       <c r="E15">
         <v>-471.509</v>
@@ -2517,37 +2517,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M15">
-        <v>43.86828369972725</v>
+        <v>42.99864349972724</v>
       </c>
       <c r="N15">
-        <v>262.2872718558283</v>
+        <v>263.1569120558283</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>262.2872718558283</v>
+        <v>263.1569120558283</v>
       </c>
       <c r="Q15">
-        <v>443.6872718558283</v>
+        <v>444.5569120558283</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.117283710194976</v>
+        <v>0.1172884863160139</v>
       </c>
       <c r="T15">
         <v>0.6123549127417505</v>
       </c>
       <c r="U15">
-        <v>0.1109771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.1109771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.978972727794661</v>
+        <v>7.120121255860028</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1171156342172612</v>
+        <v>0.1168117894425641</v>
       </c>
       <c r="C16">
-        <v>3123.660433380122</v>
+        <v>3137.201058319111</v>
       </c>
       <c r="D16">
-        <v>3128.758433380121</v>
+        <v>3142.299058319111</v>
       </c>
       <c r="E16">
         <v>-441.1019999999999</v>
@@ -2599,37 +2599,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M16">
-        <v>47.24276706124473</v>
+        <v>46.30623146124473</v>
       </c>
       <c r="N16">
-        <v>258.9127884943108</v>
+        <v>259.8493240943108</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>258.9127884943108</v>
+        <v>259.8493240943108</v>
       </c>
       <c r="Q16">
-        <v>440.3127884943108</v>
+        <v>441.2493240943109</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1181149161274758</v>
+        <v>0.1181197477848047</v>
       </c>
       <c r="T16">
         <v>0.619475318703864</v>
       </c>
       <c r="U16">
-        <v>0.1109771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.1109771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.480474675809328</v>
+        <v>6.611541166155739</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1179774060992349</v>
+        <v>0.1174415613245378</v>
       </c>
       <c r="C17">
-        <v>3055.897199773332</v>
+        <v>3079.171382946121</v>
       </c>
       <c r="D17">
-        <v>3091.402199773333</v>
+        <v>3114.676382946121</v>
       </c>
       <c r="E17">
         <v>-410.695</v>
@@ -2681,45 +2681,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M17">
-        <v>51.25579742276221</v>
+        <v>49.61381942276221</v>
       </c>
       <c r="N17">
-        <v>254.8997581327934</v>
+        <v>256.5417361327933</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>254.8997581327934</v>
+        <v>256.5417361327933</v>
       </c>
       <c r="Q17">
-        <v>436.2997581327934</v>
+        <v>437.9417361327934</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1189656798466226</v>
+        <v>0.1189705683469789</v>
       </c>
       <c r="T17">
         <v>0.6267632636297917</v>
       </c>
       <c r="U17">
-        <v>0.1123771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.1123771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>5.973091258933273</v>
+        <v>6.17077175507869</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1186431779812086</v>
+        <v>0.1182313332065116</v>
       </c>
       <c r="C18">
-        <v>2997.235410271813</v>
+        <v>3014.802784839332</v>
       </c>
       <c r="D18">
-        <v>3063.147410271813</v>
+        <v>3080.714784839332</v>
       </c>
       <c r="E18">
         <v>-380.288</v>
@@ -2763,37 +2763,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M18">
-        <v>54.67285058427969</v>
+        <v>53.40791938427969</v>
       </c>
       <c r="N18">
-        <v>251.4827049712759</v>
+        <v>252.7476361712759</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>251.4827049712759</v>
+        <v>252.7476361712759</v>
       </c>
       <c r="Q18">
-        <v>432.8827049712759</v>
+        <v>434.1476361712758</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1198366998447966</v>
+        <v>0.1198416465415858</v>
       </c>
       <c r="T18">
         <v>0.6342247310539559</v>
       </c>
       <c r="U18">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.599773055249943</v>
+        <v>5.732399971485703</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1193089498631824</v>
+        <v>0.1188711050884853</v>
       </c>
       <c r="C19">
-        <v>2939.085429044421</v>
+        <v>2957.422678392753</v>
       </c>
       <c r="D19">
-        <v>3035.404429044421</v>
+        <v>3053.741678392753</v>
       </c>
       <c r="E19">
         <v>-349.881</v>
@@ -2845,37 +2845,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M19">
-        <v>58.08990374579717</v>
+        <v>56.74591434579717</v>
       </c>
       <c r="N19">
-        <v>248.0656518097584</v>
+        <v>249.4096412097584</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>248.0656518097584</v>
+        <v>249.4096412097584</v>
       </c>
       <c r="Q19">
-        <v>429.4656518097584</v>
+        <v>430.8096412097584</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1207287082766617</v>
+        <v>0.1207337145722073</v>
       </c>
       <c r="T19">
         <v>0.6418659928738831</v>
       </c>
       <c r="U19">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.270374640235241</v>
+        <v>5.395199973163014</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1199747217451561</v>
+        <v>0.119510876970459</v>
       </c>
       <c r="C20">
-        <v>2881.433474540655</v>
+        <v>2900.510796875336</v>
       </c>
       <c r="D20">
-        <v>3008.159474540655</v>
+        <v>3027.236796875336</v>
       </c>
       <c r="E20">
         <v>-319.474</v>
@@ -2927,37 +2927,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M20">
-        <v>61.50695690731465</v>
+        <v>60.08390930731463</v>
       </c>
       <c r="N20">
-        <v>244.6485986482409</v>
+        <v>246.0716462482409</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>244.6485986482409</v>
+        <v>246.0716462482409</v>
       </c>
       <c r="Q20">
-        <v>426.048598648241</v>
+        <v>427.471646248241</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1216424730117429</v>
+        <v>0.1216475403596733</v>
       </c>
       <c r="T20">
         <v>0.6496936269333207</v>
       </c>
       <c r="U20">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.977576049111062</v>
+        <v>5.095466641320625</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1206404936271298</v>
+        <v>0.1201506488524327</v>
       </c>
       <c r="C21">
-        <v>2824.266255605969</v>
+        <v>2844.055053352452</v>
       </c>
       <c r="D21">
-        <v>2981.399255605969</v>
+        <v>3001.188053352452</v>
       </c>
       <c r="E21">
         <v>-289.067</v>
@@ -3009,37 +3009,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M21">
-        <v>64.92401006883213</v>
+        <v>63.42190426883212</v>
       </c>
       <c r="N21">
-        <v>241.2315454867234</v>
+        <v>242.7336512867234</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>241.2315454867234</v>
+        <v>242.7336512867234</v>
       </c>
       <c r="Q21">
-        <v>422.6315454867234</v>
+        <v>424.1336512867234</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1225787998390483</v>
+        <v>0.1225839297468297</v>
       </c>
       <c r="T21">
         <v>0.657714535907806</v>
       </c>
       <c r="U21">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.715598362315742</v>
+        <v>4.827284186514277</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1218262655091035</v>
+        <v>0.1207904207344064</v>
       </c>
       <c r="C22">
-        <v>2747.358754988697</v>
+        <v>2788.043773362469</v>
       </c>
       <c r="D22">
-        <v>2934.898754988697</v>
+        <v>2975.583773362468</v>
       </c>
       <c r="E22">
         <v>-258.66</v>
@@ -3091,45 +3091,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M22">
-        <v>69.92222723034962</v>
+        <v>66.7598992303496</v>
       </c>
       <c r="N22">
-        <v>236.2333283252059</v>
+        <v>239.3956563252059</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>236.2333283252059</v>
+        <v>239.3956563252059</v>
       </c>
       <c r="Q22">
-        <v>417.633328325206</v>
+        <v>420.795656325206</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1235385348370364</v>
+        <v>0.1235437288686651</v>
       </c>
       <c r="T22">
         <v>0.6659359676066536</v>
       </c>
       <c r="U22">
-        <v>0.1149771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.1149771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.378515497610884</v>
+        <v>4.585919977188562</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1225180373910772</v>
+        <v>0.1219551926163801</v>
       </c>
       <c r="C23">
-        <v>2690.487568674971</v>
+        <v>2712.126070906123</v>
       </c>
       <c r="D23">
-        <v>2908.434568674971</v>
+        <v>2930.073070906123</v>
       </c>
       <c r="E23">
         <v>-228.253</v>
@@ -3173,37 +3173,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M23">
-        <v>73.41833859186708</v>
+        <v>71.69426169186708</v>
       </c>
       <c r="N23">
-        <v>232.7372169636885</v>
+        <v>234.4612938636885</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>232.7372169636885</v>
+        <v>234.4612938636885</v>
       </c>
       <c r="Q23">
-        <v>414.1372169636885</v>
+        <v>415.8612938636885</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1245225669235812</v>
+        <v>0.1245278267024457</v>
       </c>
       <c r="T23">
         <v>0.6743655368168645</v>
       </c>
       <c r="U23">
-        <v>0.1149771881973717</v>
+        <v>0.1122771881973717</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.1149771881973717</v>
+        <v>0.1122771881973717</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.170014759629414</v>
+        <v>4.270293721293534</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1238038092730509</v>
+        <v>0.1226199644983538</v>
       </c>
       <c r="C24">
-        <v>2612.13953318179</v>
+        <v>2656.363289991794</v>
       </c>
       <c r="D24">
-        <v>2860.493533181791</v>
+        <v>2904.717289991794</v>
       </c>
       <c r="E24">
         <v>-197.846</v>
@@ -3255,45 +3255,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M24">
-        <v>78.72062575338458</v>
+        <v>75.10827415338457</v>
       </c>
       <c r="N24">
-        <v>227.434929802171</v>
+        <v>231.047281402171</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>227.434929802171</v>
+        <v>231.047281402171</v>
       </c>
       <c r="Q24">
-        <v>408.834929802171</v>
+        <v>412.447281402171</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1255318306020887</v>
+        <v>0.1255371578140155</v>
       </c>
       <c r="T24">
         <v>0.6830112488273371</v>
       </c>
       <c r="U24">
-        <v>0.1176771881973717</v>
+        <v>0.1122771881973717</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.1176771881973717</v>
+        <v>0.1122771881973717</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.889140268202104</v>
+        <v>4.076189461234737</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1245225811550247</v>
+        <v>0.1240897363803276</v>
       </c>
       <c r="C25">
-        <v>2555.614965769083</v>
+        <v>2571.424597904175</v>
       </c>
       <c r="D25">
-        <v>2834.375965769083</v>
+        <v>2850.185597904175</v>
       </c>
       <c r="E25">
         <v>-167.439</v>
@@ -3337,37 +3337,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M25">
-        <v>82.29883601490207</v>
+        <v>80.97005011490205</v>
       </c>
       <c r="N25">
-        <v>223.8567195406535</v>
+        <v>225.1855054406535</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>223.8567195406535</v>
+        <v>225.1855054406535</v>
       </c>
       <c r="Q25">
-        <v>405.2567195406535</v>
+        <v>406.5855054406535</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1265673089215963</v>
+        <v>0.1265727053180936</v>
       </c>
       <c r="T25">
         <v>0.6918815247861337</v>
       </c>
       <c r="U25">
-        <v>0.1176771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.1176771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.720047213062882</v>
+        <v>3.781096283392438</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1252413530369984</v>
+        <v>0.1247895082623013</v>
       </c>
       <c r="C26">
-        <v>2499.563012992559</v>
+        <v>2515.767665556239</v>
       </c>
       <c r="D26">
-        <v>2808.731012992559</v>
+        <v>2824.935665556239</v>
       </c>
       <c r="E26">
         <v>-137.032</v>
@@ -3419,37 +3419,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M26">
-        <v>85.87704627641953</v>
+        <v>84.49048707641953</v>
       </c>
       <c r="N26">
-        <v>220.278509279136</v>
+        <v>221.665068479136</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>220.278509279136</v>
+        <v>221.665068479136</v>
       </c>
       <c r="Q26">
-        <v>401.6785092791361</v>
+        <v>403.065068479136</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1276300366705647</v>
+        <v>0.1276355040722791</v>
       </c>
       <c r="T26">
         <v>0.7009852290596356</v>
       </c>
       <c r="U26">
-        <v>0.1176771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.1176771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.565045245851929</v>
+        <v>3.623550604917753</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1271351249189721</v>
+        <v>0.126189280144275</v>
       </c>
       <c r="C27">
-        <v>2403.758734489184</v>
+        <v>2436.171700237313</v>
       </c>
       <c r="D27">
-        <v>2743.333734489184</v>
+        <v>2775.746700237312</v>
       </c>
       <c r="E27">
         <v>-106.625</v>
@@ -3501,37 +3501,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M27">
-        <v>93.028079037937</v>
+        <v>90.139414037937</v>
       </c>
       <c r="N27">
-        <v>213.1274765176186</v>
+        <v>216.0161415176186</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>213.1274765176186</v>
+        <v>216.0161415176186</v>
       </c>
       <c r="Q27">
-        <v>394.5274765176185</v>
+        <v>397.4161415176186</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1287211038261722</v>
+        <v>0.1287266441265761</v>
       </c>
       <c r="T27">
         <v>0.7103316987804306</v>
       </c>
       <c r="U27">
-        <v>0.1223771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.1223771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.29100158491615</v>
+        <v>3.396467115114636</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1279008968009458</v>
+        <v>0.1269170520262487</v>
       </c>
       <c r="C28">
-        <v>2347.764098804338</v>
+        <v>2380.8610536001</v>
       </c>
       <c r="D28">
-        <v>2717.746098804338</v>
+        <v>2750.8430536001</v>
       </c>
       <c r="E28">
         <v>-76.21799999999996</v>
@@ -3583,37 +3583,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M28">
-        <v>96.74920219945449</v>
+        <v>93.7449905994545</v>
       </c>
       <c r="N28">
-        <v>209.4063533561011</v>
+        <v>212.4105649561011</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>209.4063533561011</v>
+        <v>212.4105649561011</v>
       </c>
       <c r="Q28">
-        <v>390.8063533561011</v>
+        <v>393.8105649561011</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1298416592832827</v>
+        <v>0.1298472744526109</v>
       </c>
       <c r="T28">
         <v>0.719930775790977</v>
       </c>
       <c r="U28">
-        <v>0.1223771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.1223771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.164424600880913</v>
+        <v>3.265833764533303</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1286666686829195</v>
+        <v>0.1276448239082225</v>
       </c>
       <c r="C29">
-        <v>2292.242374417726</v>
+        <v>2325.993298105313</v>
       </c>
       <c r="D29">
-        <v>2692.631374417726</v>
+        <v>2726.382298105313</v>
       </c>
       <c r="E29">
         <v>-45.81099999999992</v>
@@ -3665,37 +3665,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M29">
-        <v>100.470325360972</v>
+        <v>97.35056716097198</v>
       </c>
       <c r="N29">
-        <v>205.6852301945836</v>
+        <v>208.8049883945836</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>205.6852301945836</v>
+        <v>208.8049883945836</v>
       </c>
       <c r="Q29">
-        <v>387.0852301945836</v>
+        <v>390.2049883945836</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.130992914889903</v>
+        <v>0.130998606979359</v>
       </c>
       <c r="T29">
         <v>0.7297928412127712</v>
       </c>
       <c r="U29">
-        <v>0.1223771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.1223771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.047223689737176</v>
+        <v>3.144876958439477</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1320364405648932</v>
+        <v>0.1283725957901962</v>
       </c>
       <c r="C30">
-        <v>2156.618212918521</v>
+        <v>2271.556723195092</v>
       </c>
       <c r="D30">
-        <v>2587.414212918521</v>
+        <v>2702.352723195092</v>
       </c>
       <c r="E30">
         <v>-15.40399999999988</v>
@@ -3747,45 +3747,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M30">
-        <v>112.1094313224895</v>
+        <v>100.9561437224895</v>
       </c>
       <c r="N30">
-        <v>194.0461242330661</v>
+        <v>205.1994118330661</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>194.0461242330661</v>
+        <v>205.1994118330661</v>
       </c>
       <c r="Q30">
-        <v>375.4461242330661</v>
+        <v>386.5994118330661</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1321761498189294</v>
+        <v>0.1321819209651834</v>
       </c>
       <c r="T30">
         <v>0.7399288528962819</v>
       </c>
       <c r="U30">
-        <v>0.1316771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.1316771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.730863513836591</v>
+        <v>3.032559924209496</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1328952124468669</v>
+        <v>0.1313623676721699</v>
       </c>
       <c r="C31">
-        <v>2100.698919984749</v>
+        <v>2146.72248366451</v>
       </c>
       <c r="D31">
-        <v>2561.901919984749</v>
+        <v>2607.92548366451</v>
       </c>
       <c r="E31">
         <v>15.00299999999993</v>
@@ -3829,37 +3829,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M31">
-        <v>116.1133395840069</v>
+        <v>111.4397836840069</v>
       </c>
       <c r="N31">
-        <v>190.0422159715486</v>
+        <v>194.7157718715486</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>190.0422159715486</v>
+        <v>194.7157718715486</v>
       </c>
       <c r="Q31">
-        <v>371.4422159715486</v>
+        <v>376.1157718715486</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1333927153093369</v>
+        <v>0.1333985677393409</v>
       </c>
       <c r="T31">
         <v>0.7503503860356661</v>
       </c>
       <c r="U31">
-        <v>0.1316771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.1316771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.636695806462916</v>
+        <v>2.747273419191794</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1337539843288407</v>
+        <v>0.1321681395541436</v>
       </c>
       <c r="C32">
-        <v>2045.277824829812</v>
+        <v>2091.984833081232</v>
       </c>
       <c r="D32">
-        <v>2536.887824829812</v>
+        <v>2583.594833081233</v>
       </c>
       <c r="E32">
         <v>45.40999999999997</v>
@@ -3911,37 +3911,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M32">
-        <v>120.1172478455244</v>
+        <v>115.2825348455244</v>
       </c>
       <c r="N32">
-        <v>186.0383077100312</v>
+        <v>190.8730207100311</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>186.0383077100312</v>
+        <v>190.8730207100311</v>
       </c>
       <c r="Q32">
-        <v>367.4383077100312</v>
+        <v>372.2730207100311</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1346440398137559</v>
+        <v>0.134649975849903</v>
       </c>
       <c r="T32">
         <v>0.7610696772647471</v>
       </c>
       <c r="U32">
-        <v>0.1316771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.1316771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.548805946247485</v>
+        <v>2.655697638552067</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1360697562108144</v>
+        <v>0.1329739114361173</v>
       </c>
       <c r="C33">
-        <v>1949.789741872833</v>
+        <v>2037.696971977105</v>
       </c>
       <c r="D33">
-        <v>2471.806741872833</v>
+        <v>2559.713971977105</v>
       </c>
       <c r="E33">
         <v>75.81700000000001</v>
@@ -3993,45 +3993,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M33">
-        <v>128.5514560070419</v>
+        <v>119.1252860070419</v>
       </c>
       <c r="N33">
-        <v>177.6040995485137</v>
+        <v>187.0302695485137</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>177.6040995485137</v>
+        <v>187.0302695485137</v>
       </c>
       <c r="Q33">
-        <v>359.0040995485136</v>
+        <v>368.4302695485137</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1359316345936654</v>
+        <v>0.1359376566593219</v>
       </c>
       <c r="T33">
         <v>0.7720996725874245</v>
       </c>
       <c r="U33">
-        <v>0.1363771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.1363771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.381579836316943</v>
+        <v>2.570029972792323</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1369755280927881</v>
+        <v>0.135027683318091</v>
       </c>
       <c r="C34">
-        <v>1894.826886905007</v>
+        <v>1948.372510646177</v>
       </c>
       <c r="D34">
-        <v>2447.250886905007</v>
+        <v>2500.796510646177</v>
       </c>
       <c r="E34">
         <v>106.224</v>
@@ -4075,37 +4075,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M34">
-        <v>132.6982771685594</v>
+        <v>126.7628307685594</v>
       </c>
       <c r="N34">
-        <v>173.4572783869962</v>
+        <v>179.3927247869962</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>173.4572783869962</v>
+        <v>179.3927247869962</v>
       </c>
       <c r="Q34">
-        <v>354.8572783869962</v>
+        <v>360.7927247869961</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1372570998082782</v>
+        <v>0.1372632104337237</v>
       </c>
       <c r="T34">
         <v>0.7834540795372397</v>
       </c>
       <c r="U34">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.307155466432039</v>
+        <v>2.415183959677638</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1378812999747618</v>
+        <v>0.1358724552000647</v>
       </c>
       <c r="C35">
-        <v>1840.3471268321</v>
+        <v>1894.51103091606</v>
       </c>
       <c r="D35">
-        <v>2423.1781268321</v>
+        <v>2477.34203091606</v>
       </c>
       <c r="E35">
         <v>136.6310000000001</v>
@@ -4157,37 +4157,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M35">
-        <v>136.8450983300769</v>
+        <v>130.7241692300769</v>
       </c>
       <c r="N35">
-        <v>169.3104572254787</v>
+        <v>175.4313863254787</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>169.3104572254787</v>
+        <v>175.4313863254787</v>
       </c>
       <c r="Q35">
-        <v>350.7104572254787</v>
+        <v>356.8313863254787</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1386221311487003</v>
+        <v>0.1386283329775106</v>
       </c>
       <c r="T35">
         <v>0.7951474240079448</v>
       </c>
       <c r="U35">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.237241664418947</v>
+        <v>2.341996566960133</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1387870718567356</v>
+        <v>0.1367172270820385</v>
       </c>
       <c r="C36">
-        <v>1786.336344408669</v>
+        <v>1841.085413246813</v>
       </c>
       <c r="D36">
-        <v>2399.574344408669</v>
+        <v>2454.323413246813</v>
       </c>
       <c r="E36">
         <v>167.038</v>
@@ -4239,37 +4239,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M36">
-        <v>140.9919194915943</v>
+        <v>134.6855076915944</v>
       </c>
       <c r="N36">
-        <v>165.1636360639612</v>
+        <v>171.4700478639612</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>165.1636360639612</v>
+        <v>171.4700478639612</v>
       </c>
       <c r="Q36">
-        <v>346.5636360639612</v>
+        <v>352.8700478639612</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1400285270751957</v>
+        <v>0.1400348228711092</v>
       </c>
       <c r="T36">
         <v>0.8071951122504893</v>
       </c>
       <c r="U36">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.17144043899486</v>
+        <v>2.273114314990718</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1396928437387092</v>
+        <v>0.1375619989640122</v>
       </c>
       <c r="C37">
-        <v>1732.780967138094</v>
+        <v>1788.083619844439</v>
       </c>
       <c r="D37">
-        <v>2376.425967138094</v>
+        <v>2431.728619844439</v>
       </c>
       <c r="E37">
         <v>197.4450000000002</v>
@@ -4321,37 +4321,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M37">
-        <v>145.1387406531119</v>
+        <v>138.6468461531119</v>
       </c>
       <c r="N37">
-        <v>161.0168149024437</v>
+        <v>167.5087094024437</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>161.0168149024437</v>
+        <v>167.5087094024437</v>
       </c>
       <c r="Q37">
-        <v>342.4168149024437</v>
+        <v>348.9087094024437</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1414781967225064</v>
+        <v>0.1414845893768186</v>
       </c>
       <c r="T37">
         <v>0.8196134985928046</v>
       </c>
       <c r="U37">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.109399283595006</v>
+        <v>2.208168191705268</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.140598615620683</v>
+        <v>0.1384067708459859</v>
       </c>
       <c r="C38">
-        <v>1679.667941248025</v>
+        <v>1735.494052156686</v>
       </c>
       <c r="D38">
-        <v>2353.719941248024</v>
+        <v>2409.546052156686</v>
       </c>
       <c r="E38">
         <v>227.8519999999999</v>
@@ -4403,37 +4403,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M38">
-        <v>149.2855618146293</v>
+        <v>142.6081846146293</v>
       </c>
       <c r="N38">
-        <v>156.8699937409263</v>
+        <v>163.5473709409263</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>156.8699937409263</v>
+        <v>163.5473709409263</v>
       </c>
       <c r="Q38">
-        <v>338.2699937409263</v>
+        <v>344.9473709409262</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1429731685462956</v>
+        <v>0.1429796610858314</v>
       </c>
       <c r="T38">
         <v>0.8324199595083172</v>
       </c>
       <c r="U38">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.050804859050701</v>
+        <v>2.146830186380122</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1475353875026567</v>
+        <v>0.1392515427279596</v>
       </c>
       <c r="C39">
-        <v>1488.773831430275</v>
+        <v>1683.305531020024</v>
       </c>
       <c r="D39">
-        <v>2193.232831430275</v>
+        <v>2387.764531020024</v>
       </c>
       <c r="E39">
         <v>258.259</v>
@@ -4485,45 +4485,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M39">
-        <v>171.7708446761468</v>
+        <v>146.5695230761468</v>
       </c>
       <c r="N39">
-        <v>134.3847108794088</v>
+        <v>159.5860324794088</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>134.3847108794088</v>
+        <v>159.5860324794088</v>
       </c>
       <c r="Q39">
-        <v>315.7847108794087</v>
+        <v>340.9860324794088</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1445155997930622</v>
+        <v>0.1445221953887811</v>
       </c>
       <c r="T39">
         <v>0.8456329747386079</v>
       </c>
       <c r="U39">
-        <v>0.1526771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V39">
         <v>0</v>
       </c>
       <c r="W39">
-        <v>0.1526771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.782348780625577</v>
+        <v>2.08880774891039</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1486041593846304</v>
+        <v>0.1400963146099333</v>
       </c>
       <c r="C40">
-        <v>1435.565559624879</v>
+        <v>1631.50727787377</v>
       </c>
       <c r="D40">
-        <v>2170.431559624879</v>
+        <v>2366.37327787377</v>
       </c>
       <c r="E40">
         <v>288.6659999999999</v>
@@ -4567,45 +4567,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M40">
-        <v>176.4132999376643</v>
+        <v>150.5308615376643</v>
       </c>
       <c r="N40">
-        <v>129.7422556178913</v>
+        <v>155.6246940178913</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>129.7422556178913</v>
+        <v>155.6246940178913</v>
       </c>
       <c r="Q40">
-        <v>311.1422556178913</v>
+        <v>337.0246940178913</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1461077868864986</v>
+        <v>0.1461144888627937</v>
       </c>
       <c r="T40">
         <v>0.8592722162666498</v>
       </c>
       <c r="U40">
-        <v>0.1526771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.1526771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.735444865345956</v>
+        <v>2.033839123939064</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1496729312666041</v>
+        <v>0.146479086491907</v>
       </c>
       <c r="C41">
-        <v>1382.826502616479</v>
+        <v>1451.078844957007</v>
       </c>
       <c r="D41">
-        <v>2148.099502616479</v>
+        <v>2216.351844957007</v>
       </c>
       <c r="E41">
         <v>319.0730000000001</v>
@@ -4649,37 +4649,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M41">
-        <v>181.0557551991818</v>
+        <v>171.3315965991818</v>
       </c>
       <c r="N41">
-        <v>125.0998003563738</v>
+        <v>134.8239589563738</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>125.0998003563738</v>
+        <v>134.8239589563738</v>
       </c>
       <c r="Q41">
-        <v>306.4998003563738</v>
+        <v>316.2239589563738</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1477521768354577</v>
+        <v>0.1477589886802165</v>
       </c>
       <c r="T41">
         <v>0.873358646041513</v>
       </c>
       <c r="U41">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.690946279055034</v>
+        <v>1.786918242942573</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1507417031485778</v>
+        <v>0.1474658583738808</v>
       </c>
       <c r="C42">
-        <v>1330.542324343245</v>
+        <v>1399.159867227755</v>
       </c>
       <c r="D42">
-        <v>2126.222324343245</v>
+        <v>2194.839867227755</v>
       </c>
       <c r="E42">
         <v>349.48</v>
@@ -4731,37 +4731,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M42">
-        <v>185.6982104606992</v>
+        <v>175.7247144606992</v>
       </c>
       <c r="N42">
-        <v>120.4573450948563</v>
+        <v>130.4308410948563</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>120.4573450948563</v>
+        <v>130.4308410948563</v>
       </c>
       <c r="Q42">
-        <v>301.8573450948563</v>
+        <v>311.8308410948563</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1494513797827153</v>
+        <v>0.1494583051582201</v>
       </c>
       <c r="T42">
         <v>0.8879146234755383</v>
       </c>
       <c r="U42">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.648672622078658</v>
+        <v>1.742245286869009</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1518104750305516</v>
+        <v>0.1484526302558545</v>
       </c>
       <c r="C43">
-        <v>1278.699266874132</v>
+        <v>1347.654467108663</v>
       </c>
       <c r="D43">
-        <v>2104.786266874132</v>
+        <v>2173.741467108663</v>
       </c>
       <c r="E43">
         <v>379.8870000000002</v>
@@ -4813,37 +4813,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M43">
-        <v>190.3406657222168</v>
+        <v>180.1178323222167</v>
       </c>
       <c r="N43">
-        <v>115.8148898333388</v>
+        <v>126.0377232333389</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>115.8148898333388</v>
+        <v>126.0377232333389</v>
       </c>
       <c r="Q43">
-        <v>297.2148898333388</v>
+        <v>307.4377232333388</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1512081828298799</v>
+        <v>0.1512152255846306</v>
       </c>
       <c r="T43">
         <v>0.9029640238734287</v>
       </c>
       <c r="U43">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.608461094710886</v>
+        <v>1.699751499384399</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1528792469125253</v>
+        <v>0.1494394021378282</v>
       </c>
       <c r="C44">
-        <v>1227.284121556887</v>
+        <v>1296.550831329439</v>
       </c>
       <c r="D44">
-        <v>2083.778121556887</v>
+        <v>2153.044831329439</v>
       </c>
       <c r="E44">
         <v>410.2939999999999</v>
@@ -4895,37 +4895,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M44">
-        <v>194.9831209837342</v>
+        <v>184.5109501837342</v>
       </c>
       <c r="N44">
-        <v>111.1724345718214</v>
+        <v>121.6446053718214</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>111.1724345718214</v>
+        <v>121.6446053718214</v>
       </c>
       <c r="Q44">
-        <v>292.5724345718214</v>
+        <v>303.0446053718214</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1530255652924641</v>
+        <v>0.1530327294740208</v>
       </c>
       <c r="T44">
         <v>0.9185323691126257</v>
       </c>
       <c r="U44">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.570164401979675</v>
+        <v>1.659281225589532</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.153948018794499</v>
+        <v>0.1504261740198019</v>
       </c>
       <c r="C45">
-        <v>1176.284201876834</v>
+        <v>1245.837592282768</v>
       </c>
       <c r="D45">
-        <v>2063.185201876834</v>
+        <v>2132.738592282768</v>
       </c>
       <c r="E45">
         <v>440.701</v>
@@ -4977,37 +4977,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M45">
-        <v>199.6255762452517</v>
+        <v>188.9040680452517</v>
       </c>
       <c r="N45">
-        <v>106.5299793103039</v>
+        <v>117.2514875103039</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>106.5299793103039</v>
+        <v>117.2514875103039</v>
       </c>
       <c r="Q45">
-        <v>287.9299793103039</v>
+        <v>298.6514875103039</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1549067155607529</v>
+        <v>0.1549140054297054</v>
       </c>
       <c r="T45">
         <v>0.9346469720795139</v>
       </c>
       <c r="U45">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.533648950770845</v>
+        <v>1.620693290110706</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1837927906764727</v>
+        <v>0.1514129459017756</v>
       </c>
       <c r="C46">
-        <v>699.6561246856154</v>
+        <v>1195.503807204524</v>
       </c>
       <c r="D46">
-        <v>1616.964124685615</v>
+        <v>2112.811807204524</v>
       </c>
       <c r="E46">
         <v>471.1079999999999</v>
@@ -5059,45 +5059,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M46">
-        <v>291.7672147067692</v>
+        <v>193.2971859067691</v>
       </c>
       <c r="N46">
-        <v>14.38834084878641</v>
+        <v>112.8583696487864</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>14.38834084878641</v>
+        <v>112.8583696487864</v>
       </c>
       <c r="Q46">
-        <v>195.7883408487864</v>
+        <v>294.2583696487865</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1568550497671949</v>
+        <v>0.1568624698123787</v>
       </c>
       <c r="T46">
         <v>0.9513370965809338</v>
       </c>
       <c r="U46">
-        <v>0.2180771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46">
-        <v>0.2180771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.049314453864348</v>
+        <v>1.583859351699099</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1855155625584464</v>
+        <v>0.1523997177837493</v>
       </c>
       <c r="C47">
-        <v>649.311042791529</v>
+        <v>1145.538938510342</v>
       </c>
       <c r="D47">
-        <v>1597.026042791529</v>
+        <v>2093.253938510342</v>
       </c>
       <c r="E47">
         <v>501.5150000000001</v>
@@ -5141,45 +5141,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M47">
-        <v>298.3982877682867</v>
+        <v>197.6903037682866</v>
       </c>
       <c r="N47">
-        <v>7.757267787268916</v>
+        <v>108.4652517872689</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>7.757267787268916</v>
+        <v>108.4652517872689</v>
       </c>
       <c r="Q47">
-        <v>189.1572677872689</v>
+        <v>289.8652517872689</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1588742324902349</v>
+        <v>0.158881787445331</v>
       </c>
       <c r="T47">
         <v>0.9686341347005871</v>
       </c>
       <c r="U47">
-        <v>0.2180771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.2180771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.025996354889585</v>
+        <v>1.548662477216896</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1872383344404202</v>
+        <v>0.153386489665723</v>
       </c>
       <c r="C48">
-        <v>599.4516675059592</v>
+        <v>1095.932835214281</v>
       </c>
       <c r="D48">
-        <v>1577.573667505959</v>
+        <v>2074.054835214281</v>
       </c>
       <c r="E48">
         <v>531.922</v>
@@ -5223,45 +5223,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M48">
-        <v>305.0293608298041</v>
+        <v>202.0834216298041</v>
       </c>
       <c r="N48">
-        <v>1.126194725751475</v>
+        <v>104.0721339257514</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>1.126194725751475</v>
+        <v>104.0721339257514</v>
       </c>
       <c r="Q48">
-        <v>182.5261947257515</v>
+        <v>285.4721339257515</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1609681997585725</v>
+        <v>0.1609758946202446</v>
       </c>
       <c r="T48">
         <v>0.9865718038617092</v>
       </c>
       <c r="U48">
-        <v>0.2180771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0.2180771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.003692086305029</v>
+        <v>1.514995901625225</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1889611063223939</v>
+        <v>0.1810692615476968</v>
       </c>
       <c r="C49">
-        <v>550.060464142784</v>
+        <v>641.0717780470031</v>
       </c>
       <c r="D49">
-        <v>1558.589464142784</v>
+        <v>1649.600778047003</v>
       </c>
       <c r="E49">
         <v>562.329</v>
@@ -5305,37 +5305,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M49">
-        <v>311.6604338913216</v>
+        <v>287.6510666913216</v>
       </c>
       <c r="N49">
-        <v>-5.504878335766023</v>
+        <v>18.50448886423396</v>
       </c>
       <c r="O49">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>-5.504878335766023</v>
+        <v>18.50448886423396</v>
       </c>
       <c r="Q49">
-        <v>175.895121664234</v>
+        <v>199.904488864234</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1631411846596777</v>
+        <v>0.163149024707419</v>
       </c>
       <c r="T49">
         <v>1.005186366198723</v>
       </c>
       <c r="U49">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9823369355325815</v>
+        <v>1.064329637560813</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1906838782043676</v>
+        <v>0.1826240334296705</v>
       </c>
       <c r="C50">
-        <v>501.1207320152105</v>
+        <v>591.9198774480326</v>
       </c>
       <c r="D50">
-        <v>1540.05673201521</v>
+        <v>1630.855877448033</v>
       </c>
       <c r="E50">
         <v>592.7359999999999</v>
@@ -5387,37 +5387,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M50">
-        <v>318.291506952839</v>
+        <v>293.771302152839</v>
       </c>
       <c r="N50">
-        <v>-12.13595139728346</v>
+        <v>12.38425340271652</v>
       </c>
       <c r="O50">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>-12.13595139728346</v>
+        <v>12.38425340271652</v>
       </c>
       <c r="Q50">
-        <v>169.2640486027165</v>
+        <v>193.7842534027165</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.165397745903133</v>
+        <v>0.1654057367210232</v>
       </c>
       <c r="T50">
         <v>1.024516873241005</v>
       </c>
       <c r="U50">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9618715827089862</v>
+        <v>1.042156103444963</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1924066500863413</v>
+        <v>0.1841788053116442</v>
       </c>
       <c r="C51">
-        <v>452.6165554342185</v>
+        <v>543.1891980659386</v>
       </c>
       <c r="D51">
-        <v>1521.959555434218</v>
+        <v>1612.532198065938</v>
       </c>
       <c r="E51">
         <v>623.143</v>
@@ -5469,37 +5469,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M51">
-        <v>324.9225800143565</v>
+        <v>299.8915376143566</v>
       </c>
       <c r="N51">
-        <v>-18.76702445880096</v>
+        <v>6.264017941198972</v>
       </c>
       <c r="O51">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>-18.76702445880096</v>
+        <v>6.264017941198972</v>
       </c>
       <c r="Q51">
-        <v>162.632975541199</v>
+        <v>187.664017941199</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1677427997443709</v>
+        <v>0.1677509472449649</v>
       </c>
       <c r="T51">
         <v>1.044605439382986</v>
       </c>
       <c r="U51">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
       <c r="W51">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9422415504088028</v>
+        <v>1.020887611537923</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.194129421968315</v>
+        <v>0.1857335771936179</v>
       </c>
       <c r="C52">
-        <v>404.5327581217916</v>
+        <v>494.8656996056638</v>
       </c>
       <c r="D52">
-        <v>1504.282758121792</v>
+        <v>1594.615699605664</v>
       </c>
       <c r="E52">
         <v>653.55</v>
@@ -5551,37 +5551,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M52">
-        <v>331.553653075874</v>
+        <v>306.011773075874</v>
       </c>
       <c r="N52">
-        <v>-25.39809752031846</v>
+        <v>0.1437824796815335</v>
       </c>
       <c r="O52">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>-25.39809752031846</v>
+        <v>0.1437824796815335</v>
       </c>
       <c r="Q52">
-        <v>156.0019024796815</v>
+        <v>181.5437824796815</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1701816557392583</v>
+        <v>0.1701899661898642</v>
       </c>
       <c r="T52">
         <v>1.065497548170646</v>
       </c>
       <c r="U52">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V52">
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9233967194006266</v>
+        <v>1.000469859307164</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1958521938502887</v>
+        <v>0.1872883490755916</v>
       </c>
       <c r="C53">
-        <v>356.8548607644645</v>
+        <v>446.9359589100598</v>
       </c>
       <c r="D53">
-        <v>1487.011860764464</v>
+        <v>1577.092958910059</v>
       </c>
       <c r="E53">
         <v>683.9569999999999</v>
@@ -5633,37 +5633,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M53">
-        <v>338.1847261373915</v>
+        <v>312.1320085373915</v>
       </c>
       <c r="N53">
-        <v>-32.0291705818359</v>
+        <v>-5.976452981835962</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-32.0291705818359</v>
+        <v>-5.976452981835962</v>
       </c>
       <c r="Q53">
-        <v>149.3708294181641</v>
+        <v>175.423547018164</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1727200568767942</v>
+        <v>0.1727285369284328</v>
       </c>
       <c r="T53">
         <v>1.087242396092496</v>
       </c>
       <c r="U53">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V53">
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9052909013731635</v>
+        <v>0.9808528032423178</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1975749657322625</v>
+        <v>0.1888431209575654</v>
       </c>
       <c r="C54">
-        <v>309.5690414576923</v>
+        <v>399.387136420745</v>
       </c>
       <c r="D54">
-        <v>1470.133041457692</v>
+        <v>1559.951136420745</v>
       </c>
       <c r="E54">
         <v>714.364</v>
@@ -5715,37 +5715,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M54">
-        <v>344.815799198909</v>
+        <v>318.252243998909</v>
       </c>
       <c r="N54">
-        <v>-38.66024364335345</v>
+        <v>-12.09668844335346</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-38.66024364335345</v>
+        <v>-12.09668844335346</v>
       </c>
       <c r="Q54">
-        <v>142.7397563566466</v>
+        <v>169.3033115566465</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1753642247283941</v>
+        <v>0.1753728814477752</v>
       </c>
       <c r="T54">
         <v>1.109893279344423</v>
       </c>
       <c r="U54">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8878814609621409</v>
+        <v>0.9619902493338117</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1992977376142362</v>
+        <v>0.1903978928395391</v>
       </c>
       <c r="C55">
-        <v>262.6620988139193</v>
+        <v>352.2069448027223</v>
       </c>
       <c r="D55">
-        <v>1453.633098813919</v>
+        <v>1543.177944802722</v>
       </c>
       <c r="E55">
         <v>744.771</v>
@@ -5797,37 +5797,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M55">
-        <v>351.4468722604265</v>
+        <v>324.3724794604265</v>
       </c>
       <c r="N55">
-        <v>-45.29131670487089</v>
+        <v>-18.2169239048709</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-45.29131670487089</v>
+        <v>-18.2169239048709</v>
       </c>
       <c r="Q55">
-        <v>136.1086832951291</v>
+        <v>163.1830760951291</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1781209103609132</v>
+        <v>0.178129751265813</v>
       </c>
       <c r="T55">
         <v>1.133508029968772</v>
       </c>
       <c r="U55">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V55">
         <v>0</v>
       </c>
       <c r="W55">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8711289805666289</v>
+        <v>0.9438394899124192</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.2010205094962099</v>
+        <v>0.1919526647215128</v>
       </c>
       <c r="C56">
-        <v>216.1214175274004</v>
+        <v>305.3836195716153</v>
       </c>
       <c r="D56">
-        <v>1437.499417527401</v>
+        <v>1526.761619571615</v>
       </c>
       <c r="E56">
         <v>775.1780000000001</v>
@@ -5879,37 +5879,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M56">
-        <v>358.077945321944</v>
+        <v>330.492714921944</v>
       </c>
       <c r="N56">
-        <v>-51.92238976638839</v>
+        <v>-24.33715936638845</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-51.92238976638839</v>
+        <v>-24.33715936638845</v>
       </c>
       <c r="Q56">
-        <v>129.4776102336116</v>
+        <v>157.0628406336116</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1809974518904982</v>
+        <v>0.1810064849889828</v>
       </c>
       <c r="T56">
         <v>1.158149508881137</v>
       </c>
       <c r="U56">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8549969624079876</v>
+        <v>0.9263609808399668</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.2027432813781836</v>
+        <v>0.1935074366034865</v>
       </c>
       <c r="C57">
-        <v>169.9349362069977</v>
+        <v>258.905891575984</v>
       </c>
       <c r="D57">
-        <v>1421.719936206998</v>
+        <v>1510.690891575984</v>
       </c>
       <c r="E57">
         <v>805.585</v>
@@ -5961,37 +5961,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M57">
-        <v>364.7090183834615</v>
+        <v>336.6129503834615</v>
       </c>
       <c r="N57">
-        <v>-58.55346282790589</v>
+        <v>-30.45739482790589</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-58.55346282790589</v>
+        <v>-30.45739482790589</v>
       </c>
       <c r="Q57">
-        <v>122.8465371720941</v>
+        <v>150.9426051720941</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1840018397102871</v>
+        <v>0.1840110735442935</v>
       </c>
       <c r="T57">
         <v>1.183886164634051</v>
       </c>
       <c r="U57">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8394515630914787</v>
+        <v>0.9095180539156038</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2044660532601573</v>
+        <v>0.1950622084854602</v>
       </c>
       <c r="C58">
-        <v>124.0911173045763</v>
+        <v>212.7629611994414</v>
       </c>
       <c r="D58">
-        <v>1406.283117304577</v>
+        <v>1494.954961199441</v>
       </c>
       <c r="E58">
         <v>835.9920000000002</v>
@@ -6043,37 +6043,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M58">
-        <v>371.340091444979</v>
+        <v>342.733185844979</v>
       </c>
       <c r="N58">
-        <v>-65.18453588942339</v>
+        <v>-36.57763028942344</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-65.18453588942339</v>
+        <v>-36.57763028942344</v>
       </c>
       <c r="Q58">
-        <v>116.2154641105766</v>
+        <v>144.8223697105766</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1871427906127936</v>
+        <v>0.1871522343066639</v>
       </c>
       <c r="T58">
         <v>1.210792668375734</v>
       </c>
       <c r="U58">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V58">
         <v>0</v>
       </c>
       <c r="W58">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8244613566077023</v>
+        <v>0.8932766600956821</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.206188825142131</v>
+        <v>0.196616980367434</v>
       </c>
       <c r="C59">
-        <v>78.57891898144044</v>
+        <v>166.9444741584775</v>
       </c>
       <c r="D59">
-        <v>1391.17791898144</v>
+        <v>1479.543474158478</v>
       </c>
       <c r="E59">
         <v>866.3990000000001</v>
@@ -6125,37 +6125,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M59">
-        <v>377.9711645064964</v>
+        <v>348.8534213064964</v>
       </c>
       <c r="N59">
-        <v>-71.81560895094083</v>
+        <v>-42.69786575094088</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-71.81560895094083</v>
+        <v>-42.69786575094088</v>
       </c>
       <c r="Q59">
-        <v>109.5843910490592</v>
+        <v>138.7021342490591</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1904298322549516</v>
+        <v>0.1904394955696095</v>
       </c>
       <c r="T59">
         <v>1.238950637407728</v>
       </c>
       <c r="U59">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V59">
         <v>0</v>
       </c>
       <c r="W59">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8099971222812514</v>
+        <v>0.8776051397431264</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2381875970241047</v>
+        <v>0.1981717522494077</v>
       </c>
       <c r="C60">
-        <v>-183.2150600406449</v>
+        <v>121.4404987820053</v>
       </c>
       <c r="D60">
-        <v>1159.790939959355</v>
+        <v>1464.446498782005</v>
       </c>
       <c r="E60">
         <v>896.8059999999998</v>
@@ -6207,45 +6207,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M60">
-        <v>476.6624707680138</v>
+        <v>354.9736567680139</v>
       </c>
       <c r="N60">
-        <v>-170.5069152124582</v>
+        <v>-48.81810121245832</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-170.5069152124582</v>
+        <v>-48.81810121245832</v>
       </c>
       <c r="Q60">
-        <v>10.89308478754177</v>
+        <v>132.5818987875417</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1938733996895932</v>
+        <v>0.1938832930831716</v>
       </c>
       <c r="T60">
         <v>1.268449462107912</v>
       </c>
       <c r="U60">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.6422900360967541</v>
+        <v>0.8624740166441072</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2404323689060784</v>
+        <v>0.1997265241313814</v>
       </c>
       <c r="C61">
-        <v>-226.9983864226404</v>
+        <v>76.24150466786773</v>
       </c>
       <c r="D61">
-        <v>1146.414613577359</v>
+        <v>1449.654504667868</v>
       </c>
       <c r="E61">
         <v>927.2129999999997</v>
@@ -6289,45 +6289,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M61">
-        <v>484.8807892295313</v>
+        <v>361.0938922295313</v>
       </c>
       <c r="N61">
-        <v>-178.7252336739757</v>
+        <v>-54.93833667397575</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-178.7252336739757</v>
+        <v>-54.93833667397575</v>
       </c>
       <c r="Q61">
-        <v>2.674766326024297</v>
+        <v>126.4616633260243</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1974849460234858</v>
+        <v>0.1974950807193465</v>
       </c>
       <c r="T61">
         <v>1.299387253866641</v>
       </c>
       <c r="U61">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V61">
         <v>0</v>
       </c>
       <c r="W61">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.631403764298504</v>
+        <v>0.8478558129721732</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2426771407880522</v>
+        <v>0.2012812960133551</v>
       </c>
       <c r="C62">
-        <v>-270.4766819490858</v>
+        <v>31.33834261992229</v>
       </c>
       <c r="D62">
-        <v>1133.343318050914</v>
+        <v>1435.158342619922</v>
       </c>
       <c r="E62">
         <v>957.6199999999999</v>
@@ -6371,45 +6371,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M62">
-        <v>493.0991076910488</v>
+        <v>367.2141276910488</v>
       </c>
       <c r="N62">
-        <v>-186.9435521354932</v>
+        <v>-61.05857213549325</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-186.9435521354932</v>
+        <v>-61.05857213549325</v>
       </c>
       <c r="Q62">
-        <v>-5.543552135493229</v>
+        <v>120.3414278645068</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2012770696740729</v>
+        <v>0.2012874577373302</v>
       </c>
       <c r="T62">
         <v>1.331871935213307</v>
       </c>
       <c r="U62">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V62">
         <v>0</v>
       </c>
       <c r="W62">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.6208803682268622</v>
+        <v>0.8337248827559702</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2449219126700259</v>
+        <v>0.2028360678953288</v>
       </c>
       <c r="C63">
-        <v>-313.6602627827551</v>
+        <v>-13.27777422304871</v>
       </c>
       <c r="D63">
-        <v>1120.566737217245</v>
+        <v>1420.949225776951</v>
       </c>
       <c r="E63">
         <v>988.0269999999998</v>
@@ -6453,45 +6453,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M63">
-        <v>501.3174261525663</v>
+        <v>373.3343631525663</v>
       </c>
       <c r="N63">
-        <v>-195.1618705970107</v>
+        <v>-67.17880759701075</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-195.1618705970107</v>
+        <v>-67.17880759701075</v>
       </c>
       <c r="Q63">
-        <v>-13.7618705970107</v>
+        <v>114.2211924029893</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2052636612041774</v>
+        <v>0.205274315628031</v>
       </c>
       <c r="T63">
         <v>1.366022497654674</v>
       </c>
       <c r="U63">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V63">
         <v>0</v>
       </c>
       <c r="W63">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.6107020015346185</v>
+        <v>0.8200572617271839</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2471666845519996</v>
+        <v>0.2043908397773025</v>
       </c>
       <c r="C64">
-        <v>-356.5589850811912</v>
+        <v>-57.61528814839676</v>
       </c>
       <c r="D64">
-        <v>1108.075014918809</v>
+        <v>1407.018711851603</v>
       </c>
       <c r="E64">
         <v>1018.434</v>
@@ -6535,45 +6535,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M64">
-        <v>509.5357446140838</v>
+        <v>379.4545986140838</v>
       </c>
       <c r="N64">
-        <v>-203.3801890585282</v>
+        <v>-73.29904305852824</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-203.3801890585282</v>
+        <v>-73.29904305852824</v>
       </c>
       <c r="Q64">
-        <v>-21.98018905852823</v>
+        <v>108.1009569414718</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2094600733411294</v>
+        <v>0.2094710081445582</v>
       </c>
       <c r="T64">
         <v>1.401970458119271</v>
       </c>
       <c r="U64">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.6008519692518022</v>
+        <v>0.8068305316993261</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2494114564339733</v>
+        <v>0.2399656116592762</v>
       </c>
       <c r="C65">
-        <v>-399.1822703539895</v>
+        <v>-345.8144341419168</v>
       </c>
       <c r="D65">
-        <v>1095.85872964601</v>
+        <v>1149.226565858083</v>
       </c>
       <c r="E65">
         <v>1048.841</v>
@@ -6617,37 +6617,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M65">
-        <v>517.7540630756013</v>
+        <v>489.0194480756012</v>
       </c>
       <c r="N65">
-        <v>-211.5985075200457</v>
+        <v>-182.8638925200456</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-211.5985075200457</v>
+        <v>-182.8638925200456</v>
       </c>
       <c r="Q65">
-        <v>-30.19850752004569</v>
+        <v>-1.463892520045619</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2138833185665653</v>
+        <v>0.2138945489052219</v>
       </c>
       <c r="T65">
         <v>1.439861551581954</v>
       </c>
       <c r="U65">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V65">
         <v>0</v>
       </c>
       <c r="W65">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5913146364065354</v>
+        <v>0.6260600815782376</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.251656228315947</v>
+        <v>0.24206038354125</v>
       </c>
       <c r="C66">
-        <v>-441.5391291610265</v>
+        <v>-388.4876258854522</v>
       </c>
       <c r="D66">
-        <v>1083.908870838973</v>
+        <v>1136.960374114548</v>
       </c>
       <c r="E66">
         <v>1079.248</v>
@@ -6699,37 +6699,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M66">
-        <v>525.9723815371187</v>
+        <v>496.7816615371187</v>
       </c>
       <c r="N66">
-        <v>-219.8168259815632</v>
+        <v>-190.6261059815632</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-219.8168259815632</v>
+        <v>-190.6261059815632</v>
       </c>
       <c r="Q66">
-        <v>-38.41682598156316</v>
+        <v>-9.226105981563165</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2185522996378588</v>
+        <v>0.2185638419303669</v>
       </c>
       <c r="T66">
         <v>1.479857705792564</v>
       </c>
       <c r="U66">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V66">
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5820753452126833</v>
+        <v>0.6162778928035775</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2539010001979207</v>
+        <v>0.2441551554232237</v>
       </c>
       <c r="C67">
-        <v>-483.6381832768989</v>
+        <v>-430.9017381661074</v>
       </c>
       <c r="D67">
-        <v>1072.216816723101</v>
+        <v>1124.953261833893</v>
       </c>
       <c r="E67">
         <v>1109.655</v>
@@ -6781,37 +6781,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M67">
-        <v>534.1906999986362</v>
+        <v>504.5438749986362</v>
       </c>
       <c r="N67">
-        <v>-228.0351444430806</v>
+        <v>-198.3883194430806</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-228.0351444430806</v>
+        <v>-198.3883194430806</v>
       </c>
       <c r="Q67">
-        <v>-46.63514444308063</v>
+        <v>-16.9883194430806</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2234880796275119</v>
+        <v>0.223499951699806</v>
       </c>
       <c r="T67">
         <v>1.522139354529494</v>
       </c>
       <c r="U67">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V67">
         <v>0</v>
       </c>
       <c r="W67">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.573120339901719</v>
+        <v>0.6067966944527532</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2561457720798945</v>
+        <v>0.2462499273051974</v>
       </c>
       <c r="C68">
-        <v>-525.4876864361504</v>
+        <v>-473.0648933970165</v>
       </c>
       <c r="D68">
-        <v>1060.77431356385</v>
+        <v>1113.197106602984</v>
       </c>
       <c r="E68">
         <v>1140.062</v>
@@ -6863,37 +6863,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M68">
-        <v>542.4090184601538</v>
+        <v>512.3060884601537</v>
       </c>
       <c r="N68">
-        <v>-236.2534629045982</v>
+        <v>-206.1505329045981</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-236.2534629045982</v>
+        <v>-206.1505329045981</v>
       </c>
       <c r="Q68">
-        <v>-54.85346290459822</v>
+        <v>-24.75053290459809</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2287141996165564</v>
+        <v>0.2287264208674473</v>
       </c>
       <c r="T68">
         <v>1.566908159074479</v>
       </c>
       <c r="U68">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V68">
         <v>0</v>
       </c>
       <c r="W68">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5644366983880564</v>
+        <v>0.597602805142863</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2583905439618682</v>
+        <v>0.2483446991871711</v>
       </c>
       <c r="C69">
-        <v>-567.0955437641944</v>
+        <v>-514.9848779745664</v>
       </c>
       <c r="D69">
-        <v>1049.573456235806</v>
+        <v>1101.684122025434</v>
       </c>
       <c r="E69">
         <v>1170.469</v>
@@ -6945,37 +6945,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M69">
-        <v>550.6273369216711</v>
+        <v>520.0683019216712</v>
       </c>
       <c r="N69">
-        <v>-244.4717813661156</v>
+        <v>-213.9127463661156</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-244.4717813661156</v>
+        <v>-213.9127463661156</v>
       </c>
       <c r="Q69">
-        <v>-63.07178136611557</v>
+        <v>-32.51274636611558</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2342570541503915</v>
+        <v>0.2342696457422185</v>
       </c>
       <c r="T69">
         <v>1.614390224500979</v>
       </c>
       <c r="U69">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V69">
         <v>0</v>
       </c>
       <c r="W69">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5560122700539065</v>
+        <v>0.5886833602899845</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2606353158438419</v>
+        <v>0.2504394710691448</v>
       </c>
       <c r="C70">
-        <v>-608.4693299900523</v>
+        <v>-556.6691594764129</v>
       </c>
       <c r="D70">
-        <v>1038.606670009948</v>
+        <v>1090.406840523587</v>
       </c>
       <c r="E70">
         <v>1200.876</v>
@@ -7027,37 +7027,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M70">
-        <v>558.8456553831886</v>
+        <v>527.8305153831886</v>
       </c>
       <c r="N70">
-        <v>-252.690099827633</v>
+        <v>-221.6749598276331</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-252.690099827633</v>
+        <v>-221.6749598276331</v>
       </c>
       <c r="Q70">
-        <v>-71.29009982763304</v>
+        <v>-40.27495982763307</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2401463370925912</v>
+        <v>0.2401593221716628</v>
       </c>
       <c r="T70">
         <v>1.664839919016635</v>
       </c>
       <c r="U70">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V70">
         <v>0</v>
       </c>
       <c r="W70">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5478356190237019</v>
+        <v>0.5800262520504258</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2628800877258156</v>
+        <v>0.2525342429511185</v>
       </c>
       <c r="C71">
-        <v>-649.6163065290953</v>
+        <v>-598.1249028139196</v>
       </c>
       <c r="D71">
-        <v>1027.866693470905</v>
+        <v>1079.358097186081</v>
       </c>
       <c r="E71">
         <v>1231.283</v>
@@ -7109,37 +7109,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M71">
-        <v>567.0639738447062</v>
+        <v>535.5927288447061</v>
       </c>
       <c r="N71">
-        <v>-260.9084182891506</v>
+        <v>-229.4371732891506</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-260.9084182891506</v>
+        <v>-229.4371732891506</v>
       </c>
       <c r="Q71">
-        <v>-79.50841828915063</v>
+        <v>-48.03717328915056</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2464155737729974</v>
+        <v>0.2464289777255874</v>
       </c>
       <c r="T71">
         <v>1.7185444325333</v>
       </c>
       <c r="U71">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V71">
         <v>0</v>
       </c>
       <c r="W71">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5398959723711845</v>
+        <v>0.5716200744844777</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2651248596077894</v>
+        <v>0.2546290148330922</v>
       </c>
       <c r="C72">
-        <v>-690.5434375167406</v>
+        <v>-639.3589854124425</v>
       </c>
       <c r="D72">
-        <v>1017.34656248326</v>
+        <v>1068.531014587558</v>
       </c>
       <c r="E72">
         <v>1261.69</v>
@@ -7191,37 +7191,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M72">
-        <v>575.2822923062237</v>
+        <v>543.3549423062236</v>
       </c>
       <c r="N72">
-        <v>-269.1267367506681</v>
+        <v>-237.1993867506681</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-269.1267367506681</v>
+        <v>-237.1993867506681</v>
       </c>
       <c r="Q72">
-        <v>-87.7267367506681</v>
+        <v>-55.79938675066805</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2531027595654306</v>
+        <v>0.2531166103164403</v>
       </c>
       <c r="T72">
         <v>1.775829246951077</v>
       </c>
       <c r="U72">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V72">
         <v>0</v>
       </c>
       <c r="W72">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5321831727658819</v>
+        <v>0.5634540734204136</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2673696314897631</v>
+        <v>0.256723786715066</v>
       </c>
       <c r="C73">
-        <v>-731.2574048675008</v>
+        <v>-680.3780114870478</v>
       </c>
       <c r="D73">
-        <v>1007.039595132499</v>
+        <v>1057.918988512952</v>
       </c>
       <c r="E73">
         <v>1292.097</v>
@@ -7273,37 +7273,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M73">
-        <v>583.5006107677411</v>
+        <v>551.1171557677411</v>
       </c>
       <c r="N73">
-        <v>-277.3450552121856</v>
+        <v>-244.9616002121855</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-277.3450552121856</v>
+        <v>-244.9616002121855</v>
       </c>
       <c r="Q73">
-        <v>-95.94505521218557</v>
+        <v>-63.56160021218554</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2602511305849282</v>
+        <v>0.2602654589480417</v>
       </c>
       <c r="T73">
         <v>1.837064738225251</v>
       </c>
       <c r="U73">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5246876351212919</v>
+        <v>0.5555181005553373</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2696144033717368</v>
+        <v>0.2588185585970397</v>
       </c>
       <c r="C74">
-        <v>-771.7646224278196</v>
+        <v>-721.1883254759246</v>
       </c>
       <c r="D74">
-        <v>996.9393775721799</v>
+        <v>1047.515674524075</v>
       </c>
       <c r="E74">
         <v>1322.504</v>
@@ -7355,37 +7355,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M74">
-        <v>591.7189292292585</v>
+        <v>558.8793692292585</v>
       </c>
       <c r="N74">
-        <v>-285.5633736737029</v>
+        <v>-252.7238136737029</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-285.5633736737029</v>
+        <v>-252.7238136737029</v>
       </c>
       <c r="Q74">
-        <v>-104.1633736737029</v>
+        <v>-71.32381367370292</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2679100995343899</v>
+        <v>0.2679249396247574</v>
       </c>
       <c r="T74">
         <v>1.902674193161868</v>
       </c>
       <c r="U74">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V74">
         <v>0</v>
       </c>
       <c r="W74">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5174003068557186</v>
+        <v>0.5478025713809578</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2718591752537105</v>
+        <v>0.2609133304790134</v>
       </c>
       <c r="C75">
-        <v>-812.0712492856765</v>
+        <v>-761.7960246889093</v>
       </c>
       <c r="D75">
-        <v>987.0397507143234</v>
+        <v>1037.31497531109</v>
       </c>
       <c r="E75">
         <v>1352.911</v>
@@ -7437,37 +7437,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M75">
-        <v>599.9372476907761</v>
+        <v>566.641582690776</v>
       </c>
       <c r="N75">
-        <v>-293.7816921352205</v>
+        <v>-260.4860271352204</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-293.7816921352205</v>
+        <v>-260.4860271352204</v>
       </c>
       <c r="Q75">
-        <v>-112.3816921352205</v>
+        <v>-79.08602713522041</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.276136399517145</v>
+        <v>0.2761517892404892</v>
       </c>
       <c r="T75">
         <v>1.973143607723418</v>
       </c>
       <c r="U75">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5103126314193388</v>
+        <v>0.54029842656752</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2741039471356842</v>
+        <v>0.2630081023609871</v>
       </c>
       <c r="C76">
-        <v>-852.1832022949952</v>
+        <v>-802.2069712241114</v>
       </c>
       <c r="D76">
-        <v>977.3347977050047</v>
+        <v>1027.311028775889</v>
       </c>
       <c r="E76">
         <v>1383.318</v>
@@ -7519,37 +7519,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M76">
-        <v>608.1555661522935</v>
+        <v>574.4037961522935</v>
       </c>
       <c r="N76">
-        <v>-302.000010596738</v>
+        <v>-268.2482405967379</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-302.000010596738</v>
+        <v>-268.2482405967379</v>
       </c>
       <c r="Q76">
-        <v>-120.600010596738</v>
+        <v>-86.8482405967379</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.284995491806266</v>
+        <v>0.2850114734420464</v>
       </c>
       <c r="T76">
         <v>2.049033746482011</v>
       </c>
       <c r="U76">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V76">
         <v>0</v>
       </c>
       <c r="W76">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.503416514778537</v>
+        <v>0.5329970964787698</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.298848719017658</v>
+        <v>0.2651028742429609</v>
       </c>
       <c r="C77">
-        <v>-978.1604415572522</v>
+        <v>-842.4268032015759</v>
       </c>
       <c r="D77">
-        <v>881.7645584427474</v>
+        <v>1017.498196798424</v>
       </c>
       <c r="E77">
         <v>1413.725</v>
@@ -7601,45 +7601,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M77">
-        <v>684.789634613811</v>
+        <v>582.166009613811</v>
       </c>
       <c r="N77">
-        <v>-378.6340790582555</v>
+        <v>-276.0104540582554</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-378.6340790582555</v>
+        <v>-276.0104540582554</v>
       </c>
       <c r="Q77">
-        <v>-197.2340790582554</v>
+        <v>-94.61045405825539</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2945633114785167</v>
+        <v>0.2945799323797283</v>
       </c>
       <c r="T77">
         <v>2.130995096341292</v>
       </c>
       <c r="U77">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4470797162813552</v>
+        <v>0.5258904685257195</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.3013934908996317</v>
+        <v>0.2671976461249346</v>
       </c>
       <c r="C78">
-        <v>-1017.346576139077</v>
+        <v>-882.4609453592188</v>
       </c>
       <c r="D78">
-        <v>872.9854238609232</v>
+        <v>1007.871054640781</v>
       </c>
       <c r="E78">
         <v>1444.132</v>
@@ -7683,45 +7683,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M78">
-        <v>693.9201630753286</v>
+        <v>589.9282230753284</v>
       </c>
       <c r="N78">
-        <v>-387.764607519773</v>
+        <v>-283.7726675197729</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-387.764607519773</v>
+        <v>-283.7726675197729</v>
       </c>
       <c r="Q78">
-        <v>-206.364607519773</v>
+        <v>-102.3726675197729</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3049284494567883</v>
+        <v>0.3049457628955504</v>
       </c>
       <c r="T78">
         <v>2.219786558688846</v>
       </c>
       <c r="U78">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V78">
         <v>0</v>
       </c>
       <c r="W78">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4411970884355479</v>
+        <v>0.5189708570977495</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.3039382627816054</v>
+        <v>0.2692924180069083</v>
       </c>
       <c r="C79">
-        <v>-1056.359618250291</v>
+        <v>-922.3146190528719</v>
       </c>
       <c r="D79">
-        <v>864.379381749709</v>
+        <v>998.424380947128</v>
       </c>
       <c r="E79">
         <v>1474.539</v>
@@ -7765,45 +7765,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M79">
-        <v>703.0506915368461</v>
+        <v>597.6904365368459</v>
       </c>
       <c r="N79">
-        <v>-396.8951359812905</v>
+        <v>-291.5348809812904</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-396.8951359812905</v>
+        <v>-291.5348809812904</v>
       </c>
       <c r="Q79">
-        <v>-215.4951359812905</v>
+        <v>-110.1348809812904</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3161949037809964</v>
+        <v>0.3162129699779656</v>
       </c>
       <c r="T79">
         <v>2.316299017762274</v>
       </c>
       <c r="U79">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V79">
         <v>0</v>
       </c>
       <c r="W79">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4354672561182031</v>
+        <v>0.5122309758367398</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.3064830346635791</v>
+        <v>0.271387189888882</v>
       </c>
       <c r="C80">
-        <v>-1095.204637045312</v>
+        <v>-961.9928516991727</v>
       </c>
       <c r="D80">
-        <v>855.9413629546876</v>
+        <v>989.1531483008274</v>
       </c>
       <c r="E80">
         <v>1504.946</v>
@@ -7847,45 +7847,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M80">
-        <v>712.1812199983635</v>
+        <v>605.4526499983634</v>
       </c>
       <c r="N80">
-        <v>-406.025664442808</v>
+        <v>-299.2970944428079</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-406.025664442808</v>
+        <v>-299.2970944428079</v>
       </c>
       <c r="Q80">
-        <v>-224.625664442808</v>
+        <v>-117.8970944428079</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3284855812255872</v>
+        <v>0.3285044686133277</v>
       </c>
       <c r="T80">
         <v>2.421585336751468</v>
       </c>
       <c r="U80">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4298843425782262</v>
+        <v>0.505663912043961</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.3090278065455528</v>
+        <v>0.3011319617708558</v>
       </c>
       <c r="C81">
-        <v>-1133.886505653042</v>
+        <v>-1107.630763444365</v>
       </c>
       <c r="D81">
-        <v>847.6664943469578</v>
+        <v>873.9222365556351</v>
       </c>
       <c r="E81">
         <v>1535.353</v>
@@ -7929,37 +7929,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M81">
-        <v>721.311748459881</v>
+        <v>697.290218459881</v>
       </c>
       <c r="N81">
-        <v>-415.1561929043254</v>
+        <v>-391.1346629043254</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-415.1561929043254</v>
+        <v>-391.1346629043254</v>
       </c>
       <c r="Q81">
-        <v>-233.7561929043254</v>
+        <v>-209.7346629043254</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3419467993791866</v>
+        <v>0.3419665861663433</v>
       </c>
       <c r="T81">
         <v>2.536898924215824</v>
       </c>
       <c r="U81">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V81">
         <v>0</v>
       </c>
       <c r="W81">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4244427686215398</v>
+        <v>0.4390647501577859</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.3115725784275266</v>
+        <v>0.3035767336528294</v>
       </c>
       <c r="C82">
-        <v>-1172.409910561585</v>
+        <v>-1146.326100722469</v>
       </c>
       <c r="D82">
-        <v>839.5500894384147</v>
+        <v>865.6338992775306</v>
       </c>
       <c r="E82">
         <v>1565.76</v>
@@ -8011,37 +8011,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M82">
-        <v>730.4422769213985</v>
+        <v>706.1166769213985</v>
       </c>
       <c r="N82">
-        <v>-424.2867213658429</v>
+        <v>-399.9611213658429</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-424.2867213658429</v>
+        <v>-399.9611213658429</v>
       </c>
       <c r="Q82">
-        <v>-242.8867213658429</v>
+        <v>-218.5611213658429</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3567541393481459</v>
+        <v>0.3567749154746605</v>
       </c>
       <c r="T82">
         <v>2.663743870426615</v>
       </c>
       <c r="U82">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V82">
         <v>0</v>
       </c>
       <c r="W82">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4191372340137705</v>
+        <v>0.4335764407808135</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3141173503095003</v>
+        <v>0.3060215055348032</v>
       </c>
       <c r="C83">
-        <v>-1210.779360468932</v>
+        <v>-1184.865700726791</v>
       </c>
       <c r="D83">
-        <v>831.5876395310679</v>
+        <v>857.5012992732087</v>
       </c>
       <c r="E83">
         <v>1596.167</v>
@@ -8093,37 +8093,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M83">
-        <v>739.572805382916</v>
+        <v>714.943135382916</v>
       </c>
       <c r="N83">
-        <v>-433.4172498273605</v>
+        <v>-408.7875798273604</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-433.4172498273605</v>
+        <v>-408.7875798273604</v>
       </c>
       <c r="Q83">
-        <v>-252.0172498273605</v>
+        <v>-227.3875798273604</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3731201466822589</v>
+        <v>0.3731420162891163</v>
       </c>
       <c r="T83">
         <v>2.803940916238543</v>
       </c>
       <c r="U83">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V83">
         <v>0</v>
       </c>
       <c r="W83">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4139627002605141</v>
+        <v>0.4282236452156183</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.316662122191474</v>
+        <v>0.3084662774167769</v>
       </c>
       <c r="C84">
-        <v>-1248.999194634721</v>
+        <v>-1223.25391204115</v>
       </c>
       <c r="D84">
-        <v>823.7748053652795</v>
+        <v>849.5200879588506</v>
       </c>
       <c r="E84">
         <v>1626.574</v>
@@ -8175,37 +8175,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M84">
-        <v>748.7033338444336</v>
+        <v>723.7695938444335</v>
       </c>
       <c r="N84">
-        <v>-442.547778288878</v>
+        <v>-417.614038288878</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-442.547778288878</v>
+        <v>-417.614038288878</v>
       </c>
       <c r="Q84">
-        <v>-261.147778288878</v>
+        <v>-236.214038288878</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3913045992757177</v>
+        <v>0.3913276838607339</v>
       </c>
       <c r="T84">
         <v>2.959715411585128</v>
       </c>
       <c r="U84">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V84">
         <v>0</v>
       </c>
       <c r="W84">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.408914374647581</v>
+        <v>0.423001405639818</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3192068940734477</v>
+        <v>0.3109110492987506</v>
       </c>
       <c r="C85">
-        <v>-1287.073590765591</v>
+        <v>-1261.494922844196</v>
       </c>
       <c r="D85">
-        <v>816.1074092344094</v>
+        <v>841.6860771558033</v>
       </c>
       <c r="E85">
         <v>1656.981</v>
@@ -8257,37 +8257,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M85">
-        <v>757.8338623059509</v>
+        <v>732.5960523059509</v>
       </c>
       <c r="N85">
-        <v>-451.6783067503953</v>
+        <v>-426.4404967503954</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-451.6783067503953</v>
+        <v>-426.4404967503954</v>
       </c>
       <c r="Q85">
-        <v>-270.2783067503954</v>
+        <v>-245.0404967503954</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.4116283992331129</v>
+        <v>0.4116528417348947</v>
       </c>
       <c r="T85">
         <v>3.13381631814896</v>
       </c>
       <c r="U85">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V85">
         <v>0</v>
       </c>
       <c r="W85">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4039876954349596</v>
+        <v>0.4179050031622299</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.3217516659554214</v>
+        <v>0.3133558211807243</v>
       </c>
       <c r="C86">
-        <v>-1325.006572464232</v>
+        <v>-1299.592768237873</v>
       </c>
       <c r="D86">
-        <v>808.5814275357681</v>
+        <v>833.9952317621263</v>
       </c>
       <c r="E86">
         <v>1687.388</v>
@@ -8339,37 +8339,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M86">
-        <v>766.9643907674683</v>
+        <v>741.4225107674683</v>
       </c>
       <c r="N86">
-        <v>-460.8088352119128</v>
+        <v>-435.2669552119128</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-460.8088352119128</v>
+        <v>-435.2669552119128</v>
       </c>
       <c r="Q86">
-        <v>-279.4088352119128</v>
+        <v>-253.8669552119128</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4344926741851823</v>
+        <v>0.4345186443433255</v>
       </c>
       <c r="T86">
         <v>3.329679838033268</v>
       </c>
       <c r="U86">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V86">
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3991783181083529</v>
+        <v>0.4129299436007748</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.3242964378373951</v>
+        <v>0.315800593062698</v>
       </c>
       <c r="C87">
-        <v>-1362.80201627004</v>
+        <v>-1337.551337177719</v>
       </c>
       <c r="D87">
-        <v>801.1929837299601</v>
+        <v>826.4436628222807</v>
       </c>
       <c r="E87">
         <v>1717.795</v>
@@ -8421,37 +8421,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M87">
-        <v>776.0949192289859</v>
+        <v>750.2489692289859</v>
       </c>
       <c r="N87">
-        <v>-469.9393636734303</v>
+        <v>-444.0934136734303</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-469.9393636734303</v>
+        <v>-444.0934136734303</v>
       </c>
       <c r="Q87">
-        <v>-288.5393636734303</v>
+        <v>-262.6934136734303</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4604055191308611</v>
+        <v>0.4604332206328805</v>
       </c>
       <c r="T87">
         <v>3.551658493902153</v>
       </c>
       <c r="U87">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V87">
         <v>0</v>
       </c>
       <c r="W87">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3944821026011958</v>
+        <v>0.4080719442642951</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.3268412097193689</v>
+        <v>0.3182453649446718</v>
       </c>
       <c r="C88">
-        <v>-1400.463658317256</v>
+        <v>-1375.37437903005</v>
       </c>
       <c r="D88">
-        <v>793.938341682744</v>
+        <v>819.0276209699496</v>
       </c>
       <c r="E88">
         <v>1748.202</v>
@@ -8503,37 +8503,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M88">
-        <v>785.2254476905034</v>
+        <v>759.0754276905034</v>
       </c>
       <c r="N88">
-        <v>-479.0698921349478</v>
+        <v>-452.9198721349478</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-479.0698921349478</v>
+        <v>-452.9198721349478</v>
       </c>
       <c r="Q88">
-        <v>-297.6698921349479</v>
+        <v>-271.5198721349478</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4900201990687797</v>
+        <v>0.4900498792495149</v>
       </c>
       <c r="T88">
         <v>3.805348386323735</v>
       </c>
       <c r="U88">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V88">
         <v>0</v>
       </c>
       <c r="W88">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3898951014081586</v>
+        <v>0.4033269216565707</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.3293859816013425</v>
+        <v>0.3206901368266454</v>
       </c>
       <c r="C89">
-        <v>-1437.995100634631</v>
+        <v>-1413.065509779237</v>
       </c>
       <c r="D89">
-        <v>786.8138993653686</v>
+        <v>811.7434902207626</v>
       </c>
       <c r="E89">
         <v>1778.609</v>
@@ -8585,37 +8585,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M89">
-        <v>794.3559761520207</v>
+        <v>767.9018861520208</v>
       </c>
       <c r="N89">
-        <v>-488.2004205964652</v>
+        <v>-461.7463305964652</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-488.2004205964652</v>
+        <v>-461.7463305964652</v>
       </c>
       <c r="Q89">
-        <v>-306.8004205964652</v>
+        <v>-280.3463305964652</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5241909836125319</v>
+        <v>0.5242229468840929</v>
       </c>
       <c r="T89">
         <v>4.098067492964022</v>
       </c>
       <c r="U89">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V89">
         <v>0</v>
       </c>
       <c r="W89">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3854135485184097</v>
+        <v>0.3986909800283344</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.3319307534833162</v>
+        <v>0.3231349087086192</v>
       </c>
       <c r="C90">
-        <v>-1475.399817108921</v>
+        <v>-1450.628217906669</v>
       </c>
       <c r="D90">
-        <v>779.8161828910789</v>
+        <v>804.5877820933307</v>
       </c>
       <c r="E90">
         <v>1809.016</v>
@@ -8667,37 +8667,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M90">
-        <v>803.4865046135383</v>
+        <v>776.7283446135383</v>
       </c>
       <c r="N90">
-        <v>-497.3309490579827</v>
+        <v>-470.5727890579827</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-497.3309490579827</v>
+        <v>-470.5727890579827</v>
       </c>
       <c r="Q90">
-        <v>-315.9309490579827</v>
+        <v>-289.1727890579828</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5640568989135765</v>
+        <v>0.5640915257911007</v>
       </c>
       <c r="T90">
         <v>4.439573117377692</v>
       </c>
       <c r="U90">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V90">
         <v>0</v>
       </c>
       <c r="W90">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3810338491034277</v>
+        <v>0.3941604007098305</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.33447552536529</v>
+        <v>0.3255796805905929</v>
       </c>
       <c r="C91">
-        <v>-1512.681159132957</v>
+        <v>-1488.06586996149</v>
       </c>
       <c r="D91">
-        <v>772.9418408670429</v>
+        <v>797.5571300385096</v>
       </c>
       <c r="E91">
         <v>1839.423</v>
@@ -8749,37 +8749,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M91">
-        <v>812.6170330750558</v>
+        <v>785.5548030750558</v>
       </c>
       <c r="N91">
-        <v>-506.4614775195002</v>
+        <v>-479.3992475195002</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-506.4614775195002</v>
+        <v>-479.3992475195002</v>
       </c>
       <c r="Q91">
-        <v>-325.0614775195003</v>
+        <v>-297.9992475195003</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.6111711624511743</v>
+        <v>0.6112089372266554</v>
       </c>
       <c r="T91">
         <v>4.843170673502937</v>
       </c>
       <c r="U91">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V91">
         <v>0</v>
       </c>
       <c r="W91">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3767525699000185</v>
+        <v>0.389731632162529</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.3370202972472637</v>
+        <v>0.3280244524725666</v>
       </c>
       <c r="C92">
-        <v>-1549.842360957596</v>
+        <v>-1525.381715841793</v>
       </c>
       <c r="D92">
-        <v>766.1876390424038</v>
+        <v>790.6482841582068</v>
       </c>
       <c r="E92">
         <v>1869.83</v>
@@ -8831,37 +8831,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M92">
-        <v>821.7475615365734</v>
+        <v>794.3812615365733</v>
       </c>
       <c r="N92">
-        <v>-515.5920059810178</v>
+        <v>-488.2257059810178</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-515.5920059810178</v>
+        <v>-488.2257059810178</v>
       </c>
       <c r="Q92">
-        <v>-334.1920059810178</v>
+        <v>-306.8257059810178</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6677082786962918</v>
+        <v>0.6677498309493209</v>
       </c>
       <c r="T92">
         <v>5.327487740853231</v>
       </c>
       <c r="U92">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V92">
         <v>0</v>
       </c>
       <c r="W92">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3725664302344627</v>
+        <v>0.3854012806940564</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.3395650691292375</v>
+        <v>0.3304692243545403</v>
       </c>
       <c r="C93">
-        <v>-1586.886544765495</v>
+        <v>-1562.578893803684</v>
       </c>
       <c r="D93">
-        <v>759.5504552345045</v>
+        <v>783.858106196316</v>
       </c>
       <c r="E93">
         <v>1900.237</v>
@@ -8913,37 +8913,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M93">
-        <v>830.8780899980908</v>
+        <v>803.2077199980907</v>
       </c>
       <c r="N93">
-        <v>-524.7225344425352</v>
+        <v>-497.0521644425352</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-524.7225344425352</v>
+        <v>-497.0521644425352</v>
       </c>
       <c r="Q93">
-        <v>-343.3225344425352</v>
+        <v>-315.6521644425352</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7368091985514353</v>
+        <v>0.7368553677214678</v>
       </c>
       <c r="T93">
         <v>5.919430823170257</v>
       </c>
       <c r="U93">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V93">
         <v>0</v>
       </c>
       <c r="W93">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3684722936384796</v>
+        <v>0.3811661017853306</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.3421098410112111</v>
+        <v>0.3329139962365141</v>
       </c>
       <c r="C94">
-        <v>-1623.816725483438</v>
+        <v>-1599.660435214432</v>
       </c>
       <c r="D94">
-        <v>753.0272745165616</v>
+        <v>777.1835647855681</v>
       </c>
       <c r="E94">
         <v>1930.644</v>
@@ -8995,37 +8995,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M94">
-        <v>840.0086184596083</v>
+        <v>812.0341784596083</v>
       </c>
       <c r="N94">
-        <v>-533.8530629040528</v>
+        <v>-505.8786229040527</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-533.8530629040528</v>
+        <v>-505.8786229040527</v>
       </c>
       <c r="Q94">
-        <v>-352.4530629040528</v>
+        <v>-324.4786229040527</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.8231853483703651</v>
+        <v>0.8232372886866515</v>
       </c>
       <c r="T94">
         <v>6.659359676066541</v>
       </c>
       <c r="U94">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V94">
         <v>0</v>
       </c>
       <c r="W94">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3644671600119743</v>
+        <v>0.3770229919833161</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.3446546128931849</v>
+        <v>0.3353587681184877</v>
       </c>
       <c r="C95">
-        <v>-1660.6358153488</v>
+        <v>-1636.629269064832</v>
       </c>
       <c r="D95">
-        <v>746.6151846511996</v>
+        <v>770.6217309351687</v>
       </c>
       <c r="E95">
         <v>1961.051</v>
@@ -9077,37 +9077,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M95">
-        <v>849.1391469211258</v>
+        <v>820.8606369211258</v>
       </c>
       <c r="N95">
-        <v>-542.9835913655702</v>
+        <v>-514.7050813655702</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-542.9835913655702</v>
+        <v>-514.7050813655702</v>
       </c>
       <c r="Q95">
-        <v>-361.5835913655702</v>
+        <v>-333.3050813655702</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.9342403981375601</v>
+        <v>0.9342997584990302</v>
       </c>
       <c r="T95">
         <v>7.610696772647476</v>
       </c>
       <c r="U95">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V95">
         <v>0</v>
       </c>
       <c r="W95">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3605481582914155</v>
+        <v>0.3729689813168289</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3471993847751586</v>
+        <v>0.3378035400004615</v>
       </c>
       <c r="C96">
-        <v>-1697.346628244677</v>
+        <v>-1673.488226254889</v>
       </c>
       <c r="D96">
-        <v>740.3113717553227</v>
+        <v>764.1697737451113</v>
       </c>
       <c r="E96">
         <v>1991.458</v>
@@ -9159,37 +9159,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M96">
-        <v>858.2696753826432</v>
+        <v>829.6870953826432</v>
       </c>
       <c r="N96">
-        <v>-552.1141198270876</v>
+        <v>-523.5315398270876</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-552.1141198270876</v>
+        <v>-523.5315398270876</v>
       </c>
       <c r="Q96">
-        <v>-370.7141198270876</v>
+        <v>-342.1315398270876</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.082313797827154</v>
+        <v>1.082383051582202</v>
       </c>
       <c r="T96">
         <v>8.879146234755391</v>
       </c>
       <c r="U96">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V96">
         <v>0</v>
       </c>
       <c r="W96">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3567125395861876</v>
+        <v>0.369001226196437</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3497441566571323</v>
+        <v>0.3402483118824352</v>
       </c>
       <c r="C97">
-        <v>-1733.951883817241</v>
+        <v>-1710.240043666008</v>
       </c>
       <c r="D97">
-        <v>734.1131161827589</v>
+        <v>757.8249563339922</v>
       </c>
       <c r="E97">
         <v>2021.865</v>
@@ -9241,37 +9241,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M97">
-        <v>867.4002038441607</v>
+        <v>838.5135538441607</v>
       </c>
       <c r="N97">
-        <v>-561.2446482886052</v>
+        <v>-532.3579982886051</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-561.2446482886052</v>
+        <v>-532.3579982886051</v>
       </c>
       <c r="Q97">
-        <v>-379.8446482886052</v>
+        <v>-350.9579982886052</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.289616557392585</v>
+        <v>1.289699661898643</v>
       </c>
       <c r="T97">
         <v>10.65497548170647</v>
       </c>
       <c r="U97">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V97">
         <v>0</v>
       </c>
       <c r="W97">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3529576707484383</v>
+        <v>0.3651170027627904</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.352288928539106</v>
+        <v>0.3426930837644089</v>
       </c>
       <c r="C98">
-        <v>-1770.454211387977</v>
+        <v>-1746.887368031978</v>
       </c>
       <c r="D98">
-        <v>728.0177886120221</v>
+        <v>751.5846319680213</v>
       </c>
       <c r="E98">
         <v>2052.272</v>
@@ -9323,37 +9323,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M98">
-        <v>876.5307323056782</v>
+        <v>847.3400123056781</v>
       </c>
       <c r="N98">
-        <v>-570.3751767501226</v>
+        <v>-541.1844567501225</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-570.3751767501226</v>
+        <v>-541.1844567501225</v>
       </c>
       <c r="Q98">
-        <v>-388.9751767501226</v>
+        <v>-359.7844567501226</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.600570696740728</v>
+        <v>1.600674577373301</v>
       </c>
       <c r="T98">
         <v>13.31871935213306</v>
       </c>
       <c r="U98">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V98">
         <v>0</v>
       </c>
       <c r="W98">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3492810283448088</v>
+        <v>0.3613137006506779</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.3548337004210798</v>
+        <v>0.3451378556463826</v>
       </c>
       <c r="C99">
-        <v>-1806.856153672629</v>
+        <v>-1783.432759620277</v>
       </c>
       <c r="D99">
-        <v>722.0228463273709</v>
+        <v>745.446240379723</v>
       </c>
       <c r="E99">
         <v>2082.679</v>
@@ -9405,37 +9405,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M99">
-        <v>885.6612607671956</v>
+        <v>856.1664707671956</v>
       </c>
       <c r="N99">
-        <v>-579.50570521164</v>
+        <v>-550.0109152116401</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-579.50570521164</v>
+        <v>-550.0109152116401</v>
       </c>
       <c r="Q99">
-        <v>-398.10570521164</v>
+        <v>-368.6109152116401</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.118827595654304</v>
+        <v>2.118966103164401</v>
       </c>
       <c r="T99">
         <v>17.75829246951075</v>
       </c>
       <c r="U99">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V99">
         <v>0</v>
       </c>
       <c r="W99">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3456801930010479</v>
+        <v>0.3575888171388153</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.3573784723030534</v>
+        <v>0.3475826275283563</v>
       </c>
       <c r="C100">
-        <v>-1843.160170317892</v>
+        <v>-1819.878695734425</v>
       </c>
       <c r="D100">
-        <v>716.1258296821084</v>
+        <v>739.4073042655754</v>
       </c>
       <c r="E100">
         <v>2113.086</v>
@@ -9487,37 +9487,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M100">
-        <v>894.7917892287131</v>
+        <v>864.9929292287131</v>
       </c>
       <c r="N100">
-        <v>-588.6362336731576</v>
+        <v>-558.8373736731576</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-588.6362336731576</v>
+        <v>-558.8373736731576</v>
       </c>
       <c r="Q100">
-        <v>-407.2362336731576</v>
+        <v>-377.4373736731576</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.155341393481455</v>
+        <v>3.155549154746601</v>
       </c>
       <c r="T100">
         <v>26.63743870426612</v>
       </c>
       <c r="U100">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V100">
         <v>0</v>
       </c>
       <c r="W100">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3421528440928739</v>
+        <v>0.353939951657807</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3599232441850271</v>
+        <v>0.35002739941033</v>
       </c>
       <c r="C101">
-        <v>-1879.368641266207</v>
+        <v>-1856.227574047483</v>
       </c>
       <c r="D101">
-        <v>710.3243587337928</v>
+        <v>733.4654259525169</v>
       </c>
       <c r="E101">
         <v>2143.492999999999</v>
@@ -9569,37 +9569,37 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M101">
-        <v>903.9223176902306</v>
+        <v>873.8193876902305</v>
       </c>
       <c r="N101">
-        <v>-597.766762134675</v>
+        <v>-567.663832134675</v>
       </c>
       <c r="O101">
         <v>-0</v>
       </c>
       <c r="P101">
-        <v>-597.766762134675</v>
+        <v>-567.663832134675</v>
       </c>
       <c r="Q101">
-        <v>-416.366762134675</v>
+        <v>-386.263832134675</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.264882786962911</v>
+        <v>6.265298309493203</v>
       </c>
       <c r="T101">
         <v>53.27487740853225</v>
       </c>
       <c r="U101">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V101">
         <v>0</v>
       </c>
       <c r="W101">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3386967547586025</v>
+        <v>0.3503648006309604</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/bahrain/bahrain_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_telecom_services.xlsx
@@ -1133,43 +1133,43 @@
         <v>3.93577981651376</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>96.09523008874631</v>
       </c>
       <c r="G2">
         <v>1.97538742023701</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.06929580674567</v>
       </c>
       <c r="I2">
         <v>0.2850659387641</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>2173.9</v>
       </c>
       <c r="L2">
-        <v>4008.35367386677</v>
+        <v>3944.24492195147</v>
       </c>
       <c r="M2">
         <v>2620.1</v>
       </c>
       <c r="N2">
-        <v>3587.75367386677</v>
+        <v>3554.05192195147</v>
       </c>
       <c r="O2">
         <v>866.8</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>30.407</v>
       </c>
       <c r="Q2">
         <v>0.130964794891387</v>
       </c>
       <c r="R2">
-        <v>0.107994983094932</v>
+        <v>0.108584754976906</v>
       </c>
       <c r="S2">
         <v>0.126377188197372</v>
@@ -1191,13 +1191,13 @@
         <v>0.132794013108588</v>
       </c>
       <c r="X2">
-        <v>0.107994983094932</v>
+        <v>0.108623215247406</v>
       </c>
       <c r="Y2">
         <v>0.745171901817582</v>
       </c>
       <c r="Z2">
-        <v>0.532748774085323</v>
+        <v>0.53813007483366</v>
       </c>
       <c r="AA2">
         <v>866.8</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1079949830949321</v>
+        <v>0.1085847549769058</v>
       </c>
       <c r="C2">
-        <v>4008.353673866769</v>
+        <v>3944.24492195147</v>
       </c>
       <c r="D2">
-        <v>3587.75367386677</v>
+        <v>3554.05192195147</v>
       </c>
       <c r="E2">
-        <v>-866.8</v>
+        <v>-836.3929999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30.407</v>
       </c>
       <c r="G2">
         <v>420.6</v>
@@ -1451,28 +1451,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.18595996151748</v>
       </c>
       <c r="N2">
-        <v>306.1555555555556</v>
+        <v>302.9695955940381</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>306.1555555555556</v>
+        <v>302.9695955940381</v>
       </c>
       <c r="Q2">
-        <v>487.5555555555555</v>
+        <v>484.3695955940381</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1079949830949321</v>
+        <v>0.1086232152474061</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5381300748336596</v>
       </c>
       <c r="U2">
         <v>0.1047771881973717</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>96.09523008874629</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1085847549769058</v>
+        <v>0.1091745268588795</v>
       </c>
       <c r="C3">
-        <v>3944.24492195147</v>
+        <v>3880.76343612045</v>
       </c>
       <c r="D3">
-        <v>3554.05192195147</v>
+        <v>3520.97743612045</v>
       </c>
       <c r="E3">
-        <v>-836.3929999999999</v>
+        <v>-805.986</v>
       </c>
       <c r="F3">
-        <v>30.407</v>
+        <v>60.814</v>
       </c>
       <c r="G3">
         <v>420.6</v>
@@ -1533,28 +1533,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M3">
-        <v>3.18595996151748</v>
+        <v>6.371919923034961</v>
       </c>
       <c r="N3">
-        <v>302.9695955940381</v>
+        <v>299.7836356325206</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>302.9695955940381</v>
+        <v>299.7836356325206</v>
       </c>
       <c r="Q3">
-        <v>484.3695955940381</v>
+        <v>481.1836356325206</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1086232152474061</v>
+        <v>0.1092642684642164</v>
       </c>
       <c r="T3">
-        <v>0.5381300748336596</v>
+        <v>0.5436211980462479</v>
       </c>
       <c r="U3">
         <v>0.1047771881973717</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>96.09523008874629</v>
+        <v>48.04761504437315</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1091745268588795</v>
+        <v>0.1097642987408532</v>
       </c>
       <c r="C4">
-        <v>3880.76343612045</v>
+        <v>3817.891865574609</v>
       </c>
       <c r="D4">
-        <v>3520.97743612045</v>
+        <v>3488.512865574609</v>
       </c>
       <c r="E4">
-        <v>-805.986</v>
+        <v>-775.579</v>
       </c>
       <c r="F4">
-        <v>60.814</v>
+        <v>91.22099999999999</v>
       </c>
       <c r="G4">
         <v>420.6</v>
@@ -1615,28 +1615,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M4">
-        <v>6.371919923034961</v>
+        <v>9.55787988455244</v>
       </c>
       <c r="N4">
-        <v>299.7836356325206</v>
+        <v>296.5976756710031</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>299.7836356325206</v>
+        <v>296.5976756710031</v>
       </c>
       <c r="Q4">
-        <v>481.1836356325206</v>
+        <v>477.9976756710031</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1092642684642164</v>
+        <v>0.1099185392731258</v>
       </c>
       <c r="T4">
-        <v>0.5436211980462479</v>
+        <v>0.5492255402941473</v>
       </c>
       <c r="U4">
         <v>0.1047771881973717</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>48.04761504437315</v>
+        <v>32.03174336291544</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1097642987408532</v>
+        <v>0.110354070622827</v>
       </c>
       <c r="C5">
-        <v>3817.891865574609</v>
+        <v>3755.61349358878</v>
       </c>
       <c r="D5">
-        <v>3488.512865574609</v>
+        <v>3456.641493588781</v>
       </c>
       <c r="E5">
-        <v>-775.579</v>
+        <v>-745.1719999999999</v>
       </c>
       <c r="F5">
-        <v>91.22099999999999</v>
+        <v>121.628</v>
       </c>
       <c r="G5">
         <v>420.6</v>
@@ -1697,28 +1697,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M5">
-        <v>9.55787988455244</v>
+        <v>12.74383984606992</v>
       </c>
       <c r="N5">
-        <v>296.5976756710031</v>
+        <v>293.4117157094856</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>296.5976756710031</v>
+        <v>293.4117157094856</v>
       </c>
       <c r="Q5">
-        <v>477.9976756710031</v>
+        <v>474.8117157094856</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1099185392731258</v>
+        <v>0.1105864407238876</v>
       </c>
       <c r="T5">
-        <v>0.5492255402941473</v>
+        <v>0.5549466396722115</v>
       </c>
       <c r="U5">
         <v>0.1047771881973717</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.03174336291544</v>
+        <v>24.02380752218657</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.110354070622827</v>
+        <v>0.1109438425048007</v>
       </c>
       <c r="C6">
-        <v>3755.61349358878</v>
+        <v>3693.912208809187</v>
       </c>
       <c r="D6">
-        <v>3456.641493588781</v>
+        <v>3425.347208809187</v>
       </c>
       <c r="E6">
-        <v>-745.1719999999999</v>
+        <v>-714.765</v>
       </c>
       <c r="F6">
-        <v>121.628</v>
+        <v>152.035</v>
       </c>
       <c r="G6">
         <v>420.6</v>
@@ -1779,28 +1779,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M6">
-        <v>12.74383984606992</v>
+        <v>15.9297998075874</v>
       </c>
       <c r="N6">
-        <v>293.4117157094856</v>
+        <v>290.2257557479682</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>293.4117157094856</v>
+        <v>290.2257557479682</v>
       </c>
       <c r="Q6">
-        <v>474.8117157094856</v>
+        <v>471.6257557479681</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1105864407238876</v>
+        <v>0.1112684032578233</v>
       </c>
       <c r="T6">
-        <v>0.5549466396722115</v>
+        <v>0.5607881832477083</v>
       </c>
       <c r="U6">
         <v>0.1047771881973717</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.02380752218657</v>
+        <v>19.21904601774926</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1109438425048007</v>
+        <v>0.1115336143867744</v>
       </c>
       <c r="C7">
-        <v>3693.912208809187</v>
+        <v>3632.772478096006</v>
       </c>
       <c r="D7">
-        <v>3425.347208809187</v>
+        <v>3394.614478096006</v>
       </c>
       <c r="E7">
-        <v>-714.765</v>
+        <v>-684.3579999999999</v>
       </c>
       <c r="F7">
-        <v>152.035</v>
+        <v>182.442</v>
       </c>
       <c r="G7">
         <v>420.6</v>
@@ -1861,28 +1861,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M7">
-        <v>15.9297998075874</v>
+        <v>19.11575976910488</v>
       </c>
       <c r="N7">
-        <v>290.2257557479682</v>
+        <v>287.0397957864507</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>290.2257557479682</v>
+        <v>287.0397957864507</v>
       </c>
       <c r="Q7">
-        <v>471.6257557479681</v>
+        <v>468.4397957864506</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1112684032578233</v>
+        <v>0.1119648756329065</v>
       </c>
       <c r="T7">
-        <v>0.5607881832477083</v>
+        <v>0.5667540149843862</v>
       </c>
       <c r="U7">
         <v>0.1047771881973717</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.21904601774926</v>
+        <v>16.01587168145771</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1115336143867744</v>
+        <v>0.1121233862687481</v>
       </c>
       <c r="C8">
-        <v>3632.772478096006</v>
+        <v>3572.179320814931</v>
       </c>
       <c r="D8">
-        <v>3394.614478096006</v>
+        <v>3364.428320814931</v>
       </c>
       <c r="E8">
-        <v>-684.3579999999999</v>
+        <v>-653.951</v>
       </c>
       <c r="F8">
-        <v>182.442</v>
+        <v>212.849</v>
       </c>
       <c r="G8">
         <v>420.6</v>
@@ -1943,28 +1943,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M8">
-        <v>19.11575976910488</v>
+        <v>22.30171973062236</v>
       </c>
       <c r="N8">
-        <v>287.0397957864507</v>
+        <v>283.8538358249332</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>287.0397957864507</v>
+        <v>283.8538358249332</v>
       </c>
       <c r="Q8">
-        <v>468.4397957864506</v>
+        <v>465.2538358249332</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1119648756329065</v>
+        <v>0.1126763259085291</v>
       </c>
       <c r="T8">
-        <v>0.5667540149843862</v>
+        <v>0.5728481441777665</v>
       </c>
       <c r="U8">
         <v>0.1047771881973717</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.01587168145772</v>
+        <v>13.72789001267804</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1121233862687481</v>
+        <v>0.1128331581507218</v>
       </c>
       <c r="C9">
-        <v>3572.179320814931</v>
+        <v>3506.148508855165</v>
       </c>
       <c r="D9">
-        <v>3364.428320814931</v>
+        <v>3328.804508855165</v>
       </c>
       <c r="E9">
-        <v>-653.9509999999999</v>
+        <v>-623.544</v>
       </c>
       <c r="F9">
-        <v>212.849</v>
+        <v>243.256</v>
       </c>
       <c r="G9">
         <v>420.6</v>
@@ -2025,45 +2025,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M9">
-        <v>22.30171973062236</v>
+        <v>25.85256369213984</v>
       </c>
       <c r="N9">
-        <v>283.8538358249332</v>
+        <v>280.3029918634157</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>283.8538358249332</v>
+        <v>280.3029918634157</v>
       </c>
       <c r="Q9">
-        <v>465.2538358249332</v>
+        <v>461.7029918634157</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1126763259085291</v>
+        <v>0.1134032424944914</v>
       </c>
       <c r="T9">
-        <v>0.5728481441777665</v>
+        <v>0.5790747544405684</v>
       </c>
       <c r="U9">
-        <v>0.1047771881973717</v>
+        <v>0.1062771881973717</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.1047771881973717</v>
+        <v>0.1062771881973717</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.72789001267804</v>
+        <v>11.84236732578435</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1128331581507218</v>
+        <v>0.1134379300326956</v>
       </c>
       <c r="C10">
-        <v>3506.148508855165</v>
+        <v>3445.977626865137</v>
       </c>
       <c r="D10">
-        <v>3328.804508855165</v>
+        <v>3299.040626865137</v>
       </c>
       <c r="E10">
-        <v>-623.544</v>
+        <v>-593.1369999999999</v>
       </c>
       <c r="F10">
-        <v>243.256</v>
+        <v>273.663</v>
       </c>
       <c r="G10">
         <v>420.6</v>
@@ -2107,28 +2107,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M10">
-        <v>25.85256369213984</v>
+        <v>29.08413415365732</v>
       </c>
       <c r="N10">
-        <v>280.3029918634157</v>
+        <v>277.0714214018982</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>280.3029918634157</v>
+        <v>277.0714214018982</v>
       </c>
       <c r="Q10">
-        <v>461.7029918634157</v>
+        <v>458.4714214018983</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1134032424944914</v>
+        <v>0.1141461352691562</v>
       </c>
       <c r="T10">
-        <v>0.5790747544405684</v>
+        <v>0.5854382132805748</v>
       </c>
       <c r="U10">
         <v>0.1062771881973717</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.84236732578435</v>
+        <v>10.52654873403053</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1134379300326956</v>
+        <v>0.1142127019146693</v>
       </c>
       <c r="C11">
-        <v>3445.977626865137</v>
+        <v>3378.209086629931</v>
       </c>
       <c r="D11">
-        <v>3299.040626865137</v>
+        <v>3261.679086629932</v>
       </c>
       <c r="E11">
-        <v>-593.1369999999999</v>
+        <v>-562.73</v>
       </c>
       <c r="F11">
-        <v>273.663</v>
+        <v>304.0699999999999</v>
       </c>
       <c r="G11">
         <v>420.6</v>
@@ -2189,45 +2189,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M11">
-        <v>29.08413415365732</v>
+        <v>32.8326236151748</v>
       </c>
       <c r="N11">
-        <v>277.0714214018982</v>
+        <v>273.3229319403808</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>277.0714214018982</v>
+        <v>273.3229319403808</v>
       </c>
       <c r="Q11">
-        <v>458.4714214018983</v>
+        <v>454.7229319403808</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1141461352691562</v>
+        <v>0.1149055367721468</v>
       </c>
       <c r="T11">
-        <v>0.5854382132805748</v>
+        <v>0.5919430823170255</v>
       </c>
       <c r="U11">
-        <v>0.1062771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.1062771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.52654873403053</v>
+        <v>9.324736248432325</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1142127019146693</v>
+        <v>0.114834473796643</v>
       </c>
       <c r="C12">
-        <v>3378.209086629931</v>
+        <v>3318.425164745046</v>
       </c>
       <c r="D12">
-        <v>3261.679086629932</v>
+        <v>3232.302164745046</v>
       </c>
       <c r="E12">
-        <v>-562.73</v>
+        <v>-532.323</v>
       </c>
       <c r="F12">
-        <v>304.07</v>
+        <v>334.477</v>
       </c>
       <c r="G12">
         <v>420.6</v>
@@ -2271,28 +2271,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M12">
-        <v>32.8326236151748</v>
+        <v>36.11588597669228</v>
       </c>
       <c r="N12">
-        <v>273.3229319403808</v>
+        <v>270.0396695788633</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>273.3229319403808</v>
+        <v>270.0396695788633</v>
       </c>
       <c r="Q12">
-        <v>454.7229319403808</v>
+        <v>451.4396695788632</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1149055367721468</v>
+        <v>0.1156820034774518</v>
       </c>
       <c r="T12">
-        <v>0.5919430823170255</v>
+        <v>0.5985941281857562</v>
       </c>
       <c r="U12">
         <v>0.1079771881973717</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.324736248432323</v>
+        <v>8.477032953120293</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.114834473796643</v>
+        <v>0.1154562456786167</v>
       </c>
       <c r="C13">
-        <v>3318.425164745046</v>
+        <v>3259.165696735874</v>
       </c>
       <c r="D13">
-        <v>3232.302164745046</v>
+        <v>3203.449696735875</v>
       </c>
       <c r="E13">
-        <v>-532.323</v>
+        <v>-501.916</v>
       </c>
       <c r="F13">
-        <v>334.477</v>
+        <v>364.884</v>
       </c>
       <c r="G13">
         <v>420.6</v>
@@ -2353,28 +2353,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M13">
-        <v>36.11588597669228</v>
+        <v>39.39914833820976</v>
       </c>
       <c r="N13">
-        <v>270.0396695788633</v>
+        <v>266.7564072173458</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>270.0396695788633</v>
+        <v>266.7564072173458</v>
       </c>
       <c r="Q13">
-        <v>451.4396695788632</v>
+        <v>448.1564072173458</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1156820034774518</v>
+        <v>0.1164761171533319</v>
       </c>
       <c r="T13">
-        <v>0.5985941281857562</v>
+        <v>0.605396334187867</v>
       </c>
       <c r="U13">
         <v>0.1079771881973717</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.477032953120293</v>
+        <v>7.770613540360269</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1154562456786167</v>
+        <v>0.1161820175605904</v>
       </c>
       <c r="C14">
-        <v>3259.165696735874</v>
+        <v>3195.72506405823</v>
       </c>
       <c r="D14">
-        <v>3203.449696735875</v>
+        <v>3170.41606405823</v>
       </c>
       <c r="E14">
-        <v>-501.916</v>
+        <v>-471.509</v>
       </c>
       <c r="F14">
-        <v>364.884</v>
+        <v>395.291</v>
       </c>
       <c r="G14">
         <v>420.6</v>
@@ -2435,45 +2435,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M14">
-        <v>39.39914833820976</v>
+        <v>42.99864349972724</v>
       </c>
       <c r="N14">
-        <v>266.7564072173458</v>
+        <v>263.1569120558283</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>266.7564072173458</v>
+        <v>263.1569120558283</v>
       </c>
       <c r="Q14">
-        <v>448.1564072173458</v>
+        <v>444.5569120558283</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1164761171533319</v>
+        <v>0.1172884863160139</v>
       </c>
       <c r="T14">
-        <v>0.605396334187867</v>
+        <v>0.6123549127417505</v>
       </c>
       <c r="U14">
-        <v>0.1079771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.1079771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.770613540360269</v>
+        <v>7.120121255860028</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1161820175605904</v>
+        <v>0.1168117894425641</v>
       </c>
       <c r="C15">
-        <v>3195.72506405823</v>
+        <v>3137.201058319111</v>
       </c>
       <c r="D15">
-        <v>3170.41606405823</v>
+        <v>3142.299058319111</v>
       </c>
       <c r="E15">
-        <v>-471.509</v>
+        <v>-441.1019999999999</v>
       </c>
       <c r="F15">
-        <v>395.291</v>
+        <v>425.698</v>
       </c>
       <c r="G15">
         <v>420.6</v>
@@ -2517,28 +2517,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M15">
-        <v>42.99864349972724</v>
+        <v>46.30623146124473</v>
       </c>
       <c r="N15">
-        <v>263.1569120558283</v>
+        <v>259.8493240943108</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>263.1569120558283</v>
+        <v>259.8493240943108</v>
       </c>
       <c r="Q15">
-        <v>444.5569120558283</v>
+        <v>441.2493240943109</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1172884863160139</v>
+        <v>0.1181197477848047</v>
       </c>
       <c r="T15">
-        <v>0.6123549127417505</v>
+        <v>0.619475318703864</v>
       </c>
       <c r="U15">
         <v>0.1087771881973717</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.120121255860028</v>
+        <v>6.611541166155739</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1168117894425641</v>
+        <v>0.1174415613245378</v>
       </c>
       <c r="C16">
-        <v>3137.201058319111</v>
+        <v>3079.171382946121</v>
       </c>
       <c r="D16">
-        <v>3142.299058319111</v>
+        <v>3114.676382946121</v>
       </c>
       <c r="E16">
-        <v>-441.1019999999999</v>
+        <v>-410.6949999999999</v>
       </c>
       <c r="F16">
-        <v>425.698</v>
+        <v>456.105</v>
       </c>
       <c r="G16">
         <v>420.6</v>
@@ -2599,28 +2599,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M16">
-        <v>46.30623146124473</v>
+        <v>49.61381942276221</v>
       </c>
       <c r="N16">
-        <v>259.8493240943108</v>
+        <v>256.5417361327933</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>259.8493240943108</v>
+        <v>256.5417361327933</v>
       </c>
       <c r="Q16">
-        <v>441.2493240943109</v>
+        <v>437.9417361327934</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1181197477848047</v>
+        <v>0.1189705683469789</v>
       </c>
       <c r="T16">
-        <v>0.619475318703864</v>
+        <v>0.6267632636297917</v>
       </c>
       <c r="U16">
         <v>0.1087771881973717</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.611541166155739</v>
+        <v>6.17077175507869</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1174415613245378</v>
+        <v>0.1182313332065116</v>
       </c>
       <c r="C17">
-        <v>3079.171382946121</v>
+        <v>3014.802784839332</v>
       </c>
       <c r="D17">
-        <v>3114.676382946121</v>
+        <v>3080.714784839332</v>
       </c>
       <c r="E17">
-        <v>-410.695</v>
+        <v>-380.288</v>
       </c>
       <c r="F17">
-        <v>456.105</v>
+        <v>486.512</v>
       </c>
       <c r="G17">
         <v>420.6</v>
@@ -2681,45 +2681,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M17">
-        <v>49.61381942276221</v>
+        <v>53.40791938427969</v>
       </c>
       <c r="N17">
-        <v>256.5417361327933</v>
+        <v>252.7476361712759</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>256.5417361327933</v>
+        <v>252.7476361712759</v>
       </c>
       <c r="Q17">
-        <v>437.9417361327934</v>
+        <v>434.1476361712758</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1189705683469789</v>
+        <v>0.1198416465415858</v>
       </c>
       <c r="T17">
-        <v>0.6267632636297917</v>
+        <v>0.6342247310539559</v>
       </c>
       <c r="U17">
-        <v>0.1087771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.1087771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.17077175507869</v>
+        <v>5.732399971485703</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1182313332065116</v>
+        <v>0.1188711050884853</v>
       </c>
       <c r="C18">
-        <v>3014.802784839332</v>
+        <v>2957.422678392753</v>
       </c>
       <c r="D18">
-        <v>3080.714784839332</v>
+        <v>3053.741678392753</v>
       </c>
       <c r="E18">
-        <v>-380.288</v>
+        <v>-349.881</v>
       </c>
       <c r="F18">
-        <v>486.512</v>
+        <v>516.919</v>
       </c>
       <c r="G18">
         <v>420.6</v>
@@ -2763,28 +2763,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M18">
-        <v>53.40791938427969</v>
+        <v>56.74591434579717</v>
       </c>
       <c r="N18">
-        <v>252.7476361712759</v>
+        <v>249.4096412097584</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>252.7476361712759</v>
+        <v>249.4096412097584</v>
       </c>
       <c r="Q18">
-        <v>434.1476361712758</v>
+        <v>430.8096412097584</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1198416465415858</v>
+        <v>0.1207337145722073</v>
       </c>
       <c r="T18">
-        <v>0.6342247310539559</v>
+        <v>0.6418659928738831</v>
       </c>
       <c r="U18">
         <v>0.1097771881973717</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.732399971485703</v>
+        <v>5.395199973163014</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1188711050884853</v>
+        <v>0.119510876970459</v>
       </c>
       <c r="C19">
-        <v>2957.422678392753</v>
+        <v>2900.510796875336</v>
       </c>
       <c r="D19">
-        <v>3053.741678392753</v>
+        <v>3027.236796875336</v>
       </c>
       <c r="E19">
-        <v>-349.881</v>
+        <v>-319.4739999999999</v>
       </c>
       <c r="F19">
-        <v>516.919</v>
+        <v>547.326</v>
       </c>
       <c r="G19">
         <v>420.6</v>
@@ -2845,28 +2845,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M19">
-        <v>56.74591434579717</v>
+        <v>60.08390930731465</v>
       </c>
       <c r="N19">
-        <v>249.4096412097584</v>
+        <v>246.0716462482409</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>249.4096412097584</v>
+        <v>246.0716462482409</v>
       </c>
       <c r="Q19">
-        <v>430.8096412097584</v>
+        <v>427.4716462482409</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1207337145722073</v>
+        <v>0.1216475403596733</v>
       </c>
       <c r="T19">
-        <v>0.6418659928738831</v>
+        <v>0.6496936269333207</v>
       </c>
       <c r="U19">
         <v>0.1097771881973717</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.395199973163014</v>
+        <v>5.095466641320624</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.119510876970459</v>
+        <v>0.1201506488524327</v>
       </c>
       <c r="C20">
-        <v>2900.510796875336</v>
+        <v>2844.055053352452</v>
       </c>
       <c r="D20">
-        <v>3027.236796875336</v>
+        <v>3001.188053352452</v>
       </c>
       <c r="E20">
-        <v>-319.474</v>
+        <v>-289.067</v>
       </c>
       <c r="F20">
-        <v>547.3259999999999</v>
+        <v>577.7329999999999</v>
       </c>
       <c r="G20">
         <v>420.6</v>
@@ -2927,28 +2927,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M20">
-        <v>60.08390930731463</v>
+        <v>63.42190426883212</v>
       </c>
       <c r="N20">
-        <v>246.0716462482409</v>
+        <v>242.7336512867234</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>246.0716462482409</v>
+        <v>242.7336512867234</v>
       </c>
       <c r="Q20">
-        <v>427.471646248241</v>
+        <v>424.1336512867234</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1216475403596733</v>
+        <v>0.1225839297468297</v>
       </c>
       <c r="T20">
-        <v>0.6496936269333207</v>
+        <v>0.657714535907806</v>
       </c>
       <c r="U20">
         <v>0.1097771881973717</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.095466641320625</v>
+        <v>4.827284186514277</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1201506488524327</v>
+        <v>0.1207904207344064</v>
       </c>
       <c r="C21">
-        <v>2844.055053352452</v>
+        <v>2788.043773362469</v>
       </c>
       <c r="D21">
-        <v>3001.188053352452</v>
+        <v>2975.583773362468</v>
       </c>
       <c r="E21">
-        <v>-289.067</v>
+        <v>-258.66</v>
       </c>
       <c r="F21">
-        <v>577.7329999999999</v>
+        <v>608.14</v>
       </c>
       <c r="G21">
         <v>420.6</v>
@@ -3009,28 +3009,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M21">
-        <v>63.42190426883212</v>
+        <v>66.7598992303496</v>
       </c>
       <c r="N21">
-        <v>242.7336512867234</v>
+        <v>239.3956563252059</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>242.7336512867234</v>
+        <v>239.3956563252059</v>
       </c>
       <c r="Q21">
-        <v>424.1336512867234</v>
+        <v>420.795656325206</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1225839297468297</v>
+        <v>0.1235437288686651</v>
       </c>
       <c r="T21">
-        <v>0.657714535907806</v>
+        <v>0.6659359676066536</v>
       </c>
       <c r="U21">
         <v>0.1097771881973717</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.827284186514277</v>
+        <v>4.585919977188562</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1207904207344064</v>
+        <v>0.1219551926163801</v>
       </c>
       <c r="C22">
-        <v>2788.043773362469</v>
+        <v>2712.126070906123</v>
       </c>
       <c r="D22">
-        <v>2975.583773362468</v>
+        <v>2930.073070906123</v>
       </c>
       <c r="E22">
-        <v>-258.66</v>
+        <v>-228.2529999999999</v>
       </c>
       <c r="F22">
-        <v>608.14</v>
+        <v>638.547</v>
       </c>
       <c r="G22">
         <v>420.6</v>
@@ -3091,45 +3091,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M22">
-        <v>66.7598992303496</v>
+        <v>71.6942616918671</v>
       </c>
       <c r="N22">
-        <v>239.3956563252059</v>
+        <v>234.4612938636885</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>239.3956563252059</v>
+        <v>234.4612938636885</v>
       </c>
       <c r="Q22">
-        <v>420.795656325206</v>
+        <v>415.8612938636885</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1235437288686651</v>
+        <v>0.1245278267024457</v>
       </c>
       <c r="T22">
-        <v>0.6659359676066536</v>
+        <v>0.6743655368168645</v>
       </c>
       <c r="U22">
-        <v>0.1097771881973717</v>
+        <v>0.1122771881973717</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.1097771881973717</v>
+        <v>0.1122771881973717</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.585919977188562</v>
+        <v>4.270293721293534</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1219551926163801</v>
+        <v>0.1226199644983538</v>
       </c>
       <c r="C23">
-        <v>2712.126070906123</v>
+        <v>2656.363289991794</v>
       </c>
       <c r="D23">
-        <v>2930.073070906123</v>
+        <v>2904.717289991794</v>
       </c>
       <c r="E23">
-        <v>-228.253</v>
+        <v>-197.846</v>
       </c>
       <c r="F23">
-        <v>638.5469999999999</v>
+        <v>668.954</v>
       </c>
       <c r="G23">
         <v>420.6</v>
@@ -3173,28 +3173,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M23">
-        <v>71.69426169186708</v>
+        <v>75.10827415338457</v>
       </c>
       <c r="N23">
-        <v>234.4612938636885</v>
+        <v>231.047281402171</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>234.4612938636885</v>
+        <v>231.047281402171</v>
       </c>
       <c r="Q23">
-        <v>415.8612938636885</v>
+        <v>412.447281402171</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1245278267024457</v>
+        <v>0.1255371578140155</v>
       </c>
       <c r="T23">
-        <v>0.6743655368168645</v>
+        <v>0.6830112488273371</v>
       </c>
       <c r="U23">
         <v>0.1122771881973717</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.270293721293534</v>
+        <v>4.076189461234737</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1226199644983538</v>
+        <v>0.1240897363803276</v>
       </c>
       <c r="C24">
-        <v>2656.363289991794</v>
+        <v>2571.424597904175</v>
       </c>
       <c r="D24">
-        <v>2904.717289991794</v>
+        <v>2850.185597904175</v>
       </c>
       <c r="E24">
-        <v>-197.846</v>
+        <v>-167.439</v>
       </c>
       <c r="F24">
-        <v>668.954</v>
+        <v>699.361</v>
       </c>
       <c r="G24">
         <v>420.6</v>
@@ -3255,45 +3255,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M24">
-        <v>75.10827415338457</v>
+        <v>80.97005011490205</v>
       </c>
       <c r="N24">
-        <v>231.047281402171</v>
+        <v>225.1855054406535</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>231.047281402171</v>
+        <v>225.1855054406535</v>
       </c>
       <c r="Q24">
-        <v>412.447281402171</v>
+        <v>406.5855054406535</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1255371578140155</v>
+        <v>0.1265727053180936</v>
       </c>
       <c r="T24">
-        <v>0.6830112488273371</v>
+        <v>0.6918815247861337</v>
       </c>
       <c r="U24">
-        <v>0.1122771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.1122771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.076189461234737</v>
+        <v>3.781096283392438</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1240897363803276</v>
+        <v>0.1247895082623013</v>
       </c>
       <c r="C25">
-        <v>2571.424597904175</v>
+        <v>2515.767665556239</v>
       </c>
       <c r="D25">
-        <v>2850.185597904175</v>
+        <v>2824.935665556239</v>
       </c>
       <c r="E25">
-        <v>-167.439</v>
+        <v>-137.0319999999999</v>
       </c>
       <c r="F25">
-        <v>699.361</v>
+        <v>729.768</v>
       </c>
       <c r="G25">
         <v>420.6</v>
@@ -3337,28 +3337,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M25">
-        <v>80.97005011490205</v>
+        <v>84.49048707641954</v>
       </c>
       <c r="N25">
-        <v>225.1855054406535</v>
+        <v>221.665068479136</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>225.1855054406535</v>
+        <v>221.665068479136</v>
       </c>
       <c r="Q25">
-        <v>406.5855054406535</v>
+        <v>403.065068479136</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1265727053180936</v>
+        <v>0.1276355040722791</v>
       </c>
       <c r="T25">
-        <v>0.6918815247861337</v>
+        <v>0.7009852290596356</v>
       </c>
       <c r="U25">
         <v>0.1157771881973717</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.781096283392438</v>
+        <v>3.623550604917753</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1247895082623013</v>
+        <v>0.126189280144275</v>
       </c>
       <c r="C26">
-        <v>2515.767665556239</v>
+        <v>2436.171700237313</v>
       </c>
       <c r="D26">
-        <v>2824.935665556239</v>
+        <v>2775.746700237312</v>
       </c>
       <c r="E26">
-        <v>-137.032</v>
+        <v>-106.625</v>
       </c>
       <c r="F26">
-        <v>729.7679999999999</v>
+        <v>760.175</v>
       </c>
       <c r="G26">
         <v>420.6</v>
@@ -3419,45 +3419,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M26">
-        <v>84.49048707641953</v>
+        <v>90.139414037937</v>
       </c>
       <c r="N26">
-        <v>221.665068479136</v>
+        <v>216.0161415176186</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>221.665068479136</v>
+        <v>216.0161415176186</v>
       </c>
       <c r="Q26">
-        <v>403.065068479136</v>
+        <v>397.4161415176186</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1276355040722791</v>
+        <v>0.1287266441265761</v>
       </c>
       <c r="T26">
-        <v>0.7009852290596356</v>
+        <v>0.7103316987804306</v>
       </c>
       <c r="U26">
-        <v>0.1157771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.1157771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.623550604917753</v>
+        <v>3.396467115114636</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.126189280144275</v>
+        <v>0.1269170520262487</v>
       </c>
       <c r="C27">
-        <v>2436.171700237313</v>
+        <v>2380.8610536001</v>
       </c>
       <c r="D27">
-        <v>2775.746700237312</v>
+        <v>2750.8430536001</v>
       </c>
       <c r="E27">
-        <v>-106.625</v>
+        <v>-76.21799999999996</v>
       </c>
       <c r="F27">
-        <v>760.175</v>
+        <v>790.582</v>
       </c>
       <c r="G27">
         <v>420.6</v>
@@ -3501,28 +3501,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M27">
-        <v>90.139414037937</v>
+        <v>93.7449905994545</v>
       </c>
       <c r="N27">
-        <v>216.0161415176186</v>
+        <v>212.4105649561011</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>216.0161415176186</v>
+        <v>212.4105649561011</v>
       </c>
       <c r="Q27">
-        <v>397.4161415176186</v>
+        <v>393.8105649561011</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1287266441265761</v>
+        <v>0.1298472744526109</v>
       </c>
       <c r="T27">
-        <v>0.7103316987804306</v>
+        <v>0.719930775790977</v>
       </c>
       <c r="U27">
         <v>0.1185771881973717</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.396467115114636</v>
+        <v>3.265833764533303</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1269170520262487</v>
+        <v>0.1276448239082225</v>
       </c>
       <c r="C28">
-        <v>2380.8610536001</v>
+        <v>2325.993298105313</v>
       </c>
       <c r="D28">
-        <v>2750.8430536001</v>
+        <v>2726.382298105313</v>
       </c>
       <c r="E28">
-        <v>-76.21799999999996</v>
+        <v>-45.81099999999992</v>
       </c>
       <c r="F28">
-        <v>790.582</v>
+        <v>820.989</v>
       </c>
       <c r="G28">
         <v>420.6</v>
@@ -3583,28 +3583,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M28">
-        <v>93.7449905994545</v>
+        <v>97.35056716097198</v>
       </c>
       <c r="N28">
-        <v>212.4105649561011</v>
+        <v>208.8049883945836</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>212.4105649561011</v>
+        <v>208.8049883945836</v>
       </c>
       <c r="Q28">
-        <v>393.8105649561011</v>
+        <v>390.2049883945836</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1298472744526109</v>
+        <v>0.130998606979359</v>
       </c>
       <c r="T28">
-        <v>0.719930775790977</v>
+        <v>0.7297928412127712</v>
       </c>
       <c r="U28">
         <v>0.1185771881973717</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.265833764533303</v>
+        <v>3.144876958439477</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1276448239082225</v>
+        <v>0.1283725957901962</v>
       </c>
       <c r="C29">
-        <v>2325.993298105313</v>
+        <v>2271.556723195092</v>
       </c>
       <c r="D29">
-        <v>2726.382298105313</v>
+        <v>2702.352723195092</v>
       </c>
       <c r="E29">
-        <v>-45.81099999999992</v>
+        <v>-15.40399999999988</v>
       </c>
       <c r="F29">
-        <v>820.989</v>
+        <v>851.3960000000001</v>
       </c>
       <c r="G29">
         <v>420.6</v>
@@ -3665,28 +3665,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M29">
-        <v>97.35056716097198</v>
+        <v>100.9561437224895</v>
       </c>
       <c r="N29">
-        <v>208.8049883945836</v>
+        <v>205.1994118330661</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>208.8049883945836</v>
+        <v>205.1994118330661</v>
       </c>
       <c r="Q29">
-        <v>390.2049883945836</v>
+        <v>386.5994118330661</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.130998606979359</v>
+        <v>0.1321819209651834</v>
       </c>
       <c r="T29">
-        <v>0.7297928412127712</v>
+        <v>0.7399288528962819</v>
       </c>
       <c r="U29">
         <v>0.1185771881973717</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.144876958439477</v>
+        <v>3.032559924209496</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1283725957901962</v>
+        <v>0.1313623676721699</v>
       </c>
       <c r="C30">
-        <v>2271.556723195092</v>
+        <v>2146.722483664509</v>
       </c>
       <c r="D30">
-        <v>2702.352723195092</v>
+        <v>2607.925483664509</v>
       </c>
       <c r="E30">
-        <v>-15.40399999999988</v>
+        <v>15.00300000000016</v>
       </c>
       <c r="F30">
-        <v>851.3960000000001</v>
+        <v>881.8030000000001</v>
       </c>
       <c r="G30">
         <v>420.6</v>
@@ -3747,45 +3747,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M30">
-        <v>100.9561437224895</v>
+        <v>111.439783684007</v>
       </c>
       <c r="N30">
-        <v>205.1994118330661</v>
+        <v>194.7157718715486</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>205.1994118330661</v>
+        <v>194.7157718715486</v>
       </c>
       <c r="Q30">
-        <v>386.5994118330661</v>
+        <v>376.1157718715486</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1321819209651834</v>
+        <v>0.133398567739341</v>
       </c>
       <c r="T30">
-        <v>0.7399288528962819</v>
+        <v>0.7503503860356662</v>
       </c>
       <c r="U30">
-        <v>0.1185771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.1185771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.032559924209496</v>
+        <v>2.747273419191793</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1313623676721699</v>
+        <v>0.1321681395541436</v>
       </c>
       <c r="C31">
-        <v>2146.72248366451</v>
+        <v>2091.984833081232</v>
       </c>
       <c r="D31">
-        <v>2607.92548366451</v>
+        <v>2583.594833081233</v>
       </c>
       <c r="E31">
-        <v>15.00299999999993</v>
+        <v>45.40999999999997</v>
       </c>
       <c r="F31">
-        <v>881.8029999999999</v>
+        <v>912.2099999999999</v>
       </c>
       <c r="G31">
         <v>420.6</v>
@@ -3829,28 +3829,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M31">
-        <v>111.4397836840069</v>
+        <v>115.2825348455244</v>
       </c>
       <c r="N31">
-        <v>194.7157718715486</v>
+        <v>190.8730207100311</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>194.7157718715486</v>
+        <v>190.8730207100311</v>
       </c>
       <c r="Q31">
-        <v>376.1157718715486</v>
+        <v>372.2730207100311</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1333985677393409</v>
+        <v>0.134649975849903</v>
       </c>
       <c r="T31">
-        <v>0.7503503860356661</v>
+        <v>0.7610696772647471</v>
       </c>
       <c r="U31">
         <v>0.1263771881973717</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.747273419191794</v>
+        <v>2.655697638552067</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1321681395541436</v>
+        <v>0.1329739114361173</v>
       </c>
       <c r="C32">
-        <v>2091.984833081232</v>
+        <v>2037.696971977105</v>
       </c>
       <c r="D32">
-        <v>2583.594833081233</v>
+        <v>2559.713971977105</v>
       </c>
       <c r="E32">
-        <v>45.40999999999997</v>
+        <v>75.81700000000001</v>
       </c>
       <c r="F32">
-        <v>912.2099999999999</v>
+        <v>942.617</v>
       </c>
       <c r="G32">
         <v>420.6</v>
@@ -3911,28 +3911,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M32">
-        <v>115.2825348455244</v>
+        <v>119.1252860070419</v>
       </c>
       <c r="N32">
-        <v>190.8730207100311</v>
+        <v>187.0302695485137</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>190.8730207100311</v>
+        <v>187.0302695485137</v>
       </c>
       <c r="Q32">
-        <v>372.2730207100311</v>
+        <v>368.4302695485137</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.134649975849903</v>
+        <v>0.1359376566593219</v>
       </c>
       <c r="T32">
-        <v>0.7610696772647471</v>
+        <v>0.7720996725874245</v>
       </c>
       <c r="U32">
         <v>0.1263771881973717</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.655697638552067</v>
+        <v>2.570029972792323</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1329739114361173</v>
+        <v>0.135027683318091</v>
       </c>
       <c r="C33">
-        <v>2037.696971977105</v>
+        <v>1948.372510646177</v>
       </c>
       <c r="D33">
-        <v>2559.713971977105</v>
+        <v>2500.796510646177</v>
       </c>
       <c r="E33">
-        <v>75.81700000000001</v>
+        <v>106.224</v>
       </c>
       <c r="F33">
-        <v>942.617</v>
+        <v>973.024</v>
       </c>
       <c r="G33">
         <v>420.6</v>
@@ -3993,45 +3993,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M33">
-        <v>119.1252860070419</v>
+        <v>126.7628307685594</v>
       </c>
       <c r="N33">
-        <v>187.0302695485137</v>
+        <v>179.3927247869962</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>187.0302695485137</v>
+        <v>179.3927247869962</v>
       </c>
       <c r="Q33">
-        <v>368.4302695485137</v>
+        <v>360.7927247869961</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1359376566593219</v>
+        <v>0.1372632104337237</v>
       </c>
       <c r="T33">
-        <v>0.7720996725874245</v>
+        <v>0.7834540795372397</v>
       </c>
       <c r="U33">
-        <v>0.1263771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.1263771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.570029972792323</v>
+        <v>2.415183959677638</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.135027683318091</v>
+        <v>0.1358724552000647</v>
       </c>
       <c r="C34">
-        <v>1948.372510646177</v>
+        <v>1894.51103091606</v>
       </c>
       <c r="D34">
-        <v>2500.796510646177</v>
+        <v>2477.34203091606</v>
       </c>
       <c r="E34">
-        <v>106.224</v>
+        <v>136.6310000000001</v>
       </c>
       <c r="F34">
-        <v>973.024</v>
+        <v>1003.431</v>
       </c>
       <c r="G34">
         <v>420.6</v>
@@ -4075,28 +4075,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M34">
-        <v>126.7628307685594</v>
+        <v>130.7241692300769</v>
       </c>
       <c r="N34">
-        <v>179.3927247869962</v>
+        <v>175.4313863254787</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>179.3927247869962</v>
+        <v>175.4313863254787</v>
       </c>
       <c r="Q34">
-        <v>360.7927247869961</v>
+        <v>356.8313863254787</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1372632104337237</v>
+        <v>0.1386283329775106</v>
       </c>
       <c r="T34">
-        <v>0.7834540795372397</v>
+        <v>0.7951474240079448</v>
       </c>
       <c r="U34">
         <v>0.1302771881973717</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.415183959677638</v>
+        <v>2.341996566960133</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1358724552000647</v>
+        <v>0.1367172270820385</v>
       </c>
       <c r="C35">
-        <v>1894.51103091606</v>
+        <v>1841.085413246813</v>
       </c>
       <c r="D35">
-        <v>2477.34203091606</v>
+        <v>2454.323413246813</v>
       </c>
       <c r="E35">
-        <v>136.6310000000001</v>
+        <v>167.038</v>
       </c>
       <c r="F35">
-        <v>1003.431</v>
+        <v>1033.838</v>
       </c>
       <c r="G35">
         <v>420.6</v>
@@ -4157,28 +4157,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M35">
-        <v>130.7241692300769</v>
+        <v>134.6855076915944</v>
       </c>
       <c r="N35">
-        <v>175.4313863254787</v>
+        <v>171.4700478639612</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>175.4313863254787</v>
+        <v>171.4700478639612</v>
       </c>
       <c r="Q35">
-        <v>356.8313863254787</v>
+        <v>352.8700478639612</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1386283329775106</v>
+        <v>0.1400348228711092</v>
       </c>
       <c r="T35">
-        <v>0.7951474240079448</v>
+        <v>0.8071951122504893</v>
       </c>
       <c r="U35">
         <v>0.1302771881973717</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.341996566960133</v>
+        <v>2.273114314990718</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1367172270820385</v>
+        <v>0.1375619989640122</v>
       </c>
       <c r="C36">
-        <v>1841.085413246813</v>
+        <v>1788.083619844439</v>
       </c>
       <c r="D36">
-        <v>2454.323413246813</v>
+        <v>2431.728619844439</v>
       </c>
       <c r="E36">
-        <v>167.038</v>
+        <v>197.4450000000002</v>
       </c>
       <c r="F36">
-        <v>1033.838</v>
+        <v>1064.245</v>
       </c>
       <c r="G36">
         <v>420.6</v>
@@ -4239,28 +4239,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M36">
-        <v>134.6855076915944</v>
+        <v>138.6468461531119</v>
       </c>
       <c r="N36">
-        <v>171.4700478639612</v>
+        <v>167.5087094024437</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>171.4700478639612</v>
+        <v>167.5087094024437</v>
       </c>
       <c r="Q36">
-        <v>352.8700478639612</v>
+        <v>348.9087094024437</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1400348228711092</v>
+        <v>0.1414845893768186</v>
       </c>
       <c r="T36">
-        <v>0.8071951122504893</v>
+        <v>0.8196134985928046</v>
       </c>
       <c r="U36">
         <v>0.1302771881973717</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.273114314990718</v>
+        <v>2.208168191705268</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1375619989640122</v>
+        <v>0.1384067708459859</v>
       </c>
       <c r="C37">
-        <v>1788.083619844439</v>
+        <v>1735.494052156686</v>
       </c>
       <c r="D37">
-        <v>2431.728619844439</v>
+        <v>2409.546052156687</v>
       </c>
       <c r="E37">
-        <v>197.4450000000002</v>
+        <v>227.8520000000001</v>
       </c>
       <c r="F37">
-        <v>1064.245</v>
+        <v>1094.652</v>
       </c>
       <c r="G37">
         <v>420.6</v>
@@ -4321,28 +4321,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M37">
-        <v>138.6468461531119</v>
+        <v>142.6081846146293</v>
       </c>
       <c r="N37">
-        <v>167.5087094024437</v>
+        <v>163.5473709409262</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>167.5087094024437</v>
+        <v>163.5473709409262</v>
       </c>
       <c r="Q37">
-        <v>348.9087094024437</v>
+        <v>344.9473709409262</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1414845893768186</v>
+        <v>0.1429796610858314</v>
       </c>
       <c r="T37">
-        <v>0.8196134985928046</v>
+        <v>0.8324199595083172</v>
       </c>
       <c r="U37">
         <v>0.1302771881973717</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.208168191705268</v>
+        <v>2.146830186380122</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1384067708459859</v>
+        <v>0.1392515427279596</v>
       </c>
       <c r="C38">
-        <v>1735.494052156686</v>
+        <v>1683.305531020024</v>
       </c>
       <c r="D38">
-        <v>2409.546052156686</v>
+        <v>2387.764531020024</v>
       </c>
       <c r="E38">
-        <v>227.8519999999999</v>
+        <v>258.259</v>
       </c>
       <c r="F38">
-        <v>1094.652</v>
+        <v>1125.059</v>
       </c>
       <c r="G38">
         <v>420.6</v>
@@ -4403,28 +4403,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M38">
-        <v>142.6081846146293</v>
+        <v>146.5695230761468</v>
       </c>
       <c r="N38">
-        <v>163.5473709409263</v>
+        <v>159.5860324794088</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>163.5473709409263</v>
+        <v>159.5860324794088</v>
       </c>
       <c r="Q38">
-        <v>344.9473709409262</v>
+        <v>340.9860324794088</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1429796610858314</v>
+        <v>0.1445221953887811</v>
       </c>
       <c r="T38">
-        <v>0.8324199595083172</v>
+        <v>0.8456329747386079</v>
       </c>
       <c r="U38">
         <v>0.1302771881973717</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.146830186380122</v>
+        <v>2.08880774891039</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1392515427279596</v>
+        <v>0.1400963146099333</v>
       </c>
       <c r="C39">
-        <v>1683.305531020024</v>
+        <v>1631.50727787377</v>
       </c>
       <c r="D39">
-        <v>2387.764531020024</v>
+        <v>2366.37327787377</v>
       </c>
       <c r="E39">
-        <v>258.259</v>
+        <v>288.6659999999999</v>
       </c>
       <c r="F39">
-        <v>1125.059</v>
+        <v>1155.466</v>
       </c>
       <c r="G39">
         <v>420.6</v>
@@ -4485,28 +4485,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M39">
-        <v>146.5695230761468</v>
+        <v>150.5308615376643</v>
       </c>
       <c r="N39">
-        <v>159.5860324794088</v>
+        <v>155.6246940178913</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>159.5860324794088</v>
+        <v>155.6246940178913</v>
       </c>
       <c r="Q39">
-        <v>340.9860324794088</v>
+        <v>337.0246940178913</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1445221953887811</v>
+        <v>0.1461144888627937</v>
       </c>
       <c r="T39">
-        <v>0.8456329747386079</v>
+        <v>0.8592722162666498</v>
       </c>
       <c r="U39">
         <v>0.1302771881973717</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.08880774891039</v>
+        <v>2.033839123939064</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1400963146099333</v>
+        <v>0.146479086491907</v>
       </c>
       <c r="C40">
-        <v>1631.50727787377</v>
+        <v>1451.078844957007</v>
       </c>
       <c r="D40">
-        <v>2366.37327787377</v>
+        <v>2216.351844957007</v>
       </c>
       <c r="E40">
-        <v>288.6659999999999</v>
+        <v>319.0730000000001</v>
       </c>
       <c r="F40">
-        <v>1155.466</v>
+        <v>1185.873</v>
       </c>
       <c r="G40">
         <v>420.6</v>
@@ -4567,45 +4567,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M40">
-        <v>150.5308615376643</v>
+        <v>171.3315965991818</v>
       </c>
       <c r="N40">
-        <v>155.6246940178913</v>
+        <v>134.8239589563738</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>155.6246940178913</v>
+        <v>134.8239589563738</v>
       </c>
       <c r="Q40">
-        <v>337.0246940178913</v>
+        <v>316.2239589563738</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1461144888627937</v>
+        <v>0.1477589886802165</v>
       </c>
       <c r="T40">
-        <v>0.8592722162666498</v>
+        <v>0.873358646041513</v>
       </c>
       <c r="U40">
-        <v>0.1302771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.1302771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.033839123939064</v>
+        <v>1.786918242942573</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.146479086491907</v>
+        <v>0.1474658583738808</v>
       </c>
       <c r="C41">
-        <v>1451.078844957007</v>
+        <v>1399.159867227755</v>
       </c>
       <c r="D41">
-        <v>2216.351844957007</v>
+        <v>2194.839867227755</v>
       </c>
       <c r="E41">
-        <v>319.0730000000001</v>
+        <v>349.48</v>
       </c>
       <c r="F41">
-        <v>1185.873</v>
+        <v>1216.28</v>
       </c>
       <c r="G41">
         <v>420.6</v>
@@ -4649,28 +4649,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M41">
-        <v>171.3315965991818</v>
+        <v>175.7247144606992</v>
       </c>
       <c r="N41">
-        <v>134.8239589563738</v>
+        <v>130.4308410948563</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>134.8239589563738</v>
+        <v>130.4308410948563</v>
       </c>
       <c r="Q41">
-        <v>316.2239589563738</v>
+        <v>311.8308410948563</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1477589886802165</v>
+        <v>0.1494583051582201</v>
       </c>
       <c r="T41">
-        <v>0.873358646041513</v>
+        <v>0.8879146234755383</v>
       </c>
       <c r="U41">
         <v>0.1444771881973717</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.786918242942573</v>
+        <v>1.742245286869009</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1474658583738808</v>
+        <v>0.1484526302558545</v>
       </c>
       <c r="C42">
-        <v>1399.159867227755</v>
+        <v>1347.654467108663</v>
       </c>
       <c r="D42">
-        <v>2194.839867227755</v>
+        <v>2173.741467108663</v>
       </c>
       <c r="E42">
-        <v>349.48</v>
+        <v>379.8870000000002</v>
       </c>
       <c r="F42">
-        <v>1216.28</v>
+        <v>1246.687</v>
       </c>
       <c r="G42">
         <v>420.6</v>
@@ -4731,28 +4731,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M42">
-        <v>175.7247144606992</v>
+        <v>180.1178323222167</v>
       </c>
       <c r="N42">
-        <v>130.4308410948563</v>
+        <v>126.0377232333389</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>130.4308410948563</v>
+        <v>126.0377232333389</v>
       </c>
       <c r="Q42">
-        <v>311.8308410948563</v>
+        <v>307.4377232333388</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1494583051582201</v>
+        <v>0.1512152255846306</v>
       </c>
       <c r="T42">
-        <v>0.8879146234755383</v>
+        <v>0.9029640238734287</v>
       </c>
       <c r="U42">
         <v>0.1444771881973717</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.742245286869009</v>
+        <v>1.699751499384399</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1484526302558545</v>
+        <v>0.1494394021378282</v>
       </c>
       <c r="C43">
-        <v>1347.654467108663</v>
+        <v>1296.550831329439</v>
       </c>
       <c r="D43">
-        <v>2173.741467108663</v>
+        <v>2153.044831329439</v>
       </c>
       <c r="E43">
-        <v>379.8870000000002</v>
+        <v>410.2940000000001</v>
       </c>
       <c r="F43">
-        <v>1246.687</v>
+        <v>1277.094</v>
       </c>
       <c r="G43">
         <v>420.6</v>
@@ -4813,28 +4813,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M43">
-        <v>180.1178323222167</v>
+        <v>184.5109501837342</v>
       </c>
       <c r="N43">
-        <v>126.0377232333389</v>
+        <v>121.6446053718214</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>126.0377232333389</v>
+        <v>121.6446053718214</v>
       </c>
       <c r="Q43">
-        <v>307.4377232333388</v>
+        <v>303.0446053718214</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1512152255846306</v>
+        <v>0.1530327294740208</v>
       </c>
       <c r="T43">
-        <v>0.9029640238734287</v>
+        <v>0.9185323691126258</v>
       </c>
       <c r="U43">
         <v>0.1444771881973717</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.699751499384399</v>
+        <v>1.659281225589532</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1494394021378282</v>
+        <v>0.1504261740198019</v>
       </c>
       <c r="C44">
-        <v>1296.550831329439</v>
+        <v>1245.837592282768</v>
       </c>
       <c r="D44">
-        <v>2153.044831329439</v>
+        <v>2132.738592282768</v>
       </c>
       <c r="E44">
-        <v>410.2939999999999</v>
+        <v>440.701</v>
       </c>
       <c r="F44">
-        <v>1277.094</v>
+        <v>1307.501</v>
       </c>
       <c r="G44">
         <v>420.6</v>
@@ -4895,28 +4895,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M44">
-        <v>184.5109501837342</v>
+        <v>188.9040680452517</v>
       </c>
       <c r="N44">
-        <v>121.6446053718214</v>
+        <v>117.2514875103039</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>121.6446053718214</v>
+        <v>117.2514875103039</v>
       </c>
       <c r="Q44">
-        <v>303.0446053718214</v>
+        <v>298.6514875103039</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1530327294740208</v>
+        <v>0.1549140054297054</v>
       </c>
       <c r="T44">
-        <v>0.9185323691126257</v>
+        <v>0.9346469720795139</v>
       </c>
       <c r="U44">
         <v>0.1444771881973717</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.659281225589532</v>
+        <v>1.620693290110706</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1504261740198019</v>
+        <v>0.1514129459017756</v>
       </c>
       <c r="C45">
-        <v>1245.837592282768</v>
+        <v>1195.503807204524</v>
       </c>
       <c r="D45">
-        <v>2132.738592282768</v>
+        <v>2112.811807204524</v>
       </c>
       <c r="E45">
-        <v>440.701</v>
+        <v>471.1079999999999</v>
       </c>
       <c r="F45">
-        <v>1307.501</v>
+        <v>1337.908</v>
       </c>
       <c r="G45">
         <v>420.6</v>
@@ -4977,28 +4977,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M45">
-        <v>188.9040680452517</v>
+        <v>193.2971859067691</v>
       </c>
       <c r="N45">
-        <v>117.2514875103039</v>
+        <v>112.8583696487864</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>117.2514875103039</v>
+        <v>112.8583696487864</v>
       </c>
       <c r="Q45">
-        <v>298.6514875103039</v>
+        <v>294.2583696487865</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1549140054297054</v>
+        <v>0.1568624698123787</v>
       </c>
       <c r="T45">
-        <v>0.9346469720795139</v>
+        <v>0.9513370965809338</v>
       </c>
       <c r="U45">
         <v>0.1444771881973717</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.620693290110706</v>
+        <v>1.583859351699099</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1514129459017756</v>
+        <v>0.1523997177837493</v>
       </c>
       <c r="C46">
-        <v>1195.503807204524</v>
+        <v>1145.538938510342</v>
       </c>
       <c r="D46">
-        <v>2112.811807204524</v>
+        <v>2093.253938510342</v>
       </c>
       <c r="E46">
-        <v>471.1079999999999</v>
+        <v>501.5150000000001</v>
       </c>
       <c r="F46">
-        <v>1337.908</v>
+        <v>1368.315</v>
       </c>
       <c r="G46">
         <v>420.6</v>
@@ -5059,28 +5059,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M46">
-        <v>193.2971859067691</v>
+        <v>197.6903037682866</v>
       </c>
       <c r="N46">
-        <v>112.8583696487864</v>
+        <v>108.4652517872689</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>112.8583696487864</v>
+        <v>108.4652517872689</v>
       </c>
       <c r="Q46">
-        <v>294.2583696487865</v>
+        <v>289.8652517872689</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1568624698123787</v>
+        <v>0.158881787445331</v>
       </c>
       <c r="T46">
-        <v>0.9513370965809338</v>
+        <v>0.9686341347005871</v>
       </c>
       <c r="U46">
         <v>0.1444771881973717</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.583859351699099</v>
+        <v>1.548662477216896</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1523997177837493</v>
+        <v>0.153386489665723</v>
       </c>
       <c r="C47">
-        <v>1145.538938510342</v>
+        <v>1095.932835214281</v>
       </c>
       <c r="D47">
-        <v>2093.253938510342</v>
+        <v>2074.054835214281</v>
       </c>
       <c r="E47">
-        <v>501.5150000000001</v>
+        <v>531.922</v>
       </c>
       <c r="F47">
-        <v>1368.315</v>
+        <v>1398.722</v>
       </c>
       <c r="G47">
         <v>420.6</v>
@@ -5141,28 +5141,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M47">
-        <v>197.6903037682866</v>
+        <v>202.0834216298041</v>
       </c>
       <c r="N47">
-        <v>108.4652517872689</v>
+        <v>104.0721339257514</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>108.4652517872689</v>
+        <v>104.0721339257514</v>
       </c>
       <c r="Q47">
-        <v>289.8652517872689</v>
+        <v>285.4721339257515</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.158881787445331</v>
+        <v>0.1609758946202446</v>
       </c>
       <c r="T47">
-        <v>0.9686341347005871</v>
+        <v>0.9865718038617092</v>
       </c>
       <c r="U47">
         <v>0.1444771881973717</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.548662477216896</v>
+        <v>1.514995901625225</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.153386489665723</v>
+        <v>0.1810692615476968</v>
       </c>
       <c r="C48">
-        <v>1095.932835214281</v>
+        <v>641.0717780470031</v>
       </c>
       <c r="D48">
-        <v>2074.054835214281</v>
+        <v>1649.600778047003</v>
       </c>
       <c r="E48">
-        <v>531.922</v>
+        <v>562.329</v>
       </c>
       <c r="F48">
-        <v>1398.722</v>
+        <v>1429.129</v>
       </c>
       <c r="G48">
         <v>420.6</v>
@@ -5223,45 +5223,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M48">
-        <v>202.0834216298041</v>
+        <v>287.6510666913216</v>
       </c>
       <c r="N48">
-        <v>104.0721339257514</v>
+        <v>18.50448886423396</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>104.0721339257514</v>
+        <v>18.50448886423396</v>
       </c>
       <c r="Q48">
-        <v>285.4721339257515</v>
+        <v>199.904488864234</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1609758946202446</v>
+        <v>0.163149024707419</v>
       </c>
       <c r="T48">
-        <v>0.9865718038617092</v>
+        <v>1.005186366198723</v>
       </c>
       <c r="U48">
-        <v>0.1444771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0.1444771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.514995901625225</v>
+        <v>1.064329637560813</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1810692615476968</v>
+        <v>0.1826240334296705</v>
       </c>
       <c r="C49">
-        <v>641.0717780470031</v>
+        <v>591.9198774480324</v>
       </c>
       <c r="D49">
-        <v>1649.600778047003</v>
+        <v>1630.855877448032</v>
       </c>
       <c r="E49">
-        <v>562.329</v>
+        <v>592.7360000000001</v>
       </c>
       <c r="F49">
-        <v>1429.129</v>
+        <v>1459.536</v>
       </c>
       <c r="G49">
         <v>420.6</v>
@@ -5305,28 +5305,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M49">
-        <v>287.6510666913216</v>
+        <v>293.7713021528391</v>
       </c>
       <c r="N49">
-        <v>18.50448886423396</v>
+        <v>12.38425340271647</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>18.50448886423396</v>
+        <v>12.38425340271647</v>
       </c>
       <c r="Q49">
-        <v>199.904488864234</v>
+        <v>193.7842534027165</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.163149024707419</v>
+        <v>0.1654057367210232</v>
       </c>
       <c r="T49">
-        <v>1.005186366198723</v>
+        <v>1.024516873241006</v>
       </c>
       <c r="U49">
         <v>0.2012771881973717</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.064329637560813</v>
+        <v>1.042156103444963</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1826240334296705</v>
+        <v>0.1841788053116442</v>
       </c>
       <c r="C50">
-        <v>591.9198774480326</v>
+        <v>543.1891980659386</v>
       </c>
       <c r="D50">
-        <v>1630.855877448033</v>
+        <v>1612.532198065938</v>
       </c>
       <c r="E50">
-        <v>592.7359999999999</v>
+        <v>623.143</v>
       </c>
       <c r="F50">
-        <v>1459.536</v>
+        <v>1489.943</v>
       </c>
       <c r="G50">
         <v>420.6</v>
@@ -5387,28 +5387,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M50">
-        <v>293.771302152839</v>
+        <v>299.8915376143566</v>
       </c>
       <c r="N50">
-        <v>12.38425340271652</v>
+        <v>6.264017941198972</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>12.38425340271652</v>
+        <v>6.264017941198972</v>
       </c>
       <c r="Q50">
-        <v>193.7842534027165</v>
+        <v>187.664017941199</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1654057367210232</v>
+        <v>0.1677509472449649</v>
       </c>
       <c r="T50">
-        <v>1.024516873241005</v>
+        <v>1.044605439382986</v>
       </c>
       <c r="U50">
         <v>0.2012771881973717</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.042156103444963</v>
+        <v>1.020887611537923</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1841788053116442</v>
+        <v>0.1857335771936179</v>
       </c>
       <c r="C51">
-        <v>543.1891980659386</v>
+        <v>494.8656996056638</v>
       </c>
       <c r="D51">
-        <v>1612.532198065938</v>
+        <v>1594.615699605664</v>
       </c>
       <c r="E51">
-        <v>623.143</v>
+        <v>653.55</v>
       </c>
       <c r="F51">
-        <v>1489.943</v>
+        <v>1520.35</v>
       </c>
       <c r="G51">
         <v>420.6</v>
@@ -5469,28 +5469,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M51">
-        <v>299.8915376143566</v>
+        <v>306.011773075874</v>
       </c>
       <c r="N51">
-        <v>6.264017941198972</v>
+        <v>0.1437824796815335</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>6.264017941198972</v>
+        <v>0.1437824796815335</v>
       </c>
       <c r="Q51">
-        <v>187.664017941199</v>
+        <v>181.5437824796815</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1677509472449649</v>
+        <v>0.1701899661898642</v>
       </c>
       <c r="T51">
-        <v>1.044605439382986</v>
+        <v>1.065497548170646</v>
       </c>
       <c r="U51">
         <v>0.2012771881973717</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.020887611537923</v>
+        <v>1.000469859307164</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1857335771936179</v>
+        <v>0.1872883490755916</v>
       </c>
       <c r="C52">
-        <v>494.8656996056638</v>
+        <v>446.9359589100598</v>
       </c>
       <c r="D52">
-        <v>1594.615699605664</v>
+        <v>1577.092958910059</v>
       </c>
       <c r="E52">
-        <v>653.55</v>
+        <v>683.9569999999999</v>
       </c>
       <c r="F52">
-        <v>1520.35</v>
+        <v>1550.757</v>
       </c>
       <c r="G52">
         <v>420.6</v>
@@ -5551,28 +5551,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M52">
-        <v>306.011773075874</v>
+        <v>312.1320085373915</v>
       </c>
       <c r="N52">
-        <v>0.1437824796815335</v>
+        <v>-5.976452981835962</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P52">
-        <v>0.1437824796815335</v>
+        <v>-5.976452981835962</v>
       </c>
       <c r="Q52">
-        <v>181.5437824796815</v>
+        <v>175.423547018164</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1701899661898642</v>
+        <v>0.1727285369284328</v>
       </c>
       <c r="T52">
-        <v>1.065497548170646</v>
+        <v>1.087242396092496</v>
       </c>
       <c r="U52">
         <v>0.2012771881973717</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.000469859307164</v>
+        <v>0.9808528032423178</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1872883490755916</v>
+        <v>0.1888431209575654</v>
       </c>
       <c r="C53">
-        <v>446.9359589100598</v>
+        <v>399.387136420745</v>
       </c>
       <c r="D53">
-        <v>1577.092958910059</v>
+        <v>1559.951136420745</v>
       </c>
       <c r="E53">
-        <v>683.9569999999999</v>
+        <v>714.364</v>
       </c>
       <c r="F53">
-        <v>1550.757</v>
+        <v>1581.164</v>
       </c>
       <c r="G53">
         <v>420.6</v>
@@ -5633,28 +5633,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M53">
-        <v>312.1320085373915</v>
+        <v>318.252243998909</v>
       </c>
       <c r="N53">
-        <v>-5.976452981835962</v>
+        <v>-12.09668844335346</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-5.976452981835962</v>
+        <v>-12.09668844335346</v>
       </c>
       <c r="Q53">
-        <v>175.423547018164</v>
+        <v>169.3033115566465</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1727285369284328</v>
+        <v>0.1753728814477752</v>
       </c>
       <c r="T53">
-        <v>1.087242396092496</v>
+        <v>1.109893279344423</v>
       </c>
       <c r="U53">
         <v>0.2012771881973717</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9808528032423178</v>
+        <v>0.9619902493338117</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1888431209575654</v>
+        <v>0.1903978928395391</v>
       </c>
       <c r="C54">
-        <v>399.387136420745</v>
+        <v>352.2069448027223</v>
       </c>
       <c r="D54">
-        <v>1559.951136420745</v>
+        <v>1543.177944802722</v>
       </c>
       <c r="E54">
-        <v>714.364</v>
+        <v>744.771</v>
       </c>
       <c r="F54">
-        <v>1581.164</v>
+        <v>1611.571</v>
       </c>
       <c r="G54">
         <v>420.6</v>
@@ -5715,28 +5715,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M54">
-        <v>318.252243998909</v>
+        <v>324.3724794604265</v>
       </c>
       <c r="N54">
-        <v>-12.09668844335346</v>
+        <v>-18.2169239048709</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-12.09668844335346</v>
+        <v>-18.2169239048709</v>
       </c>
       <c r="Q54">
-        <v>169.3033115566465</v>
+        <v>163.1830760951291</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1753728814477752</v>
+        <v>0.178129751265813</v>
       </c>
       <c r="T54">
-        <v>1.109893279344423</v>
+        <v>1.133508029968772</v>
       </c>
       <c r="U54">
         <v>0.2012771881973717</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9619902493338117</v>
+        <v>0.9438394899124192</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1903978928395391</v>
+        <v>0.1919526647215128</v>
       </c>
       <c r="C55">
-        <v>352.2069448027223</v>
+        <v>305.3836195716153</v>
       </c>
       <c r="D55">
-        <v>1543.177944802722</v>
+        <v>1526.761619571615</v>
       </c>
       <c r="E55">
-        <v>744.771</v>
+        <v>775.1780000000001</v>
       </c>
       <c r="F55">
-        <v>1611.571</v>
+        <v>1641.978</v>
       </c>
       <c r="G55">
         <v>420.6</v>
@@ -5797,28 +5797,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M55">
-        <v>324.3724794604265</v>
+        <v>330.492714921944</v>
       </c>
       <c r="N55">
-        <v>-18.2169239048709</v>
+        <v>-24.33715936638845</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-18.2169239048709</v>
+        <v>-24.33715936638845</v>
       </c>
       <c r="Q55">
-        <v>163.1830760951291</v>
+        <v>157.0628406336116</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.178129751265813</v>
+        <v>0.1810064849889828</v>
       </c>
       <c r="T55">
-        <v>1.133508029968772</v>
+        <v>1.158149508881137</v>
       </c>
       <c r="U55">
         <v>0.2012771881973717</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9438394899124192</v>
+        <v>0.9263609808399668</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1919526647215128</v>
+        <v>0.1935074366034865</v>
       </c>
       <c r="C56">
-        <v>305.3836195716153</v>
+        <v>258.905891575984</v>
       </c>
       <c r="D56">
-        <v>1526.761619571615</v>
+        <v>1510.690891575984</v>
       </c>
       <c r="E56">
-        <v>775.1780000000001</v>
+        <v>805.585</v>
       </c>
       <c r="F56">
-        <v>1641.978</v>
+        <v>1672.385</v>
       </c>
       <c r="G56">
         <v>420.6</v>
@@ -5879,28 +5879,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M56">
-        <v>330.492714921944</v>
+        <v>336.6129503834615</v>
       </c>
       <c r="N56">
-        <v>-24.33715936638845</v>
+        <v>-30.45739482790589</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-24.33715936638845</v>
+        <v>-30.45739482790589</v>
       </c>
       <c r="Q56">
-        <v>157.0628406336116</v>
+        <v>150.9426051720941</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1810064849889828</v>
+        <v>0.1840110735442935</v>
       </c>
       <c r="T56">
-        <v>1.158149508881137</v>
+        <v>1.183886164634051</v>
       </c>
       <c r="U56">
         <v>0.2012771881973717</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9263609808399668</v>
+        <v>0.9095180539156038</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1935074366034865</v>
+        <v>0.1950622084854602</v>
       </c>
       <c r="C57">
-        <v>258.905891575984</v>
+        <v>212.7629611994414</v>
       </c>
       <c r="D57">
-        <v>1510.690891575984</v>
+        <v>1494.954961199441</v>
       </c>
       <c r="E57">
-        <v>805.585</v>
+        <v>835.9920000000002</v>
       </c>
       <c r="F57">
-        <v>1672.385</v>
+        <v>1702.792</v>
       </c>
       <c r="G57">
         <v>420.6</v>
@@ -5961,28 +5961,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M57">
-        <v>336.6129503834615</v>
+        <v>342.733185844979</v>
       </c>
       <c r="N57">
-        <v>-30.45739482790589</v>
+        <v>-36.57763028942344</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-30.45739482790589</v>
+        <v>-36.57763028942344</v>
       </c>
       <c r="Q57">
-        <v>150.9426051720941</v>
+        <v>144.8223697105766</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1840110735442935</v>
+        <v>0.1871522343066639</v>
       </c>
       <c r="T57">
-        <v>1.183886164634051</v>
+        <v>1.210792668375734</v>
       </c>
       <c r="U57">
         <v>0.2012771881973717</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9095180539156038</v>
+        <v>0.8932766600956821</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1950622084854602</v>
+        <v>0.196616980367434</v>
       </c>
       <c r="C58">
-        <v>212.7629611994414</v>
+        <v>166.9444741584775</v>
       </c>
       <c r="D58">
-        <v>1494.954961199441</v>
+        <v>1479.543474158478</v>
       </c>
       <c r="E58">
-        <v>835.9920000000002</v>
+        <v>866.3990000000001</v>
       </c>
       <c r="F58">
-        <v>1702.792</v>
+        <v>1733.199</v>
       </c>
       <c r="G58">
         <v>420.6</v>
@@ -6043,28 +6043,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M58">
-        <v>342.733185844979</v>
+        <v>348.8534213064964</v>
       </c>
       <c r="N58">
-        <v>-36.57763028942344</v>
+        <v>-42.69786575094088</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-36.57763028942344</v>
+        <v>-42.69786575094088</v>
       </c>
       <c r="Q58">
-        <v>144.8223697105766</v>
+        <v>138.7021342490591</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1871522343066639</v>
+        <v>0.1904394955696095</v>
       </c>
       <c r="T58">
-        <v>1.210792668375734</v>
+        <v>1.238950637407728</v>
       </c>
       <c r="U58">
         <v>0.2012771881973717</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8932766600956821</v>
+        <v>0.8776051397431264</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.196616980367434</v>
+        <v>0.1981717522494077</v>
       </c>
       <c r="C59">
-        <v>166.9444741584775</v>
+        <v>121.4404987820049</v>
       </c>
       <c r="D59">
-        <v>1479.543474158478</v>
+        <v>1464.446498782005</v>
       </c>
       <c r="E59">
-        <v>866.3990000000001</v>
+        <v>896.8060000000003</v>
       </c>
       <c r="F59">
-        <v>1733.199</v>
+        <v>1763.606</v>
       </c>
       <c r="G59">
         <v>420.6</v>
@@ -6125,28 +6125,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M59">
-        <v>348.8534213064964</v>
+        <v>354.9736567680139</v>
       </c>
       <c r="N59">
-        <v>-42.69786575094088</v>
+        <v>-48.81810121245837</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-42.69786575094088</v>
+        <v>-48.81810121245837</v>
       </c>
       <c r="Q59">
-        <v>138.7021342490591</v>
+        <v>132.5818987875416</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1904394955696095</v>
+        <v>0.1938832930831717</v>
       </c>
       <c r="T59">
-        <v>1.238950637407728</v>
+        <v>1.268449462107912</v>
       </c>
       <c r="U59">
         <v>0.2012771881973717</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8776051397431264</v>
+        <v>0.8624740166441069</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1981717522494077</v>
+        <v>0.1997265241313814</v>
       </c>
       <c r="C60">
-        <v>121.4404987820053</v>
+        <v>76.24150466786773</v>
       </c>
       <c r="D60">
-        <v>1464.446498782005</v>
+        <v>1449.654504667868</v>
       </c>
       <c r="E60">
-        <v>896.8059999999998</v>
+        <v>927.2129999999997</v>
       </c>
       <c r="F60">
-        <v>1763.606</v>
+        <v>1794.013</v>
       </c>
       <c r="G60">
         <v>420.6</v>
@@ -6207,28 +6207,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M60">
-        <v>354.9736567680139</v>
+        <v>361.0938922295313</v>
       </c>
       <c r="N60">
-        <v>-48.81810121245832</v>
+        <v>-54.93833667397575</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-48.81810121245832</v>
+        <v>-54.93833667397575</v>
       </c>
       <c r="Q60">
-        <v>132.5818987875417</v>
+        <v>126.4616633260243</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1938832930831716</v>
+        <v>0.1974950807193465</v>
       </c>
       <c r="T60">
-        <v>1.268449462107912</v>
+        <v>1.299387253866641</v>
       </c>
       <c r="U60">
         <v>0.2012771881973717</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8624740166441072</v>
+        <v>0.8478558129721732</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1997265241313814</v>
+        <v>0.2012812960133551</v>
       </c>
       <c r="C61">
-        <v>76.24150466786773</v>
+        <v>31.33834261992229</v>
       </c>
       <c r="D61">
-        <v>1449.654504667868</v>
+        <v>1435.158342619922</v>
       </c>
       <c r="E61">
-        <v>927.2129999999997</v>
+        <v>957.6199999999999</v>
       </c>
       <c r="F61">
-        <v>1794.013</v>
+        <v>1824.42</v>
       </c>
       <c r="G61">
         <v>420.6</v>
@@ -6289,28 +6289,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M61">
-        <v>361.0938922295313</v>
+        <v>367.2141276910488</v>
       </c>
       <c r="N61">
-        <v>-54.93833667397575</v>
+        <v>-61.05857213549325</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-54.93833667397575</v>
+        <v>-61.05857213549325</v>
       </c>
       <c r="Q61">
-        <v>126.4616633260243</v>
+        <v>120.3414278645068</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1974950807193465</v>
+        <v>0.2012874577373302</v>
       </c>
       <c r="T61">
-        <v>1.299387253866641</v>
+        <v>1.331871935213307</v>
       </c>
       <c r="U61">
         <v>0.2012771881973717</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8478558129721732</v>
+        <v>0.8337248827559702</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2012812960133551</v>
+        <v>0.2028360678953288</v>
       </c>
       <c r="C62">
-        <v>31.33834261992229</v>
+        <v>-13.27777422304871</v>
       </c>
       <c r="D62">
-        <v>1435.158342619922</v>
+        <v>1420.949225776951</v>
       </c>
       <c r="E62">
-        <v>957.6199999999999</v>
+        <v>988.0269999999998</v>
       </c>
       <c r="F62">
-        <v>1824.42</v>
+        <v>1854.827</v>
       </c>
       <c r="G62">
         <v>420.6</v>
@@ -6371,28 +6371,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M62">
-        <v>367.2141276910488</v>
+        <v>373.3343631525663</v>
       </c>
       <c r="N62">
-        <v>-61.05857213549325</v>
+        <v>-67.17880759701075</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-61.05857213549325</v>
+        <v>-67.17880759701075</v>
       </c>
       <c r="Q62">
-        <v>120.3414278645068</v>
+        <v>114.2211924029893</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2012874577373302</v>
+        <v>0.205274315628031</v>
       </c>
       <c r="T62">
-        <v>1.331871935213307</v>
+        <v>1.366022497654674</v>
       </c>
       <c r="U62">
         <v>0.2012771881973717</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8337248827559702</v>
+        <v>0.8200572617271839</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2028360678953288</v>
+        <v>0.2043908397773025</v>
       </c>
       <c r="C63">
-        <v>-13.27777422304871</v>
+        <v>-57.61528814839676</v>
       </c>
       <c r="D63">
-        <v>1420.949225776951</v>
+        <v>1407.018711851603</v>
       </c>
       <c r="E63">
-        <v>988.0269999999998</v>
+        <v>1018.434</v>
       </c>
       <c r="F63">
-        <v>1854.827</v>
+        <v>1885.234</v>
       </c>
       <c r="G63">
         <v>420.6</v>
@@ -6453,28 +6453,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M63">
-        <v>373.3343631525663</v>
+        <v>379.4545986140838</v>
       </c>
       <c r="N63">
-        <v>-67.17880759701075</v>
+        <v>-73.29904305852824</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-67.17880759701075</v>
+        <v>-73.29904305852824</v>
       </c>
       <c r="Q63">
-        <v>114.2211924029893</v>
+        <v>108.1009569414718</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.205274315628031</v>
+        <v>0.2094710081445582</v>
       </c>
       <c r="T63">
-        <v>1.366022497654674</v>
+        <v>1.401970458119271</v>
       </c>
       <c r="U63">
         <v>0.2012771881973717</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8200572617271839</v>
+        <v>0.8068305316993261</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2043908397773025</v>
+        <v>0.2399656116592762</v>
       </c>
       <c r="C64">
-        <v>-57.61528814839676</v>
+        <v>-345.8144341419168</v>
       </c>
       <c r="D64">
-        <v>1407.018711851603</v>
+        <v>1149.226565858083</v>
       </c>
       <c r="E64">
-        <v>1018.434</v>
+        <v>1048.841</v>
       </c>
       <c r="F64">
-        <v>1885.234</v>
+        <v>1915.641</v>
       </c>
       <c r="G64">
         <v>420.6</v>
@@ -6535,45 +6535,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M64">
-        <v>379.4545986140838</v>
+        <v>489.0194480756012</v>
       </c>
       <c r="N64">
-        <v>-73.29904305852824</v>
+        <v>-182.8638925200456</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-73.29904305852824</v>
+        <v>-182.8638925200456</v>
       </c>
       <c r="Q64">
-        <v>108.1009569414718</v>
+        <v>-1.463892520045619</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2094710081445582</v>
+        <v>0.2138945489052219</v>
       </c>
       <c r="T64">
-        <v>1.401970458119271</v>
+        <v>1.439861551581954</v>
       </c>
       <c r="U64">
-        <v>0.2012771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.2012771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8068305316993261</v>
+        <v>0.6260600815782376</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2399656116592762</v>
+        <v>0.24206038354125</v>
       </c>
       <c r="C65">
-        <v>-345.8144341419168</v>
+        <v>-388.4876258854522</v>
       </c>
       <c r="D65">
-        <v>1149.226565858083</v>
+        <v>1136.960374114548</v>
       </c>
       <c r="E65">
-        <v>1048.841</v>
+        <v>1079.248</v>
       </c>
       <c r="F65">
-        <v>1915.641</v>
+        <v>1946.048</v>
       </c>
       <c r="G65">
         <v>420.6</v>
@@ -6617,28 +6617,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M65">
-        <v>489.0194480756012</v>
+        <v>496.7816615371187</v>
       </c>
       <c r="N65">
-        <v>-182.8638925200456</v>
+        <v>-190.6261059815632</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-182.8638925200456</v>
+        <v>-190.6261059815632</v>
       </c>
       <c r="Q65">
-        <v>-1.463892520045619</v>
+        <v>-9.226105981563165</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2138945489052219</v>
+        <v>0.2185638419303669</v>
       </c>
       <c r="T65">
-        <v>1.439861551581954</v>
+        <v>1.479857705792564</v>
       </c>
       <c r="U65">
         <v>0.2552771881973717</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.6260600815782376</v>
+        <v>0.6162778928035775</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.24206038354125</v>
+        <v>0.2441551554232237</v>
       </c>
       <c r="C66">
-        <v>-388.4876258854522</v>
+        <v>-430.9017381661074</v>
       </c>
       <c r="D66">
-        <v>1136.960374114548</v>
+        <v>1124.953261833893</v>
       </c>
       <c r="E66">
-        <v>1079.248</v>
+        <v>1109.655</v>
       </c>
       <c r="F66">
-        <v>1946.048</v>
+        <v>1976.455</v>
       </c>
       <c r="G66">
         <v>420.6</v>
@@ -6699,28 +6699,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M66">
-        <v>496.7816615371187</v>
+        <v>504.5438749986362</v>
       </c>
       <c r="N66">
-        <v>-190.6261059815632</v>
+        <v>-198.3883194430806</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-190.6261059815632</v>
+        <v>-198.3883194430806</v>
       </c>
       <c r="Q66">
-        <v>-9.226105981563165</v>
+        <v>-16.9883194430806</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2185638419303669</v>
+        <v>0.223499951699806</v>
       </c>
       <c r="T66">
-        <v>1.479857705792564</v>
+        <v>1.522139354529494</v>
       </c>
       <c r="U66">
         <v>0.2552771881973717</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.6162778928035775</v>
+        <v>0.6067966944527532</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2441551554232237</v>
+        <v>0.2462499273051974</v>
       </c>
       <c r="C67">
-        <v>-430.9017381661074</v>
+        <v>-473.0648933970165</v>
       </c>
       <c r="D67">
-        <v>1124.953261833893</v>
+        <v>1113.197106602984</v>
       </c>
       <c r="E67">
-        <v>1109.655</v>
+        <v>1140.062</v>
       </c>
       <c r="F67">
-        <v>1976.455</v>
+        <v>2006.862</v>
       </c>
       <c r="G67">
         <v>420.6</v>
@@ -6781,28 +6781,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M67">
-        <v>504.5438749986362</v>
+        <v>512.3060884601537</v>
       </c>
       <c r="N67">
-        <v>-198.3883194430806</v>
+        <v>-206.1505329045981</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-198.3883194430806</v>
+        <v>-206.1505329045981</v>
       </c>
       <c r="Q67">
-        <v>-16.9883194430806</v>
+        <v>-24.75053290459809</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.223499951699806</v>
+        <v>0.2287264208674473</v>
       </c>
       <c r="T67">
-        <v>1.522139354529494</v>
+        <v>1.566908159074479</v>
       </c>
       <c r="U67">
         <v>0.2552771881973717</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.6067966944527532</v>
+        <v>0.597602805142863</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2462499273051974</v>
+        <v>0.2483446991871711</v>
       </c>
       <c r="C68">
-        <v>-473.0648933970165</v>
+        <v>-514.9848779745664</v>
       </c>
       <c r="D68">
-        <v>1113.197106602984</v>
+        <v>1101.684122025434</v>
       </c>
       <c r="E68">
-        <v>1140.062</v>
+        <v>1170.469</v>
       </c>
       <c r="F68">
-        <v>2006.862</v>
+        <v>2037.269</v>
       </c>
       <c r="G68">
         <v>420.6</v>
@@ -6863,28 +6863,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M68">
-        <v>512.3060884601537</v>
+        <v>520.0683019216712</v>
       </c>
       <c r="N68">
-        <v>-206.1505329045981</v>
+        <v>-213.9127463661156</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-206.1505329045981</v>
+        <v>-213.9127463661156</v>
       </c>
       <c r="Q68">
-        <v>-24.75053290459809</v>
+        <v>-32.51274636611558</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2287264208674473</v>
+        <v>0.2342696457422185</v>
       </c>
       <c r="T68">
-        <v>1.566908159074479</v>
+        <v>1.614390224500979</v>
       </c>
       <c r="U68">
         <v>0.2552771881973717</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.597602805142863</v>
+        <v>0.5886833602899845</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2483446991871711</v>
+        <v>0.2504394710691448</v>
       </c>
       <c r="C69">
-        <v>-514.9848779745664</v>
+        <v>-556.6691594764129</v>
       </c>
       <c r="D69">
-        <v>1101.684122025434</v>
+        <v>1090.406840523587</v>
       </c>
       <c r="E69">
-        <v>1170.469</v>
+        <v>1200.876</v>
       </c>
       <c r="F69">
-        <v>2037.269</v>
+        <v>2067.676</v>
       </c>
       <c r="G69">
         <v>420.6</v>
@@ -6945,28 +6945,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M69">
-        <v>520.0683019216712</v>
+        <v>527.8305153831886</v>
       </c>
       <c r="N69">
-        <v>-213.9127463661156</v>
+        <v>-221.6749598276331</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-213.9127463661156</v>
+        <v>-221.6749598276331</v>
       </c>
       <c r="Q69">
-        <v>-32.51274636611558</v>
+        <v>-40.27495982763307</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2342696457422185</v>
+        <v>0.2401593221716628</v>
       </c>
       <c r="T69">
-        <v>1.614390224500979</v>
+        <v>1.664839919016635</v>
       </c>
       <c r="U69">
         <v>0.2552771881973717</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5886833602899845</v>
+        <v>0.5800262520504258</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2504394710691448</v>
+        <v>0.2525342429511185</v>
       </c>
       <c r="C70">
-        <v>-556.6691594764129</v>
+        <v>-598.1249028139196</v>
       </c>
       <c r="D70">
-        <v>1090.406840523587</v>
+        <v>1079.358097186081</v>
       </c>
       <c r="E70">
-        <v>1200.876</v>
+        <v>1231.283</v>
       </c>
       <c r="F70">
-        <v>2067.676</v>
+        <v>2098.083</v>
       </c>
       <c r="G70">
         <v>420.6</v>
@@ -7027,28 +7027,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M70">
-        <v>527.8305153831886</v>
+        <v>535.5927288447061</v>
       </c>
       <c r="N70">
-        <v>-221.6749598276331</v>
+        <v>-229.4371732891506</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-221.6749598276331</v>
+        <v>-229.4371732891506</v>
       </c>
       <c r="Q70">
-        <v>-40.27495982763307</v>
+        <v>-48.03717328915056</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2401593221716628</v>
+        <v>0.2464289777255874</v>
       </c>
       <c r="T70">
-        <v>1.664839919016635</v>
+        <v>1.7185444325333</v>
       </c>
       <c r="U70">
         <v>0.2552771881973717</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5800262520504258</v>
+        <v>0.5716200744844777</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2525342429511185</v>
+        <v>0.2546290148330922</v>
       </c>
       <c r="C71">
-        <v>-598.1249028139196</v>
+        <v>-639.3589854124425</v>
       </c>
       <c r="D71">
-        <v>1079.358097186081</v>
+        <v>1068.531014587558</v>
       </c>
       <c r="E71">
-        <v>1231.283</v>
+        <v>1261.69</v>
       </c>
       <c r="F71">
-        <v>2098.083</v>
+        <v>2128.49</v>
       </c>
       <c r="G71">
         <v>420.6</v>
@@ -7109,28 +7109,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M71">
-        <v>535.5927288447061</v>
+        <v>543.3549423062236</v>
       </c>
       <c r="N71">
-        <v>-229.4371732891506</v>
+        <v>-237.1993867506681</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-229.4371732891506</v>
+        <v>-237.1993867506681</v>
       </c>
       <c r="Q71">
-        <v>-48.03717328915056</v>
+        <v>-55.79938675066805</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2464289777255874</v>
+        <v>0.2531166103164403</v>
       </c>
       <c r="T71">
-        <v>1.7185444325333</v>
+        <v>1.775829246951077</v>
       </c>
       <c r="U71">
         <v>0.2552771881973717</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5716200744844777</v>
+        <v>0.5634540734204136</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2546290148330922</v>
+        <v>0.256723786715066</v>
       </c>
       <c r="C72">
-        <v>-639.3589854124425</v>
+        <v>-680.3780114870478</v>
       </c>
       <c r="D72">
-        <v>1068.531014587558</v>
+        <v>1057.918988512952</v>
       </c>
       <c r="E72">
-        <v>1261.69</v>
+        <v>1292.097</v>
       </c>
       <c r="F72">
-        <v>2128.49</v>
+        <v>2158.897</v>
       </c>
       <c r="G72">
         <v>420.6</v>
@@ -7191,28 +7191,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M72">
-        <v>543.3549423062236</v>
+        <v>551.1171557677411</v>
       </c>
       <c r="N72">
-        <v>-237.1993867506681</v>
+        <v>-244.9616002121855</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-237.1993867506681</v>
+        <v>-244.9616002121855</v>
       </c>
       <c r="Q72">
-        <v>-55.79938675066805</v>
+        <v>-63.56160021218554</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2531166103164403</v>
+        <v>0.2602654589480417</v>
       </c>
       <c r="T72">
-        <v>1.775829246951077</v>
+        <v>1.837064738225252</v>
       </c>
       <c r="U72">
         <v>0.2552771881973717</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5634540734204136</v>
+        <v>0.5555181005553373</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.256723786715066</v>
+        <v>0.2588185585970397</v>
       </c>
       <c r="C73">
-        <v>-680.3780114870478</v>
+        <v>-721.1883254759246</v>
       </c>
       <c r="D73">
-        <v>1057.918988512952</v>
+        <v>1047.515674524075</v>
       </c>
       <c r="E73">
-        <v>1292.097</v>
+        <v>1322.504</v>
       </c>
       <c r="F73">
-        <v>2158.897</v>
+        <v>2189.304</v>
       </c>
       <c r="G73">
         <v>420.6</v>
@@ -7273,28 +7273,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M73">
-        <v>551.1171557677411</v>
+        <v>558.8793692292585</v>
       </c>
       <c r="N73">
-        <v>-244.9616002121855</v>
+        <v>-252.7238136737029</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-244.9616002121855</v>
+        <v>-252.7238136737029</v>
       </c>
       <c r="Q73">
-        <v>-63.56160021218554</v>
+        <v>-71.32381367370292</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2602654589480417</v>
+        <v>0.2679249396247574</v>
       </c>
       <c r="T73">
-        <v>1.837064738225251</v>
+        <v>1.902674193161868</v>
       </c>
       <c r="U73">
         <v>0.2552771881973717</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5555181005553373</v>
+        <v>0.5478025713809578</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2588185585970397</v>
+        <v>0.2609133304790134</v>
       </c>
       <c r="C74">
-        <v>-721.1883254759246</v>
+        <v>-761.7960246889093</v>
       </c>
       <c r="D74">
-        <v>1047.515674524075</v>
+        <v>1037.31497531109</v>
       </c>
       <c r="E74">
-        <v>1322.504</v>
+        <v>1352.911</v>
       </c>
       <c r="F74">
-        <v>2189.304</v>
+        <v>2219.711</v>
       </c>
       <c r="G74">
         <v>420.6</v>
@@ -7355,28 +7355,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M74">
-        <v>558.8793692292585</v>
+        <v>566.641582690776</v>
       </c>
       <c r="N74">
-        <v>-252.7238136737029</v>
+        <v>-260.4860271352204</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-252.7238136737029</v>
+        <v>-260.4860271352204</v>
       </c>
       <c r="Q74">
-        <v>-71.32381367370292</v>
+        <v>-79.08602713522041</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2679249396247574</v>
+        <v>0.2761517892404892</v>
       </c>
       <c r="T74">
-        <v>1.902674193161868</v>
+        <v>1.973143607723418</v>
       </c>
       <c r="U74">
         <v>0.2552771881973717</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5478025713809578</v>
+        <v>0.54029842656752</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2609133304790134</v>
+        <v>0.2630081023609871</v>
       </c>
       <c r="C75">
-        <v>-761.7960246889093</v>
+        <v>-802.2069712241114</v>
       </c>
       <c r="D75">
-        <v>1037.31497531109</v>
+        <v>1027.311028775889</v>
       </c>
       <c r="E75">
-        <v>1352.911</v>
+        <v>1383.318</v>
       </c>
       <c r="F75">
-        <v>2219.711</v>
+        <v>2250.118</v>
       </c>
       <c r="G75">
         <v>420.6</v>
@@ -7437,28 +7437,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M75">
-        <v>566.641582690776</v>
+        <v>574.4037961522935</v>
       </c>
       <c r="N75">
-        <v>-260.4860271352204</v>
+        <v>-268.2482405967379</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-260.4860271352204</v>
+        <v>-268.2482405967379</v>
       </c>
       <c r="Q75">
-        <v>-79.08602713522041</v>
+        <v>-86.8482405967379</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2761517892404892</v>
+        <v>0.2850114734420464</v>
       </c>
       <c r="T75">
-        <v>1.973143607723418</v>
+        <v>2.049033746482011</v>
       </c>
       <c r="U75">
         <v>0.2552771881973717</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.54029842656752</v>
+        <v>0.5329970964787698</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2630081023609871</v>
+        <v>0.2651028742429609</v>
       </c>
       <c r="C76">
-        <v>-802.2069712241114</v>
+        <v>-842.4268032015759</v>
       </c>
       <c r="D76">
-        <v>1027.311028775889</v>
+        <v>1017.498196798424</v>
       </c>
       <c r="E76">
-        <v>1383.318</v>
+        <v>1413.725</v>
       </c>
       <c r="F76">
-        <v>2250.118</v>
+        <v>2280.525</v>
       </c>
       <c r="G76">
         <v>420.6</v>
@@ -7519,28 +7519,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M76">
-        <v>574.4037961522935</v>
+        <v>582.166009613811</v>
       </c>
       <c r="N76">
-        <v>-268.2482405967379</v>
+        <v>-276.0104540582554</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-268.2482405967379</v>
+        <v>-276.0104540582554</v>
       </c>
       <c r="Q76">
-        <v>-86.8482405967379</v>
+        <v>-94.61045405825539</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2850114734420464</v>
+        <v>0.2945799323797283</v>
       </c>
       <c r="T76">
-        <v>2.049033746482011</v>
+        <v>2.130995096341292</v>
       </c>
       <c r="U76">
         <v>0.2552771881973717</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5329970964787698</v>
+        <v>0.5258904685257195</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2651028742429609</v>
+        <v>0.2671976461249346</v>
       </c>
       <c r="C77">
-        <v>-842.4268032015759</v>
+        <v>-882.4609453592188</v>
       </c>
       <c r="D77">
-        <v>1017.498196798424</v>
+        <v>1007.871054640781</v>
       </c>
       <c r="E77">
-        <v>1413.725</v>
+        <v>1444.132</v>
       </c>
       <c r="F77">
-        <v>2280.525</v>
+        <v>2310.932</v>
       </c>
       <c r="G77">
         <v>420.6</v>
@@ -7601,28 +7601,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M77">
-        <v>582.166009613811</v>
+        <v>589.9282230753284</v>
       </c>
       <c r="N77">
-        <v>-276.0104540582554</v>
+        <v>-283.7726675197729</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-276.0104540582554</v>
+        <v>-283.7726675197729</v>
       </c>
       <c r="Q77">
-        <v>-94.61045405825539</v>
+        <v>-102.3726675197729</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2945799323797283</v>
+        <v>0.3049457628955504</v>
       </c>
       <c r="T77">
-        <v>2.130995096341292</v>
+        <v>2.219786558688846</v>
       </c>
       <c r="U77">
         <v>0.2552771881973717</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5258904685257195</v>
+        <v>0.5189708570977495</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2671976461249346</v>
+        <v>0.2692924180069083</v>
       </c>
       <c r="C78">
-        <v>-882.4609453592188</v>
+        <v>-922.3146190528719</v>
       </c>
       <c r="D78">
-        <v>1007.871054640781</v>
+        <v>998.424380947128</v>
       </c>
       <c r="E78">
-        <v>1444.132</v>
+        <v>1474.539</v>
       </c>
       <c r="F78">
-        <v>2310.932</v>
+        <v>2341.339</v>
       </c>
       <c r="G78">
         <v>420.6</v>
@@ -7683,28 +7683,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M78">
-        <v>589.9282230753284</v>
+        <v>597.6904365368459</v>
       </c>
       <c r="N78">
-        <v>-283.7726675197729</v>
+        <v>-291.5348809812904</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-283.7726675197729</v>
+        <v>-291.5348809812904</v>
       </c>
       <c r="Q78">
-        <v>-102.3726675197729</v>
+        <v>-110.1348809812904</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3049457628955504</v>
+        <v>0.3162129699779656</v>
       </c>
       <c r="T78">
-        <v>2.219786558688846</v>
+        <v>2.316299017762274</v>
       </c>
       <c r="U78">
         <v>0.2552771881973717</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5189708570977495</v>
+        <v>0.5122309758367398</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2692924180069083</v>
+        <v>0.271387189888882</v>
       </c>
       <c r="C79">
-        <v>-922.3146190528719</v>
+        <v>-961.9928516991727</v>
       </c>
       <c r="D79">
-        <v>998.424380947128</v>
+        <v>989.1531483008274</v>
       </c>
       <c r="E79">
-        <v>1474.539</v>
+        <v>1504.946</v>
       </c>
       <c r="F79">
-        <v>2341.339</v>
+        <v>2371.746</v>
       </c>
       <c r="G79">
         <v>420.6</v>
@@ -7765,28 +7765,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M79">
-        <v>597.6904365368459</v>
+        <v>605.4526499983634</v>
       </c>
       <c r="N79">
-        <v>-291.5348809812904</v>
+        <v>-299.2970944428079</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-291.5348809812904</v>
+        <v>-299.2970944428079</v>
       </c>
       <c r="Q79">
-        <v>-110.1348809812904</v>
+        <v>-117.8970944428079</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3162129699779656</v>
+        <v>0.3285044686133277</v>
       </c>
       <c r="T79">
-        <v>2.316299017762274</v>
+        <v>2.421585336751468</v>
       </c>
       <c r="U79">
         <v>0.2552771881973717</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5122309758367398</v>
+        <v>0.505663912043961</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.271387189888882</v>
+        <v>0.3011319617708558</v>
       </c>
       <c r="C80">
-        <v>-961.9928516991727</v>
+        <v>-1107.630763444365</v>
       </c>
       <c r="D80">
-        <v>989.1531483008274</v>
+        <v>873.9222365556351</v>
       </c>
       <c r="E80">
-        <v>1504.946</v>
+        <v>1535.353</v>
       </c>
       <c r="F80">
-        <v>2371.746</v>
+        <v>2402.153</v>
       </c>
       <c r="G80">
         <v>420.6</v>
@@ -7847,45 +7847,45 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M80">
-        <v>605.4526499983634</v>
+        <v>697.290218459881</v>
       </c>
       <c r="N80">
-        <v>-299.2970944428079</v>
+        <v>-391.1346629043254</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-299.2970944428079</v>
+        <v>-391.1346629043254</v>
       </c>
       <c r="Q80">
-        <v>-117.8970944428079</v>
+        <v>-209.7346629043254</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3285044686133277</v>
+        <v>0.3419665861663433</v>
       </c>
       <c r="T80">
-        <v>2.421585336751468</v>
+        <v>2.536898924215824</v>
       </c>
       <c r="U80">
-        <v>0.2552771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.2552771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.505663912043961</v>
+        <v>0.4390647501577859</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3011319617708558</v>
+        <v>0.3035767336528294</v>
       </c>
       <c r="C81">
-        <v>-1107.630763444365</v>
+        <v>-1146.326100722469</v>
       </c>
       <c r="D81">
-        <v>873.9222365556351</v>
+        <v>865.6338992775306</v>
       </c>
       <c r="E81">
-        <v>1535.353</v>
+        <v>1565.76</v>
       </c>
       <c r="F81">
-        <v>2402.153</v>
+        <v>2432.56</v>
       </c>
       <c r="G81">
         <v>420.6</v>
@@ -7929,28 +7929,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M81">
-        <v>697.290218459881</v>
+        <v>706.1166769213985</v>
       </c>
       <c r="N81">
-        <v>-391.1346629043254</v>
+        <v>-399.9611213658429</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-391.1346629043254</v>
+        <v>-399.9611213658429</v>
       </c>
       <c r="Q81">
-        <v>-209.7346629043254</v>
+        <v>-218.5611213658429</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3419665861663433</v>
+        <v>0.3567749154746605</v>
       </c>
       <c r="T81">
-        <v>2.536898924215824</v>
+        <v>2.663743870426615</v>
       </c>
       <c r="U81">
         <v>0.2902771881973717</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4390647501577859</v>
+        <v>0.4335764407808135</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3035767336528294</v>
+        <v>0.3060215055348032</v>
       </c>
       <c r="C82">
-        <v>-1146.326100722469</v>
+        <v>-1184.865700726791</v>
       </c>
       <c r="D82">
-        <v>865.6338992775306</v>
+        <v>857.5012992732087</v>
       </c>
       <c r="E82">
-        <v>1565.76</v>
+        <v>1596.167</v>
       </c>
       <c r="F82">
-        <v>2432.56</v>
+        <v>2462.967</v>
       </c>
       <c r="G82">
         <v>420.6</v>
@@ -8011,28 +8011,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M82">
-        <v>706.1166769213985</v>
+        <v>714.943135382916</v>
       </c>
       <c r="N82">
-        <v>-399.9611213658429</v>
+        <v>-408.7875798273604</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-399.9611213658429</v>
+        <v>-408.7875798273604</v>
       </c>
       <c r="Q82">
-        <v>-218.5611213658429</v>
+        <v>-227.3875798273604</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3567749154746605</v>
+        <v>0.3731420162891163</v>
       </c>
       <c r="T82">
-        <v>2.663743870426615</v>
+        <v>2.803940916238543</v>
       </c>
       <c r="U82">
         <v>0.2902771881973717</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4335764407808135</v>
+        <v>0.4282236452156183</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3060215055348032</v>
+        <v>0.3084662774167769</v>
       </c>
       <c r="C83">
-        <v>-1184.865700726791</v>
+        <v>-1223.25391204115</v>
       </c>
       <c r="D83">
-        <v>857.5012992732087</v>
+        <v>849.5200879588506</v>
       </c>
       <c r="E83">
-        <v>1596.167</v>
+        <v>1626.574</v>
       </c>
       <c r="F83">
-        <v>2462.967</v>
+        <v>2493.374</v>
       </c>
       <c r="G83">
         <v>420.6</v>
@@ -8093,28 +8093,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M83">
-        <v>714.943135382916</v>
+        <v>723.7695938444335</v>
       </c>
       <c r="N83">
-        <v>-408.7875798273604</v>
+        <v>-417.614038288878</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-408.7875798273604</v>
+        <v>-417.614038288878</v>
       </c>
       <c r="Q83">
-        <v>-227.3875798273604</v>
+        <v>-236.214038288878</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3731420162891163</v>
+        <v>0.3913276838607339</v>
       </c>
       <c r="T83">
-        <v>2.803940916238543</v>
+        <v>2.959715411585128</v>
       </c>
       <c r="U83">
         <v>0.2902771881973717</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4282236452156183</v>
+        <v>0.423001405639818</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3084662774167769</v>
+        <v>0.3109110492987506</v>
       </c>
       <c r="C84">
-        <v>-1223.25391204115</v>
+        <v>-1261.494922844196</v>
       </c>
       <c r="D84">
-        <v>849.5200879588506</v>
+        <v>841.6860771558033</v>
       </c>
       <c r="E84">
-        <v>1626.574</v>
+        <v>1656.981</v>
       </c>
       <c r="F84">
-        <v>2493.374</v>
+        <v>2523.781</v>
       </c>
       <c r="G84">
         <v>420.6</v>
@@ -8175,28 +8175,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M84">
-        <v>723.7695938444335</v>
+        <v>732.5960523059509</v>
       </c>
       <c r="N84">
-        <v>-417.614038288878</v>
+        <v>-426.4404967503954</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-417.614038288878</v>
+        <v>-426.4404967503954</v>
       </c>
       <c r="Q84">
-        <v>-236.214038288878</v>
+        <v>-245.0404967503954</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3913276838607339</v>
+        <v>0.4116528417348947</v>
       </c>
       <c r="T84">
-        <v>2.959715411585128</v>
+        <v>3.13381631814896</v>
       </c>
       <c r="U84">
         <v>0.2902771881973717</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.423001405639818</v>
+        <v>0.4179050031622299</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3109110492987506</v>
+        <v>0.3133558211807244</v>
       </c>
       <c r="C85">
-        <v>-1261.494922844196</v>
+        <v>-1299.592768237874</v>
       </c>
       <c r="D85">
-        <v>841.6860771558033</v>
+        <v>833.9952317621261</v>
       </c>
       <c r="E85">
-        <v>1656.981</v>
+        <v>1687.388</v>
       </c>
       <c r="F85">
-        <v>2523.781</v>
+        <v>2554.188</v>
       </c>
       <c r="G85">
         <v>420.6</v>
@@ -8257,28 +8257,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M85">
-        <v>732.5960523059509</v>
+        <v>741.4225107674685</v>
       </c>
       <c r="N85">
-        <v>-426.4404967503954</v>
+        <v>-435.2669552119129</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-426.4404967503954</v>
+        <v>-435.2669552119129</v>
       </c>
       <c r="Q85">
-        <v>-245.0404967503954</v>
+        <v>-253.8669552119129</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4116528417348947</v>
+        <v>0.4345186443433258</v>
       </c>
       <c r="T85">
-        <v>3.13381631814896</v>
+        <v>3.32967983803327</v>
       </c>
       <c r="U85">
         <v>0.2902771881973717</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4179050031622299</v>
+        <v>0.4129299436007747</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3133558211807243</v>
+        <v>0.315800593062698</v>
       </c>
       <c r="C86">
-        <v>-1299.592768237873</v>
+        <v>-1337.551337177719</v>
       </c>
       <c r="D86">
-        <v>833.9952317621263</v>
+        <v>826.4436628222807</v>
       </c>
       <c r="E86">
-        <v>1687.388</v>
+        <v>1717.795</v>
       </c>
       <c r="F86">
-        <v>2554.188</v>
+        <v>2584.595</v>
       </c>
       <c r="G86">
         <v>420.6</v>
@@ -8339,28 +8339,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M86">
-        <v>741.4225107674683</v>
+        <v>750.2489692289859</v>
       </c>
       <c r="N86">
-        <v>-435.2669552119128</v>
+        <v>-444.0934136734303</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-435.2669552119128</v>
+        <v>-444.0934136734303</v>
       </c>
       <c r="Q86">
-        <v>-253.8669552119128</v>
+        <v>-262.6934136734303</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4345186443433255</v>
+        <v>0.4604332206328805</v>
       </c>
       <c r="T86">
-        <v>3.329679838033268</v>
+        <v>3.551658493902153</v>
       </c>
       <c r="U86">
         <v>0.2902771881973717</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4129299436007748</v>
+        <v>0.4080719442642951</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.315800593062698</v>
+        <v>0.3182453649446718</v>
       </c>
       <c r="C87">
-        <v>-1337.551337177719</v>
+        <v>-1375.37437903005</v>
       </c>
       <c r="D87">
-        <v>826.4436628222807</v>
+        <v>819.0276209699496</v>
       </c>
       <c r="E87">
-        <v>1717.795</v>
+        <v>1748.202</v>
       </c>
       <c r="F87">
-        <v>2584.595</v>
+        <v>2615.002</v>
       </c>
       <c r="G87">
         <v>420.6</v>
@@ -8421,28 +8421,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M87">
-        <v>750.2489692289859</v>
+        <v>759.0754276905034</v>
       </c>
       <c r="N87">
-        <v>-444.0934136734303</v>
+        <v>-452.9198721349478</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-444.0934136734303</v>
+        <v>-452.9198721349478</v>
       </c>
       <c r="Q87">
-        <v>-262.6934136734303</v>
+        <v>-271.5198721349478</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4604332206328805</v>
+        <v>0.4900498792495149</v>
       </c>
       <c r="T87">
-        <v>3.551658493902153</v>
+        <v>3.805348386323735</v>
       </c>
       <c r="U87">
         <v>0.2902771881973717</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4080719442642951</v>
+        <v>0.4033269216565707</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3182453649446718</v>
+        <v>0.3206901368266454</v>
       </c>
       <c r="C88">
-        <v>-1375.37437903005</v>
+        <v>-1413.065509779237</v>
       </c>
       <c r="D88">
-        <v>819.0276209699496</v>
+        <v>811.7434902207626</v>
       </c>
       <c r="E88">
-        <v>1748.202</v>
+        <v>1778.609</v>
       </c>
       <c r="F88">
-        <v>2615.002</v>
+        <v>2645.409</v>
       </c>
       <c r="G88">
         <v>420.6</v>
@@ -8503,28 +8503,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M88">
-        <v>759.0754276905034</v>
+        <v>767.9018861520208</v>
       </c>
       <c r="N88">
-        <v>-452.9198721349478</v>
+        <v>-461.7463305964652</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-452.9198721349478</v>
+        <v>-461.7463305964652</v>
       </c>
       <c r="Q88">
-        <v>-271.5198721349478</v>
+        <v>-280.3463305964652</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4900498792495149</v>
+        <v>0.5242229468840929</v>
       </c>
       <c r="T88">
-        <v>3.805348386323735</v>
+        <v>4.098067492964022</v>
       </c>
       <c r="U88">
         <v>0.2902771881973717</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4033269216565707</v>
+        <v>0.3986909800283344</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3206901368266454</v>
+        <v>0.3231349087086192</v>
       </c>
       <c r="C89">
-        <v>-1413.065509779237</v>
+        <v>-1450.628217906669</v>
       </c>
       <c r="D89">
-        <v>811.7434902207626</v>
+        <v>804.5877820933307</v>
       </c>
       <c r="E89">
-        <v>1778.609</v>
+        <v>1809.016</v>
       </c>
       <c r="F89">
-        <v>2645.409</v>
+        <v>2675.816</v>
       </c>
       <c r="G89">
         <v>420.6</v>
@@ -8585,28 +8585,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M89">
-        <v>767.9018861520208</v>
+        <v>776.7283446135383</v>
       </c>
       <c r="N89">
-        <v>-461.7463305964652</v>
+        <v>-470.5727890579827</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-461.7463305964652</v>
+        <v>-470.5727890579827</v>
       </c>
       <c r="Q89">
-        <v>-280.3463305964652</v>
+        <v>-289.1727890579828</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5242229468840929</v>
+        <v>0.5640915257911007</v>
       </c>
       <c r="T89">
-        <v>4.098067492964022</v>
+        <v>4.439573117377692</v>
       </c>
       <c r="U89">
         <v>0.2902771881973717</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3986909800283344</v>
+        <v>0.3941604007098305</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3231349087086192</v>
+        <v>0.3255796805905929</v>
       </c>
       <c r="C90">
-        <v>-1450.628217906669</v>
+        <v>-1488.06586996149</v>
       </c>
       <c r="D90">
-        <v>804.5877820933307</v>
+        <v>797.5571300385096</v>
       </c>
       <c r="E90">
-        <v>1809.016</v>
+        <v>1839.423</v>
       </c>
       <c r="F90">
-        <v>2675.816</v>
+        <v>2706.223</v>
       </c>
       <c r="G90">
         <v>420.6</v>
@@ -8667,28 +8667,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M90">
-        <v>776.7283446135383</v>
+        <v>785.5548030750558</v>
       </c>
       <c r="N90">
-        <v>-470.5727890579827</v>
+        <v>-479.3992475195002</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-470.5727890579827</v>
+        <v>-479.3992475195002</v>
       </c>
       <c r="Q90">
-        <v>-289.1727890579828</v>
+        <v>-297.9992475195003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5640915257911007</v>
+        <v>0.6112089372266554</v>
       </c>
       <c r="T90">
-        <v>4.439573117377692</v>
+        <v>4.843170673502937</v>
       </c>
       <c r="U90">
         <v>0.2902771881973717</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3941604007098305</v>
+        <v>0.389731632162529</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3255796805905929</v>
+        <v>0.3280244524725666</v>
       </c>
       <c r="C91">
-        <v>-1488.06586996149</v>
+        <v>-1525.381715841793</v>
       </c>
       <c r="D91">
-        <v>797.5571300385096</v>
+        <v>790.6482841582068</v>
       </c>
       <c r="E91">
-        <v>1839.423</v>
+        <v>1869.83</v>
       </c>
       <c r="F91">
-        <v>2706.223</v>
+        <v>2736.63</v>
       </c>
       <c r="G91">
         <v>420.6</v>
@@ -8749,28 +8749,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M91">
-        <v>785.5548030750558</v>
+        <v>794.3812615365733</v>
       </c>
       <c r="N91">
-        <v>-479.3992475195002</v>
+        <v>-488.2257059810178</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-479.3992475195002</v>
+        <v>-488.2257059810178</v>
       </c>
       <c r="Q91">
-        <v>-297.9992475195003</v>
+        <v>-306.8257059810178</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6112089372266554</v>
+        <v>0.6677498309493209</v>
       </c>
       <c r="T91">
-        <v>4.843170673502937</v>
+        <v>5.327487740853231</v>
       </c>
       <c r="U91">
         <v>0.2902771881973717</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.389731632162529</v>
+        <v>0.3854012806940564</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3280244524725666</v>
+        <v>0.3304692243545403</v>
       </c>
       <c r="C92">
-        <v>-1525.381715841793</v>
+        <v>-1562.578893803684</v>
       </c>
       <c r="D92">
-        <v>790.6482841582068</v>
+        <v>783.858106196316</v>
       </c>
       <c r="E92">
-        <v>1869.83</v>
+        <v>1900.237</v>
       </c>
       <c r="F92">
-        <v>2736.63</v>
+        <v>2767.037</v>
       </c>
       <c r="G92">
         <v>420.6</v>
@@ -8831,28 +8831,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M92">
-        <v>794.3812615365733</v>
+        <v>803.2077199980907</v>
       </c>
       <c r="N92">
-        <v>-488.2257059810178</v>
+        <v>-497.0521644425352</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-488.2257059810178</v>
+        <v>-497.0521644425352</v>
       </c>
       <c r="Q92">
-        <v>-306.8257059810178</v>
+        <v>-315.6521644425352</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6677498309493209</v>
+        <v>0.7368553677214678</v>
       </c>
       <c r="T92">
-        <v>5.327487740853231</v>
+        <v>5.919430823170257</v>
       </c>
       <c r="U92">
         <v>0.2902771881973717</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3854012806940564</v>
+        <v>0.3811661017853306</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3304692243545403</v>
+        <v>0.3329139962365141</v>
       </c>
       <c r="C93">
-        <v>-1562.578893803684</v>
+        <v>-1599.660435214432</v>
       </c>
       <c r="D93">
-        <v>783.858106196316</v>
+        <v>777.1835647855681</v>
       </c>
       <c r="E93">
-        <v>1900.237</v>
+        <v>1930.644</v>
       </c>
       <c r="F93">
-        <v>2767.037</v>
+        <v>2797.444</v>
       </c>
       <c r="G93">
         <v>420.6</v>
@@ -8913,28 +8913,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M93">
-        <v>803.2077199980907</v>
+        <v>812.0341784596083</v>
       </c>
       <c r="N93">
-        <v>-497.0521644425352</v>
+        <v>-505.8786229040527</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-497.0521644425352</v>
+        <v>-505.8786229040527</v>
       </c>
       <c r="Q93">
-        <v>-315.6521644425352</v>
+        <v>-324.4786229040527</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7368553677214678</v>
+        <v>0.8232372886866515</v>
       </c>
       <c r="T93">
-        <v>5.919430823170257</v>
+        <v>6.659359676066541</v>
       </c>
       <c r="U93">
         <v>0.2902771881973717</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3811661017853306</v>
+        <v>0.3770229919833161</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3329139962365141</v>
+        <v>0.3353587681184877</v>
       </c>
       <c r="C94">
-        <v>-1599.660435214432</v>
+        <v>-1636.629269064832</v>
       </c>
       <c r="D94">
-        <v>777.1835647855681</v>
+        <v>770.6217309351687</v>
       </c>
       <c r="E94">
-        <v>1930.644</v>
+        <v>1961.051</v>
       </c>
       <c r="F94">
-        <v>2797.444</v>
+        <v>2827.851</v>
       </c>
       <c r="G94">
         <v>420.6</v>
@@ -8995,28 +8995,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M94">
-        <v>812.0341784596083</v>
+        <v>820.8606369211258</v>
       </c>
       <c r="N94">
-        <v>-505.8786229040527</v>
+        <v>-514.7050813655702</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-505.8786229040527</v>
+        <v>-514.7050813655702</v>
       </c>
       <c r="Q94">
-        <v>-324.4786229040527</v>
+        <v>-333.3050813655702</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8232372886866515</v>
+        <v>0.9342997584990302</v>
       </c>
       <c r="T94">
-        <v>6.659359676066541</v>
+        <v>7.610696772647476</v>
       </c>
       <c r="U94">
         <v>0.2902771881973717</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3770229919833161</v>
+        <v>0.3729689813168289</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3353587681184877</v>
+        <v>0.3378035400004615</v>
       </c>
       <c r="C95">
-        <v>-1636.629269064832</v>
+        <v>-1673.488226254889</v>
       </c>
       <c r="D95">
-        <v>770.6217309351687</v>
+        <v>764.1697737451113</v>
       </c>
       <c r="E95">
-        <v>1961.051</v>
+        <v>1991.458</v>
       </c>
       <c r="F95">
-        <v>2827.851</v>
+        <v>2858.258</v>
       </c>
       <c r="G95">
         <v>420.6</v>
@@ -9077,28 +9077,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M95">
-        <v>820.8606369211258</v>
+        <v>829.6870953826432</v>
       </c>
       <c r="N95">
-        <v>-514.7050813655702</v>
+        <v>-523.5315398270876</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-514.7050813655702</v>
+        <v>-523.5315398270876</v>
       </c>
       <c r="Q95">
-        <v>-333.3050813655702</v>
+        <v>-342.1315398270876</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9342997584990302</v>
+        <v>1.082383051582202</v>
       </c>
       <c r="T95">
-        <v>7.610696772647476</v>
+        <v>8.879146234755391</v>
       </c>
       <c r="U95">
         <v>0.2902771881973717</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3729689813168289</v>
+        <v>0.369001226196437</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3378035400004615</v>
+        <v>0.3402483118824352</v>
       </c>
       <c r="C96">
-        <v>-1673.488226254889</v>
+        <v>-1710.240043666008</v>
       </c>
       <c r="D96">
-        <v>764.1697737451113</v>
+        <v>757.8249563339922</v>
       </c>
       <c r="E96">
-        <v>1991.458</v>
+        <v>2021.865</v>
       </c>
       <c r="F96">
-        <v>2858.258</v>
+        <v>2888.665</v>
       </c>
       <c r="G96">
         <v>420.6</v>
@@ -9159,28 +9159,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M96">
-        <v>829.6870953826432</v>
+        <v>838.5135538441607</v>
       </c>
       <c r="N96">
-        <v>-523.5315398270876</v>
+        <v>-532.3579982886051</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-523.5315398270876</v>
+        <v>-532.3579982886051</v>
       </c>
       <c r="Q96">
-        <v>-342.1315398270876</v>
+        <v>-350.9579982886052</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.082383051582202</v>
+        <v>1.289699661898643</v>
       </c>
       <c r="T96">
-        <v>8.879146234755391</v>
+        <v>10.65497548170647</v>
       </c>
       <c r="U96">
         <v>0.2902771881973717</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.369001226196437</v>
+        <v>0.3651170027627904</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3402483118824352</v>
+        <v>0.3426930837644089</v>
       </c>
       <c r="C97">
-        <v>-1710.240043666008</v>
+        <v>-1746.887368031979</v>
       </c>
       <c r="D97">
-        <v>757.8249563339922</v>
+        <v>751.5846319680213</v>
       </c>
       <c r="E97">
-        <v>2021.865</v>
+        <v>2052.272</v>
       </c>
       <c r="F97">
-        <v>2888.665</v>
+        <v>2919.072</v>
       </c>
       <c r="G97">
         <v>420.6</v>
@@ -9241,28 +9241,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M97">
-        <v>838.5135538441607</v>
+        <v>847.3400123056782</v>
       </c>
       <c r="N97">
-        <v>-532.3579982886051</v>
+        <v>-541.1844567501226</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-532.3579982886051</v>
+        <v>-541.1844567501226</v>
       </c>
       <c r="Q97">
-        <v>-350.9579982886052</v>
+        <v>-359.7844567501227</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.289699661898643</v>
+        <v>1.600674577373305</v>
       </c>
       <c r="T97">
-        <v>10.65497548170647</v>
+        <v>13.3187193521331</v>
       </c>
       <c r="U97">
         <v>0.2902771881973717</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3651170027627904</v>
+        <v>0.3613137006506779</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3426930837644089</v>
+        <v>0.3451378556463826</v>
       </c>
       <c r="C98">
-        <v>-1746.887368031978</v>
+        <v>-1783.432759620277</v>
       </c>
       <c r="D98">
-        <v>751.5846319680213</v>
+        <v>745.446240379723</v>
       </c>
       <c r="E98">
-        <v>2052.272</v>
+        <v>2082.679</v>
       </c>
       <c r="F98">
-        <v>2919.072</v>
+        <v>2949.479</v>
       </c>
       <c r="G98">
         <v>420.6</v>
@@ -9323,28 +9323,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M98">
-        <v>847.3400123056781</v>
+        <v>856.1664707671956</v>
       </c>
       <c r="N98">
-        <v>-541.1844567501225</v>
+        <v>-550.0109152116401</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-541.1844567501225</v>
+        <v>-550.0109152116401</v>
       </c>
       <c r="Q98">
-        <v>-359.7844567501226</v>
+        <v>-368.6109152116401</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.600674577373301</v>
+        <v>2.118966103164401</v>
       </c>
       <c r="T98">
-        <v>13.31871935213306</v>
+        <v>17.75829246951075</v>
       </c>
       <c r="U98">
         <v>0.2902771881973717</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3613137006506779</v>
+        <v>0.3575888171388153</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3451378556463826</v>
+        <v>0.3475826275283563</v>
       </c>
       <c r="C99">
-        <v>-1783.432759620277</v>
+        <v>-1819.878695734425</v>
       </c>
       <c r="D99">
-        <v>745.446240379723</v>
+        <v>739.4073042655754</v>
       </c>
       <c r="E99">
-        <v>2082.679</v>
+        <v>2113.086</v>
       </c>
       <c r="F99">
-        <v>2949.479</v>
+        <v>2979.886</v>
       </c>
       <c r="G99">
         <v>420.6</v>
@@ -9405,28 +9405,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M99">
-        <v>856.1664707671956</v>
+        <v>864.9929292287131</v>
       </c>
       <c r="N99">
-        <v>-550.0109152116401</v>
+        <v>-558.8373736731576</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-550.0109152116401</v>
+        <v>-558.8373736731576</v>
       </c>
       <c r="Q99">
-        <v>-368.6109152116401</v>
+        <v>-377.4373736731576</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.118966103164401</v>
+        <v>3.155549154746601</v>
       </c>
       <c r="T99">
-        <v>17.75829246951075</v>
+        <v>26.63743870426612</v>
       </c>
       <c r="U99">
         <v>0.2902771881973717</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3575888171388153</v>
+        <v>0.353939951657807</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3475826275283563</v>
+        <v>0.35002739941033</v>
       </c>
       <c r="C100">
-        <v>-1819.878695734425</v>
+        <v>-1856.227574047483</v>
       </c>
       <c r="D100">
-        <v>739.4073042655754</v>
+        <v>733.4654259525169</v>
       </c>
       <c r="E100">
-        <v>2113.086</v>
+        <v>2143.492999999999</v>
       </c>
       <c r="F100">
-        <v>2979.886</v>
+        <v>3010.293</v>
       </c>
       <c r="G100">
         <v>420.6</v>
@@ -9487,28 +9487,28 @@
         <v>306.1555555555556</v>
       </c>
       <c r="M100">
-        <v>864.9929292287131</v>
+        <v>873.8193876902305</v>
       </c>
       <c r="N100">
-        <v>-558.8373736731576</v>
+        <v>-567.663832134675</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-558.8373736731576</v>
+        <v>-567.663832134675</v>
       </c>
       <c r="Q100">
-        <v>-377.4373736731576</v>
+        <v>-386.263832134675</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.155549154746601</v>
+        <v>6.265298309493203</v>
       </c>
       <c r="T100">
-        <v>26.63743870426612</v>
+        <v>53.27487740853225</v>
       </c>
       <c r="U100">
         <v>0.2902771881973717</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.353939951657807</v>
+        <v>0.3503648006309604</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.35002739941033</v>
-      </c>
-      <c r="C101">
-        <v>-1856.227574047483</v>
-      </c>
-      <c r="D101">
-        <v>733.4654259525169</v>
-      </c>
-      <c r="E101">
-        <v>2143.492999999999</v>
-      </c>
-      <c r="F101">
-        <v>3010.293</v>
-      </c>
-      <c r="G101">
-        <v>420.6</v>
-      </c>
-      <c r="H101">
-        <v>2173.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>487.5555555555555</v>
-      </c>
-      <c r="K101">
-        <v>181.4</v>
-      </c>
-      <c r="L101">
-        <v>306.1555555555556</v>
-      </c>
-      <c r="M101">
-        <v>873.8193876902305</v>
-      </c>
-      <c r="N101">
-        <v>-567.663832134675</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-567.663832134675</v>
-      </c>
-      <c r="Q101">
-        <v>-386.263832134675</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.265298309493203</v>
-      </c>
-      <c r="T101">
-        <v>53.27487740853225</v>
-      </c>
-      <c r="U101">
-        <v>0.2902771881973717</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2902771881973717</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3503648006309604</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
